--- a/Tubex_Sep26.xlsx
+++ b/Tubex_Sep26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_5D606E3DB825CB99FE44BD0EA86C5E9C9D66ACCD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_D15FADB0A5B5DBFA451313CDACCE3ADB82CCEB8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6036" uniqueCount="908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6062" uniqueCount="909">
   <si>
     <t>SEPTEMBER 2026 Tube Required Orders</t>
   </si>
@@ -1792,7 +1792,7 @@
     <t>Top 10 inks = 81.7% of all consumption. Remaining 15 inks share 18.3%.  Source: ERP ST_Stk_Cons_YFI.rpt · May 2025–Apr 2026 · 8,617,293 pcs produced.</t>
   </si>
   <si>
-    <t>FG STOCK IN HAND — Last Updated: 23-Sep-2026</t>
+    <t>FG STOCK IN HAND — Last Updated: 24-Sep-2026</t>
   </si>
   <si>
     <t>Shows latest date only from FG Stock In hand (Production.xlsx). Older dates are discarded. Re-run update_production.py to refresh.</t>
@@ -1844,6 +1844,9 @@
   </si>
   <si>
     <t>Inprogress On Packing</t>
+  </si>
+  <si>
+    <t>Inprogress On Latex</t>
   </si>
   <si>
     <t>32</t>
@@ -5002,10 +5005,10 @@
     <xf numFmtId="168" fontId="85" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="47" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="47" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="45" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="45" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -5548,8 +5551,8 @@
     <col min="13" max="13" width="14.7109375" style="90" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" style="90" customWidth="1"/>
     <col min="15" max="15" width="9.5703125" style="90" customWidth="1"/>
-    <col min="16" max="218" width="8.7109375" style="90" customWidth="1"/>
-    <col min="219" max="16384" width="8.7109375" style="90"/>
+    <col min="16" max="219" width="8.7109375" style="90" customWidth="1"/>
+    <col min="220" max="16384" width="8.7109375" style="90"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -5627,7 +5630,7 @@
       <c r="G3" s="321"/>
       <c r="H3" s="323">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="I3" s="319"/>
       <c r="J3" s="319"/>
@@ -5688,7 +5691,7 @@
       </c>
       <c r="C5" s="144">
         <f>MAX(Production_Log!$A$3:$A$8961)</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D5" s="92" t="s">
         <v>155</v>
@@ -5729,18 +5732,18 @@
       <c r="A6" s="87"/>
       <c r="B6" s="322">
         <f>SUMPRODUCT((Production_Log!$A$3:$A$8961=MAX(Production_Log!$A$3:$A$8961))*(LEFT(Production_Log!$B$3:$B$8961,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8961)))*Production_Log!$H$3:$H$8961)</f>
-        <v>4990</v>
+        <v>28084</v>
       </c>
       <c r="C6" s="319"/>
       <c r="D6" s="95">
         <f>SUMIF($B$11:$B$67,"TUBE",$H$11:$H$67)</f>
-        <v>278704</v>
+        <v>306788</v>
       </c>
       <c r="E6" s="322"/>
       <c r="F6" s="319"/>
       <c r="G6" s="96">
         <f t="array" ref="G6">IFERROR(SUMPRODUCT((Production_Log!$F$3:$F$8961&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8961,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8961)))*Production_Log!$I$3:$I$8961)/SUMPRODUCT((Production_Log!$F$3:$F$8961&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8961,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8961)))*(Production_Log!$H$3:$H$8961+Production_Log!$I$3:$I$8961)),"-")</f>
-        <v>2.4039724199755575E-2</v>
+        <v>2.3910048583691532E-2</v>
       </c>
       <c r="H6" s="96"/>
       <c r="I6" s="94"/>
@@ -5781,7 +5784,7 @@
       </c>
       <c r="C7" s="145">
         <f>MAX(Production_Log!$A$3:$A$8961)</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D7" s="98" t="s">
         <v>162</v>
@@ -5807,7 +5810,7 @@
       </c>
       <c r="O7" s="285">
         <f>IFERROR(N7/$N$12,"")</f>
-        <v>0.45945945945945948</v>
+        <v>0.45333333333333331</v>
       </c>
       <c r="P7" s="279"/>
       <c r="Q7" s="279"/>
@@ -5828,24 +5831,24 @@
       <c r="A8" s="87"/>
       <c r="B8" s="329">
         <f>SUMPRODUCT((Production_Log!$A$3:$A$8961=MAX(Production_Log!$A$3:$A$8961))*(Production_Log!$B$3:$B$8961="PF Machine")*Production_Log!$H$3:$H$8961)</f>
-        <v>6120</v>
+        <v>3600</v>
       </c>
       <c r="C8" s="319"/>
       <c r="D8" s="101">
         <f>SUMIF($B$11:$B$67,"PET",$H$11:$H$67)</f>
-        <v>259620</v>
+        <v>267180</v>
       </c>
       <c r="E8" s="329"/>
       <c r="F8" s="319"/>
       <c r="G8" s="102">
         <f t="array" ref="G8">IFERROR(SUMPRODUCT((Production_Log!$B$3:$B$8961="PF Machine")*Production_Log!$I$3:$I$8961)/SUMPRODUCT((Production_Log!$B$3:$B$8961="PF Machine")*(Production_Log!$H$3:$H$8961+Production_Log!$I$3:$I$8961)),0)</f>
-        <v>0.18990264603095358</v>
+        <v>0.19941269888832289</v>
       </c>
       <c r="H8" s="102"/>
       <c r="I8" s="100"/>
       <c r="J8" s="329">
         <f>SUMIF($B$11:$B$67,"PET",$K$11:$K$67)</f>
-        <v>223480</v>
+        <v>250960</v>
       </c>
       <c r="K8" s="319"/>
       <c r="L8" s="103"/>
@@ -5858,7 +5861,7 @@
       </c>
       <c r="O8" s="285">
         <f>IFERROR(N8/$N$12,"")</f>
-        <v>0.22747747747747746</v>
+        <v>0.22444444444444442</v>
       </c>
       <c r="P8" s="279"/>
       <c r="Q8" s="279"/>
@@ -5895,11 +5898,11 @@
       </c>
       <c r="N9" s="284">
         <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,5)="Press")+(LEFT(Production_Log!$B$3:$B$1000,5)="Print")+(LEFT(Production_Log!$B$3:$B$1000,5)="PLINE"))*Production_Log!$K$3:$K$1000)/60</f>
-        <v>10.666666666666666</v>
+        <v>11.666666666666666</v>
       </c>
       <c r="O9" s="285">
         <f>IFERROR(N9/$N$12,"")</f>
-        <v>0.14414414414414414</v>
+        <v>0.15555555555555556</v>
       </c>
       <c r="P9" s="279"/>
       <c r="Q9" s="279"/>
@@ -5960,7 +5963,7 @@
       </c>
       <c r="O10" s="285">
         <f>IFERROR(N10/$N$12,"")</f>
-        <v>0.10135135135135136</v>
+        <v>0.1</v>
       </c>
       <c r="P10" s="279"/>
       <c r="Q10" s="279"/>
@@ -6021,7 +6024,7 @@
       </c>
       <c r="O11" s="285">
         <f>IFERROR(N11/$N$12,"")</f>
-        <v>6.7567567567567571E-2</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="P11" s="279"/>
       <c r="Q11" s="279"/>
@@ -6080,7 +6083,7 @@
       </c>
       <c r="N12" s="297">
         <f>SUM(N7:N11)</f>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O12" s="298" t="s">
         <v>178</v>
@@ -6232,15 +6235,15 @@
       </c>
       <c r="H15" s="292">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$1000=F15)*((LEFT(Production_Log!$B$3:$B$1000,5)="Print")+(LEFT(Production_Log!$B$3:$B$1000,5)="PLINE"))*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$1000)))*Production_Log!$H$3:$H$1000)</f>
-        <v>169924</v>
+        <v>198008</v>
       </c>
       <c r="I15" s="291">
         <f t="shared" si="0"/>
-        <v>530076</v>
+        <v>501992</v>
       </c>
       <c r="J15" s="293">
         <f t="shared" si="1"/>
-        <v>0.24274857142857142</v>
+        <v>0.28286857142857141</v>
       </c>
       <c r="K15" s="292">
         <v>152558</v>
@@ -6308,8 +6311,8 @@
         <v>52.833333333333336</v>
       </c>
       <c r="O16" s="285">
-        <f>IFERROR(N16/$N$21,"")</f>
-        <v>0.37032710280373826</v>
+        <f t="shared" ref="O16:O21" si="2">IFERROR(N16/$N$22,"")</f>
+        <v>0.3192346424974824</v>
       </c>
       <c r="P16" s="279"/>
       <c r="Q16" s="279"/>
@@ -6371,8 +6374,8 @@
         <v>31.833333333333332</v>
       </c>
       <c r="O17" s="285">
-        <f>IFERROR(N17/$N$21,"")</f>
-        <v>0.22313084112149528</v>
+        <f t="shared" si="2"/>
+        <v>0.19234642497482377</v>
       </c>
       <c r="P17" s="279"/>
       <c r="Q17" s="279"/>
@@ -6404,15 +6407,15 @@
       </c>
       <c r="H18" s="306">
         <f>SUM(H11:H17)</f>
-        <v>278704</v>
+        <v>306788</v>
       </c>
       <c r="I18" s="306">
         <f>SUMIF(I11:I17,"&gt;"&amp;0)</f>
-        <v>774412</v>
+        <v>746328</v>
       </c>
       <c r="J18" s="307">
         <f t="shared" si="1"/>
-        <v>0.26553050079457935</v>
+        <v>0.29228705464495452</v>
       </c>
       <c r="K18" s="306">
         <f>SUM(K11:K17)</f>
@@ -6427,8 +6430,8 @@
         <v>21.833333333333332</v>
       </c>
       <c r="O18" s="285">
-        <f>IFERROR(N18/$N$21,"")</f>
-        <v>0.15303738317757007</v>
+        <f t="shared" si="2"/>
+        <v>0.13192346424974824</v>
       </c>
       <c r="P18" s="279"/>
       <c r="Q18" s="279"/>
@@ -6471,7 +6474,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="291">
-        <f t="shared" ref="I19:I24" si="2">G19-H19</f>
+        <f t="shared" ref="I19:I24" si="3">G19-H19</f>
         <v>25000</v>
       </c>
       <c r="J19" s="293">
@@ -6481,15 +6484,15 @@
       <c r="K19" s="292"/>
       <c r="L19" s="294"/>
       <c r="M19" s="283" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="N19" s="284">
-        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,2)="PF")+(LEFT(Production_Log!$B$3:$B$1000,3)="PET"))*Production_Log!$N$3:$N$1000)/60</f>
-        <v>19.166666666666668</v>
+        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,2)="PF")+(LEFT(Production_Log!$B$3:$B$1000,3)="PET"))*Production_Log!$S$3:$S$1000)/60</f>
+        <v>21</v>
       </c>
       <c r="O19" s="285">
-        <f>IFERROR(N19/$N$21,"")</f>
-        <v>0.13434579439252337</v>
+        <f t="shared" si="2"/>
+        <v>0.12688821752265861</v>
       </c>
       <c r="P19" s="279"/>
       <c r="Q19" s="279"/>
@@ -6529,30 +6532,30 @@
       </c>
       <c r="H20" s="292">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$1000=F20)*Production_Log!$H$3:$H$1000)</f>
-        <v>32880</v>
+        <v>36840</v>
       </c>
       <c r="I20" s="291">
-        <f t="shared" si="2"/>
-        <v>27280</v>
+        <f t="shared" si="3"/>
+        <v>23320</v>
       </c>
       <c r="J20" s="293">
         <f t="shared" si="1"/>
-        <v>0.54654255319148937</v>
+        <v>0.6123670212765957</v>
       </c>
       <c r="K20" s="292">
-        <v>32880</v>
+        <v>36840</v>
       </c>
       <c r="L20" s="294"/>
       <c r="M20" s="283" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="N20" s="284">
-        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,2)="PF")+(LEFT(Production_Log!$B$3:$B$1000,3)="PET"))*Production_Log!$S$3:$S$1000)/60</f>
-        <v>17</v>
+        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,2)="PF")+(LEFT(Production_Log!$B$3:$B$1000,3)="PET"))*Production_Log!$N$3:$N$1000)/60</f>
+        <v>19.166666666666668</v>
       </c>
       <c r="O20" s="285">
-        <f>IFERROR(N20/$N$21,"")</f>
-        <v>0.11915887850467288</v>
+        <f t="shared" si="2"/>
+        <v>0.11581067472306143</v>
       </c>
       <c r="P20" s="279"/>
       <c r="Q20" s="279"/>
@@ -6595,7 +6598,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="291">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9480</v>
       </c>
       <c r="J21" s="293">
@@ -6604,15 +6607,16 @@
       </c>
       <c r="K21" s="292"/>
       <c r="L21" s="294"/>
-      <c r="M21" s="296" t="s">
-        <v>177</v>
-      </c>
-      <c r="N21" s="297">
-        <f>SUM(N16:N20)</f>
-        <v>142.66666666666669</v>
-      </c>
-      <c r="O21" s="298" t="s">
-        <v>178</v>
+      <c r="M21" s="283" t="s">
+        <v>176</v>
+      </c>
+      <c r="N21" s="284">
+        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,2)="PF")+(LEFT(Production_Log!$B$3:$B$1000,3)="PET"))*Production_Log!$O$3:$O$1000)/60</f>
+        <v>18.833333333333332</v>
+      </c>
+      <c r="O21" s="285">
+        <f t="shared" si="2"/>
+        <v>0.11379657603222557</v>
       </c>
       <c r="P21" s="279"/>
       <c r="Q21" s="279"/>
@@ -6655,7 +6659,7 @@
         <v>203220</v>
       </c>
       <c r="I22" s="291">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>549967</v>
       </c>
       <c r="J22" s="293">
@@ -6666,13 +6670,20 @@
         <v>190440</v>
       </c>
       <c r="L22" s="294"/>
-      <c r="M22" s="308"/>
-      <c r="N22" s="309"/>
-      <c r="O22" s="310"/>
+      <c r="M22" s="296" t="s">
+        <v>177</v>
+      </c>
+      <c r="N22" s="297">
+        <f>SUM(N16:N21)</f>
+        <v>165.5</v>
+      </c>
+      <c r="O22" s="298" t="s">
+        <v>178</v>
+      </c>
       <c r="P22" s="279"/>
       <c r="Q22" s="279"/>
       <c r="R22" s="279"/>
-      <c r="S22" s="311"/>
+      <c r="S22" s="308"/>
       <c r="T22" s="295"/>
       <c r="U22" s="295"/>
       <c r="V22" s="295"/>
@@ -6703,7 +6714,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="291">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J23" s="293" t="str">
@@ -6714,9 +6725,9 @@
         <v>160</v>
       </c>
       <c r="L23" s="294"/>
-      <c r="M23" s="308"/>
-      <c r="N23" s="309"/>
-      <c r="O23" s="310"/>
+      <c r="M23" s="309"/>
+      <c r="N23" s="310"/>
+      <c r="O23" s="311"/>
       <c r="P23" s="279"/>
       <c r="Q23" s="279"/>
       <c r="R23" s="279"/>
@@ -6755,21 +6766,23 @@
       </c>
       <c r="H24" s="292">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$1000=F24)*Production_Log!$H$3:$H$1000)</f>
-        <v>23520</v>
+        <v>27120</v>
       </c>
       <c r="I24" s="291">
-        <f t="shared" si="2"/>
-        <v>23480</v>
+        <f t="shared" si="3"/>
+        <v>19880</v>
       </c>
       <c r="J24" s="293">
         <f t="shared" si="1"/>
-        <v>0.50042553191489358</v>
-      </c>
-      <c r="K24" s="292"/>
+        <v>0.57702127659574465</v>
+      </c>
+      <c r="K24" s="292">
+        <v>23520</v>
+      </c>
       <c r="L24" s="294"/>
-      <c r="M24" s="308"/>
-      <c r="N24" s="309"/>
-      <c r="O24" s="310"/>
+      <c r="M24" s="309"/>
+      <c r="N24" s="310"/>
+      <c r="O24" s="311"/>
       <c r="P24" s="279"/>
       <c r="Q24" s="279"/>
       <c r="R24" s="279"/>
@@ -6800,24 +6813,24 @@
       </c>
       <c r="H25" s="306">
         <f>SUM(H19:H24)</f>
-        <v>259620</v>
+        <v>267180</v>
       </c>
       <c r="I25" s="306">
         <f>SUMIF(I19:I24,"&gt;"&amp;0)</f>
-        <v>635207</v>
+        <v>627647</v>
       </c>
       <c r="J25" s="307">
         <f t="shared" si="1"/>
-        <v>0.29013429411495184</v>
+        <v>0.29858285456294903</v>
       </c>
       <c r="K25" s="306">
         <f>SUM(K19:K24)</f>
-        <v>223480</v>
+        <v>250960</v>
       </c>
       <c r="L25" s="306"/>
-      <c r="M25" s="308"/>
-      <c r="N25" s="309"/>
-      <c r="O25" s="310"/>
+      <c r="M25" s="309"/>
+      <c r="N25" s="310"/>
+      <c r="O25" s="311"/>
       <c r="P25" s="279"/>
       <c r="Q25" s="279"/>
       <c r="R25" s="280"/>
@@ -6859,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="291">
-        <f t="shared" ref="I26:I67" si="3">G26-H26</f>
+        <f t="shared" ref="I26:I67" si="4">G26-H26</f>
         <v>0</v>
       </c>
       <c r="J26" s="293" t="str">
@@ -6868,9 +6881,9 @@
       </c>
       <c r="K26" s="292"/>
       <c r="L26" s="294"/>
-      <c r="M26" s="308"/>
-      <c r="N26" s="309"/>
-      <c r="O26" s="310"/>
+      <c r="M26" s="309"/>
+      <c r="N26" s="310"/>
+      <c r="O26" s="311"/>
       <c r="P26" s="279"/>
       <c r="Q26" s="279"/>
       <c r="R26" s="280"/>
@@ -6912,7 +6925,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J27" s="293" t="str">
@@ -6965,7 +6978,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J28" s="293" t="str">
@@ -7018,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J29" s="293" t="str">
@@ -7071,7 +7084,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J30" s="293" t="str">
@@ -7124,7 +7137,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J31" s="293" t="str">
@@ -7177,7 +7190,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J32" s="293" t="str">
@@ -7230,7 +7243,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J33" s="293" t="str">
@@ -7283,7 +7296,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J34" s="293" t="str">
@@ -7336,7 +7349,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J35" s="293" t="str">
@@ -7389,7 +7402,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J36" s="293" t="str">
@@ -7442,7 +7455,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J37" s="293" t="str">
@@ -7495,7 +7508,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J38" s="293" t="str">
@@ -7548,7 +7561,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J39" s="293" t="str">
@@ -7601,7 +7614,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J40" s="293" t="str">
@@ -7654,7 +7667,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J41" s="293" t="str">
@@ -7707,7 +7720,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J42" s="293" t="str">
@@ -7760,11 +7773,11 @@
         <v>0</v>
       </c>
       <c r="I43" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J43" s="293" t="str">
-        <f t="shared" ref="J43:J67" si="4">IF(G43=0,"-",H43/G43)</f>
+        <f t="shared" ref="J43:J67" si="5">IF(G43=0,"-",H43/G43)</f>
         <v>-</v>
       </c>
       <c r="K43" s="292"/>
@@ -7813,11 +7826,11 @@
         <v>0</v>
       </c>
       <c r="I44" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J44" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K44" s="292"/>
@@ -7866,11 +7879,11 @@
         <v>0</v>
       </c>
       <c r="I45" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J45" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K45" s="292"/>
@@ -7919,11 +7932,11 @@
         <v>0</v>
       </c>
       <c r="I46" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J46" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K46" s="292"/>
@@ -7972,11 +7985,11 @@
         <v>0</v>
       </c>
       <c r="I47" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J47" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K47" s="292"/>
@@ -8025,11 +8038,11 @@
         <v>0</v>
       </c>
       <c r="I48" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J48" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K48" s="292"/>
@@ -8078,11 +8091,11 @@
         <v>0</v>
       </c>
       <c r="I49" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J49" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K49" s="292"/>
@@ -8131,11 +8144,11 @@
         <v>0</v>
       </c>
       <c r="I50" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J50" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K50" s="292"/>
@@ -8184,11 +8197,11 @@
         <v>0</v>
       </c>
       <c r="I51" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J51" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K51" s="292"/>
@@ -8237,11 +8250,11 @@
         <v>0</v>
       </c>
       <c r="I52" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J52" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K52" s="292"/>
@@ -8290,11 +8303,11 @@
         <v>0</v>
       </c>
       <c r="I53" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J53" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K53" s="292"/>
@@ -8343,11 +8356,11 @@
         <v>0</v>
       </c>
       <c r="I54" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J54" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K54" s="292"/>
@@ -8396,11 +8409,11 @@
         <v>0</v>
       </c>
       <c r="I55" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J55" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K55" s="292"/>
@@ -8449,11 +8462,11 @@
         <v>0</v>
       </c>
       <c r="I56" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J56" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K56" s="292"/>
@@ -8502,11 +8515,11 @@
         <v>0</v>
       </c>
       <c r="I57" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J57" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K57" s="292"/>
@@ -8555,11 +8568,11 @@
         <v>0</v>
       </c>
       <c r="I58" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J58" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K58" s="292"/>
@@ -8607,11 +8620,11 @@
         <v>0</v>
       </c>
       <c r="I59" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J59" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K59" s="292"/>
@@ -8652,11 +8665,11 @@
         <v>0</v>
       </c>
       <c r="I60" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J60" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K60" s="292"/>
@@ -8697,11 +8710,11 @@
         <v>0</v>
       </c>
       <c r="I61" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J61" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K61" s="292"/>
@@ -8732,11 +8745,11 @@
         <v>0</v>
       </c>
       <c r="I62" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J62" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K62" s="292"/>
@@ -8768,11 +8781,11 @@
         <v>0</v>
       </c>
       <c r="I63" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J63" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K63" s="292"/>
@@ -8819,11 +8832,11 @@
         <v>0</v>
       </c>
       <c r="I64" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J64" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K64" s="292"/>
@@ -8869,11 +8882,11 @@
         <v>0</v>
       </c>
       <c r="I65" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J65" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K65" s="292"/>
@@ -8904,11 +8917,11 @@
         <v>0</v>
       </c>
       <c r="I66" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J66" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K66" s="292"/>
@@ -8939,11 +8952,11 @@
         <v>0</v>
       </c>
       <c r="I67" s="291">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J67" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K67" s="292"/>
@@ -10734,28 +10747,28 @@
         <v>240</v>
       </c>
       <c r="B1" s="227" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C1" s="227" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D1" s="227" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E1" s="227" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F1" s="227" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="G1" s="227" t="s">
         <v>32</v>
       </c>
       <c r="H1" s="227" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="I1" s="227" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="J1" s="227" t="s">
         <v>386</v>
@@ -10763,10 +10776,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="228" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B2" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C2" s="228" t="s">
         <v>261</v>
@@ -10781,10 +10794,10 @@
         <v>170</v>
       </c>
       <c r="G2" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H2" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I2" s="231">
         <v>0</v>
@@ -10795,13 +10808,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="228" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B3" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C3" s="228" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D3" s="229">
         <v>9345</v>
@@ -10813,24 +10826,24 @@
         <v>285</v>
       </c>
       <c r="G3" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H3" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I3" s="231">
         <v>0</v>
       </c>
       <c r="J3" s="230" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="228" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B4" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C4" s="228" t="s">
         <v>261</v>
@@ -10845,27 +10858,27 @@
         <v>170</v>
       </c>
       <c r="G4" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H4" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I4" s="231">
         <v>0</v>
       </c>
       <c r="J4" s="230" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="228" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B5" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C5" s="228" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D5" s="229">
         <v>23300</v>
@@ -10877,10 +10890,10 @@
         <v>270</v>
       </c>
       <c r="G5" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H5" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I5" s="231">
         <v>0</v>
@@ -10891,10 +10904,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="228" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B6" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C6" s="228" t="s">
         <v>261</v>
@@ -10909,10 +10922,10 @@
         <v>150</v>
       </c>
       <c r="G6" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H6" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I6" s="231">
         <v>0</v>
@@ -10923,13 +10936,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="228" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B7" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C7" s="228" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D7" s="229">
         <v>18505</v>
@@ -10941,10 +10954,10 @@
         <v>375</v>
       </c>
       <c r="G7" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H7" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I7" s="231">
         <v>0</v>
@@ -10955,13 +10968,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="228" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B8" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C8" s="228" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D8" s="229">
         <v>10450</v>
@@ -10973,24 +10986,24 @@
         <v>340</v>
       </c>
       <c r="G8" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H8" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I8" s="231">
         <v>0</v>
       </c>
       <c r="J8" s="230" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="228" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B9" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C9" s="228" t="s">
         <v>261</v>
@@ -11005,10 +11018,10 @@
         <v>355</v>
       </c>
       <c r="G9" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H9" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I9" s="231">
         <v>0</v>
@@ -11019,13 +11032,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="228" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B10" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C10" s="228" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D10" s="229">
         <v>1230</v>
@@ -11037,10 +11050,10 @@
         <v>90</v>
       </c>
       <c r="G10" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H10" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I10" s="231">
         <v>0</v>
@@ -11051,10 +11064,10 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="228" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B11" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C11" s="228" t="s">
         <v>261</v>
@@ -11069,10 +11082,10 @@
         <v>265</v>
       </c>
       <c r="G11" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H11" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I11" s="231">
         <v>0</v>
@@ -11083,13 +11096,13 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="228" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B12" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C12" s="228" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D12" s="229">
         <v>15754</v>
@@ -11101,10 +11114,10 @@
         <v>250</v>
       </c>
       <c r="G12" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H12" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I12" s="231">
         <v>0</v>
@@ -11115,13 +11128,13 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="228" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B13" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C13" s="228" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D13" s="229">
         <v>26407</v>
@@ -11133,10 +11146,10 @@
         <v>355</v>
       </c>
       <c r="G13" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H13" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I13" s="231">
         <v>0</v>
@@ -11147,13 +11160,13 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="228" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B14" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C14" s="228" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D14" s="229">
         <v>3280</v>
@@ -11165,10 +11178,10 @@
         <v>95</v>
       </c>
       <c r="G14" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H14" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I14" s="231">
         <v>0</v>
@@ -11179,10 +11192,10 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="228" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B15" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C15" s="228" t="s">
         <v>261</v>
@@ -11197,10 +11210,10 @@
         <v>565</v>
       </c>
       <c r="G15" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H15" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I15" s="231">
         <v>0</v>
@@ -11211,10 +11224,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="228" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B16" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C16" s="228" t="s">
         <v>261</v>
@@ -11229,10 +11242,10 @@
         <v>750</v>
       </c>
       <c r="G16" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H16" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I16" s="231">
         <v>0</v>
@@ -11243,10 +11256,10 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="228" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B17" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C17" s="228" t="s">
         <v>261</v>
@@ -11261,10 +11274,10 @@
         <v>175</v>
       </c>
       <c r="G17" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H17" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I17" s="231">
         <v>0</v>
@@ -11275,10 +11288,10 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="228" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B18" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C18" s="228" t="s">
         <v>264</v>
@@ -11293,10 +11306,10 @@
         <v>190</v>
       </c>
       <c r="G18" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H18" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I18" s="231">
         <v>0</v>
@@ -11307,10 +11320,10 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="228" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B19" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C19" s="228" t="s">
         <v>261</v>
@@ -11325,10 +11338,10 @@
         <v>150</v>
       </c>
       <c r="G19" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H19" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I19" s="231">
         <v>0</v>
@@ -11339,10 +11352,10 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="228" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B20" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C20" s="228" t="s">
         <v>264</v>
@@ -11357,10 +11370,10 @@
         <v>155</v>
       </c>
       <c r="G20" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H20" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I20" s="231">
         <v>0</v>
@@ -11371,10 +11384,10 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="228" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B21" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C21" s="228" t="s">
         <v>264</v>
@@ -11389,10 +11402,10 @@
         <v>200</v>
       </c>
       <c r="G21" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H21" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I21" s="231">
         <v>0</v>
@@ -11403,10 +11416,10 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="228" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B22" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C22" s="228" t="s">
         <v>261</v>
@@ -11421,10 +11434,10 @@
         <v>290</v>
       </c>
       <c r="G22" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H22" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I22" s="231">
         <v>0</v>
@@ -11435,10 +11448,10 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="228" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B23" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C23" s="228" t="s">
         <v>261</v>
@@ -11453,10 +11466,10 @@
         <v>120</v>
       </c>
       <c r="G23" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H23" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I23" s="231">
         <v>0</v>
@@ -11467,10 +11480,10 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="228" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B24" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C24" s="228" t="s">
         <v>261</v>
@@ -11485,7 +11498,7 @@
         <v>140</v>
       </c>
       <c r="G24" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H24" s="230" t="s">
         <v>165</v>
@@ -11499,10 +11512,10 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="228" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B25" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C25" s="228" t="s">
         <v>264</v>
@@ -11517,7 +11530,7 @@
         <v>45</v>
       </c>
       <c r="G25" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H25" s="230" t="s">
         <v>176</v>
@@ -11531,10 +11544,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="228" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B26" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C26" s="228" t="s">
         <v>261</v>
@@ -11549,10 +11562,10 @@
         <v>255</v>
       </c>
       <c r="G26" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H26" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I26" s="231">
         <v>0</v>
@@ -11563,10 +11576,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="228" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B27" s="228" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C27" s="228" t="s">
         <v>261</v>
@@ -11581,10 +11594,10 @@
         <v>255</v>
       </c>
       <c r="G27" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H27" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I27" s="231">
         <v>0</v>
@@ -11595,10 +11608,10 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="228" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B28" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C28" s="228" t="s">
         <v>264</v>
@@ -11613,7 +11626,7 @@
         <v>635</v>
       </c>
       <c r="G28" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H28" s="230" t="s">
         <v>167</v>
@@ -11627,10 +11640,10 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="228" t="s">
+        <v>676</v>
+      </c>
+      <c r="B29" s="228" t="s">
         <v>675</v>
-      </c>
-      <c r="B29" s="228" t="s">
-        <v>674</v>
       </c>
       <c r="C29" s="228" t="s">
         <v>264</v>
@@ -11645,7 +11658,7 @@
         <v>200</v>
       </c>
       <c r="G29" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H29" s="230" t="s">
         <v>176</v>
@@ -11654,15 +11667,15 @@
         <v>360</v>
       </c>
       <c r="J29" s="230" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="228" t="s">
+        <v>676</v>
+      </c>
+      <c r="B30" s="228" t="s">
         <v>675</v>
-      </c>
-      <c r="B30" s="228" t="s">
-        <v>674</v>
       </c>
       <c r="C30" s="228" t="s">
         <v>261</v>
@@ -11677,7 +11690,7 @@
         <v>525</v>
       </c>
       <c r="G30" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H30" s="230" t="s">
         <v>165</v>
@@ -11691,10 +11704,10 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="228" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B31" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C31" s="228" t="s">
         <v>264</v>
@@ -11709,10 +11722,10 @@
         <v>650</v>
       </c>
       <c r="G31" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H31" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I31" s="231">
         <v>0</v>
@@ -11723,10 +11736,10 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="228" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B32" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C32" s="228" t="s">
         <v>261</v>
@@ -11741,10 +11754,10 @@
         <v>430</v>
       </c>
       <c r="G32" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H32" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I32" s="231">
         <v>0</v>
@@ -11755,10 +11768,10 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="228" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B33" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C33" s="228" t="s">
         <v>264</v>
@@ -11773,10 +11786,10 @@
         <v>760</v>
       </c>
       <c r="G33" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H33" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I33" s="231">
         <v>0</v>
@@ -11787,10 +11800,10 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="228" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B34" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C34" s="228" t="s">
         <v>261</v>
@@ -11805,10 +11818,10 @@
         <v>208</v>
       </c>
       <c r="G34" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H34" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I34" s="231">
         <v>0</v>
@@ -11819,10 +11832,10 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="228" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B35" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C35" s="228" t="s">
         <v>264</v>
@@ -11837,7 +11850,7 @@
         <v>55</v>
       </c>
       <c r="G35" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H35" s="230" t="s">
         <v>183</v>
@@ -11851,10 +11864,10 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="228" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B36" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C36" s="228" t="s">
         <v>264</v>
@@ -11869,10 +11882,10 @@
         <v>325</v>
       </c>
       <c r="G36" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H36" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I36" s="231">
         <v>0</v>
@@ -11883,10 +11896,10 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="228" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B37" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C37" s="228" t="s">
         <v>261</v>
@@ -11901,7 +11914,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="228" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H37" s="230" t="s">
         <v>176</v>
@@ -11910,15 +11923,15 @@
         <v>210</v>
       </c>
       <c r="J37" s="230" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="228" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B38" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C38" s="228" t="s">
         <v>264</v>
@@ -11933,10 +11946,10 @@
         <v>300</v>
       </c>
       <c r="G38" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H38" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I38" s="231">
         <v>0</v>
@@ -11947,10 +11960,10 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="228" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B39" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C39" s="228" t="s">
         <v>261</v>
@@ -11965,7 +11978,7 @@
         <v>900</v>
       </c>
       <c r="G39" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H39" s="230" t="s">
         <v>167</v>
@@ -11979,10 +11992,10 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="228" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B40" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C40" s="228" t="s">
         <v>264</v>
@@ -11997,10 +12010,10 @@
         <v>460</v>
       </c>
       <c r="G40" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H40" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I40" s="231">
         <v>0</v>
@@ -12011,10 +12024,10 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="228" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B41" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C41" s="228" t="s">
         <v>261</v>
@@ -12029,10 +12042,10 @@
         <v>345</v>
       </c>
       <c r="G41" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H41" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I41" s="231">
         <v>0</v>
@@ -12043,10 +12056,10 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="228" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B42" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C42" s="228" t="s">
         <v>264</v>
@@ -12061,7 +12074,7 @@
         <v>305</v>
       </c>
       <c r="G42" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H42" s="230" t="s">
         <v>176</v>
@@ -12075,10 +12088,10 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="228" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B43" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C43" s="228" t="s">
         <v>261</v>
@@ -12093,10 +12106,10 @@
         <v>260</v>
       </c>
       <c r="G43" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H43" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I43" s="231">
         <v>0</v>
@@ -12107,10 +12120,10 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="228" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B44" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C44" s="228" t="s">
         <v>264</v>
@@ -12125,10 +12138,10 @@
         <v>350</v>
       </c>
       <c r="G44" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H44" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I44" s="231">
         <v>0</v>
@@ -12139,10 +12152,10 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="228" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B45" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C45" s="228" t="s">
         <v>261</v>
@@ -12157,10 +12170,10 @@
         <v>290</v>
       </c>
       <c r="G45" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H45" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I45" s="231">
         <v>0</v>
@@ -12171,10 +12184,10 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="228" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B46" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C46" s="228" t="s">
         <v>264</v>
@@ -12189,10 +12202,10 @@
         <v>340</v>
       </c>
       <c r="G46" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H46" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I46" s="231">
         <v>0</v>
@@ -12203,10 +12216,10 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="228" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B47" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C47" s="228" t="s">
         <v>261</v>
@@ -12221,10 +12234,10 @@
         <v>270</v>
       </c>
       <c r="G47" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H47" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I47" s="231">
         <v>0</v>
@@ -12235,10 +12248,10 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="228" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B48" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C48" s="228" t="s">
         <v>264</v>
@@ -12253,10 +12266,10 @@
         <v>380</v>
       </c>
       <c r="G48" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H48" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I48" s="231">
         <v>0</v>
@@ -12267,10 +12280,10 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="228" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B49" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C49" s="228" t="s">
         <v>261</v>
@@ -12285,7 +12298,7 @@
         <v>340</v>
       </c>
       <c r="G49" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H49" s="230" t="s">
         <v>167</v>
@@ -12299,10 +12312,10 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="228" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B50" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C50" s="228" t="s">
         <v>264</v>
@@ -12317,10 +12330,10 @@
         <v>740</v>
       </c>
       <c r="G50" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H50" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I50" s="231">
         <v>0</v>
@@ -12331,10 +12344,10 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="228" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B51" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C51" s="228" t="s">
         <v>261</v>
@@ -12349,10 +12362,10 @@
         <v>810</v>
       </c>
       <c r="G51" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H51" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I51" s="231">
         <v>0</v>
@@ -12363,10 +12376,10 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="228" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B52" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C52" s="228" t="s">
         <v>264</v>
@@ -12381,10 +12394,10 @@
         <v>245</v>
       </c>
       <c r="G52" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H52" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I52" s="231">
         <v>0</v>
@@ -12395,10 +12408,10 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="228" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B53" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C53" s="228" t="s">
         <v>261</v>
@@ -12413,7 +12426,7 @@
         <v>240</v>
       </c>
       <c r="G53" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H53" s="230" t="s">
         <v>165</v>
@@ -12427,13 +12440,13 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="228" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B54" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C54" s="228" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D54" s="229">
         <v>2472</v>
@@ -12445,7 +12458,7 @@
         <v>120</v>
       </c>
       <c r="G54" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H54" s="230" t="s">
         <v>167</v>
@@ -12459,10 +12472,10 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="228" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B55" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C55" s="228" t="s">
         <v>264</v>
@@ -12477,10 +12490,10 @@
         <v>350</v>
       </c>
       <c r="G55" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H55" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I55" s="231">
         <v>0</v>
@@ -12491,10 +12504,10 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="228" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B56" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C56" s="228" t="s">
         <v>264</v>
@@ -12509,10 +12522,10 @@
         <v>380</v>
       </c>
       <c r="G56" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H56" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I56" s="231">
         <v>0</v>
@@ -12523,10 +12536,10 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="228" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B57" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C57" s="228" t="s">
         <v>264</v>
@@ -12541,10 +12554,10 @@
         <v>500</v>
       </c>
       <c r="G57" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H57" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I57" s="231">
         <v>0</v>
@@ -12555,10 +12568,10 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="228" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B58" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C58" s="228" t="s">
         <v>261</v>
@@ -12573,7 +12586,7 @@
         <v>220</v>
       </c>
       <c r="G58" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H58" s="230" t="s">
         <v>176</v>
@@ -12587,10 +12600,10 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="228" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B59" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C59" s="228" t="s">
         <v>264</v>
@@ -12605,10 +12618,10 @@
         <v>280</v>
       </c>
       <c r="G59" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H59" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I59" s="231">
         <v>0</v>
@@ -12619,10 +12632,10 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="228" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B60" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C60" s="228" t="s">
         <v>261</v>
@@ -12637,7 +12650,7 @@
         <v>300</v>
       </c>
       <c r="G60" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H60" s="230" t="s">
         <v>167</v>
@@ -12651,10 +12664,10 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="228" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B61" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C61" s="228" t="s">
         <v>264</v>
@@ -12669,10 +12682,10 @@
         <v>260</v>
       </c>
       <c r="G61" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H61" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I61" s="231">
         <v>0</v>
@@ -12683,10 +12696,10 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="228" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B62" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C62" s="228" t="s">
         <v>261</v>
@@ -12701,7 +12714,7 @@
         <v>270</v>
       </c>
       <c r="G62" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H62" s="230" t="s">
         <v>176</v>
@@ -12715,10 +12728,10 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="228" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B63" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C63" s="228" t="s">
         <v>264</v>
@@ -12733,7 +12746,7 @@
         <v>390</v>
       </c>
       <c r="G63" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H63" s="230" t="s">
         <v>176</v>
@@ -12747,10 +12760,10 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="228" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B64" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C64" s="228" t="s">
         <v>261</v>
@@ -12765,7 +12778,7 @@
         <v>370</v>
       </c>
       <c r="G64" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H64" s="230" t="s">
         <v>180</v>
@@ -12779,10 +12792,10 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="228" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B65" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C65" s="228" t="s">
         <v>264</v>
@@ -12797,7 +12810,7 @@
         <v>200</v>
       </c>
       <c r="G65" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H65" s="230" t="s">
         <v>165</v>
@@ -12811,10 +12824,10 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="228" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B66" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C66" s="228" t="s">
         <v>261</v>
@@ -12829,7 +12842,7 @@
         <v>280</v>
       </c>
       <c r="G66" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H66" s="230" t="s">
         <v>167</v>
@@ -12838,15 +12851,15 @@
         <v>180</v>
       </c>
       <c r="J66" s="230" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="228" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B67" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C67" s="228" t="s">
         <v>264</v>
@@ -12861,7 +12874,7 @@
         <v>290</v>
       </c>
       <c r="G67" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H67" s="230" t="s">
         <v>165</v>
@@ -12875,10 +12888,10 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="228" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B68" s="228" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C68" s="228" t="s">
         <v>261</v>
@@ -12893,10 +12906,10 @@
         <v>260</v>
       </c>
       <c r="G68" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H68" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I68" s="231">
         <v>0</v>
@@ -12907,10 +12920,10 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="228" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B69" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C69" s="228" t="s">
         <v>264</v>
@@ -12925,24 +12938,24 @@
         <v>320</v>
       </c>
       <c r="G69" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H69" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I69" s="231">
         <v>0</v>
       </c>
       <c r="J69" s="230" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="228" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B70" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C70" s="228" t="s">
         <v>261</v>
@@ -12957,7 +12970,7 @@
         <v>240</v>
       </c>
       <c r="G70" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H70" s="230" t="s">
         <v>176</v>
@@ -12971,10 +12984,10 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="228" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B71" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C71" s="228" t="s">
         <v>264</v>
@@ -12989,10 +13002,10 @@
         <v>260</v>
       </c>
       <c r="G71" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H71" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I71" s="231">
         <v>0</v>
@@ -13003,10 +13016,10 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="228" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B72" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C72" s="228" t="s">
         <v>261</v>
@@ -13021,10 +13034,10 @@
         <v>360</v>
       </c>
       <c r="G72" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H72" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I72" s="231">
         <v>0</v>
@@ -13035,13 +13048,13 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="228" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B73" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C73" s="228" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D73" s="229">
         <v>7838</v>
@@ -13053,7 +13066,7 @@
         <v>350</v>
       </c>
       <c r="G73" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H73" s="230" t="s">
         <v>167</v>
@@ -13067,10 +13080,10 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="228" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B74" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C74" s="228" t="s">
         <v>261</v>
@@ -13085,7 +13098,7 @@
         <v>240</v>
       </c>
       <c r="G74" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H74" s="230" t="s">
         <v>180</v>
@@ -13099,13 +13112,13 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="228" t="s">
+        <v>708</v>
+      </c>
+      <c r="B75" s="228" t="s">
+        <v>703</v>
+      </c>
+      <c r="C75" s="228" t="s">
         <v>707</v>
-      </c>
-      <c r="B75" s="228" t="s">
-        <v>702</v>
-      </c>
-      <c r="C75" s="228" t="s">
-        <v>706</v>
       </c>
       <c r="D75" s="229">
         <v>10858</v>
@@ -13117,7 +13130,7 @@
         <v>250</v>
       </c>
       <c r="G75" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H75" s="230" t="s">
         <v>167</v>
@@ -13131,10 +13144,10 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="228" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B76" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C76" s="228" t="s">
         <v>261</v>
@@ -13149,10 +13162,10 @@
         <v>330</v>
       </c>
       <c r="G76" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H76" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I76" s="231">
         <v>0</v>
@@ -13163,13 +13176,13 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="228" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B77" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C77" s="228" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D77" s="229">
         <v>4410</v>
@@ -13181,7 +13194,7 @@
         <v>250</v>
       </c>
       <c r="G77" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H77" s="230" t="s">
         <v>165</v>
@@ -13195,10 +13208,10 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="228" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B78" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C78" s="228" t="s">
         <v>261</v>
@@ -13213,7 +13226,7 @@
         <v>260</v>
       </c>
       <c r="G78" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H78" s="230" t="s">
         <v>165</v>
@@ -13227,10 +13240,10 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="228" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B79" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C79" s="228" t="s">
         <v>261</v>
@@ -13245,7 +13258,7 @@
         <v>270</v>
       </c>
       <c r="G79" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H79" s="230" t="s">
         <v>165</v>
@@ -13259,13 +13272,13 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="228" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B80" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C80" s="228" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D80" s="229">
         <v>18156</v>
@@ -13277,7 +13290,7 @@
         <v>600</v>
       </c>
       <c r="G80" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H80" s="230" t="s">
         <v>167</v>
@@ -13291,10 +13304,10 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="228" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B81" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C81" s="228" t="s">
         <v>261</v>
@@ -13309,10 +13322,10 @@
         <v>250</v>
       </c>
       <c r="G81" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H81" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I81" s="231">
         <v>0</v>
@@ -13323,13 +13336,13 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="228" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B82" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C82" s="228" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D82" s="229">
         <v>6311</v>
@@ -13341,7 +13354,7 @@
         <v>155</v>
       </c>
       <c r="G82" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H82" s="230" t="s">
         <v>176</v>
@@ -13355,10 +13368,10 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="228" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B83" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C83" s="228" t="s">
         <v>261</v>
@@ -13373,10 +13386,10 @@
         <v>260</v>
       </c>
       <c r="G83" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H83" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I83" s="231">
         <v>0</v>
@@ -13387,10 +13400,10 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="228" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B84" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C84" s="228" t="s">
         <v>264</v>
@@ -13405,7 +13418,7 @@
         <v>250</v>
       </c>
       <c r="G84" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H84" s="230" t="s">
         <v>167</v>
@@ -13419,10 +13432,10 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="228" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B85" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C85" s="228" t="s">
         <v>261</v>
@@ -13437,7 +13450,7 @@
         <v>140</v>
       </c>
       <c r="G85" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H85" s="230" t="s">
         <v>165</v>
@@ -13451,10 +13464,10 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="228" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B86" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C86" s="228" t="s">
         <v>264</v>
@@ -13469,7 +13482,7 @@
         <v>305</v>
       </c>
       <c r="G86" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H86" s="230" t="s">
         <v>165</v>
@@ -13483,10 +13496,10 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="228" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B87" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C87" s="228" t="s">
         <v>261</v>
@@ -13501,10 +13514,10 @@
         <v>300</v>
       </c>
       <c r="G87" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H87" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I87" s="231">
         <v>0</v>
@@ -13515,10 +13528,10 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="228" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B88" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C88" s="228" t="s">
         <v>261</v>
@@ -13533,24 +13546,24 @@
         <v>660</v>
       </c>
       <c r="G88" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H88" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I88" s="231">
         <v>0</v>
       </c>
       <c r="J88" s="230" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="228" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B89" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C89" s="228" t="s">
         <v>264</v>
@@ -13565,24 +13578,24 @@
         <v>270</v>
       </c>
       <c r="G89" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H89" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I89" s="231">
         <v>0</v>
       </c>
       <c r="J89" s="230" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="228" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B90" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C90" s="228" t="s">
         <v>261</v>
@@ -13597,7 +13610,7 @@
         <v>200</v>
       </c>
       <c r="G90" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H90" s="230" t="s">
         <v>165</v>
@@ -13611,10 +13624,10 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="228" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B91" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C91" s="228" t="s">
         <v>264</v>
@@ -13629,7 +13642,7 @@
         <v>230</v>
       </c>
       <c r="G91" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H91" s="230" t="s">
         <v>165</v>
@@ -13643,10 +13656,10 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="228" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B92" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C92" s="228" t="s">
         <v>264</v>
@@ -13661,10 +13674,10 @@
         <v>280</v>
       </c>
       <c r="G92" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H92" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I92" s="231">
         <v>0</v>
@@ -13675,10 +13688,10 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="228" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B93" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C93" s="228" t="s">
         <v>261</v>
@@ -13693,7 +13706,7 @@
         <v>160</v>
       </c>
       <c r="G93" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H93" s="230" t="s">
         <v>176</v>
@@ -13707,10 +13720,10 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="228" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B94" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C94" s="228" t="s">
         <v>264</v>
@@ -13725,7 +13738,7 @@
         <v>310</v>
       </c>
       <c r="G94" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H94" s="230" t="s">
         <v>176</v>
@@ -13734,15 +13747,15 @@
         <v>300</v>
       </c>
       <c r="J94" s="230" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="228" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B95" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C95" s="228" t="s">
         <v>261</v>
@@ -13757,7 +13770,7 @@
         <v>210</v>
       </c>
       <c r="G95" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H95" s="230" t="s">
         <v>176</v>
@@ -13771,10 +13784,10 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="228" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B96" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C96" s="228" t="s">
         <v>264</v>
@@ -13789,10 +13802,10 @@
         <v>380</v>
       </c>
       <c r="G96" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H96" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I96" s="231">
         <v>0</v>
@@ -13803,10 +13816,10 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="228" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B97" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C97" s="228" t="s">
         <v>261</v>
@@ -13821,7 +13834,7 @@
         <v>210</v>
       </c>
       <c r="G97" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H97" s="230" t="s">
         <v>176</v>
@@ -13835,10 +13848,10 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="228" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B98" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C98" s="228" t="s">
         <v>264</v>
@@ -13853,10 +13866,10 @@
         <v>210</v>
       </c>
       <c r="G98" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H98" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I98" s="231">
         <v>0</v>
@@ -13867,10 +13880,10 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="228" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B99" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C99" s="228" t="s">
         <v>264</v>
@@ -13885,7 +13898,7 @@
         <v>380</v>
       </c>
       <c r="G99" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H99" s="230" t="s">
         <v>165</v>
@@ -13899,10 +13912,10 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="228" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B100" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C100" s="228" t="s">
         <v>261</v>
@@ -13917,7 +13930,7 @@
         <v>450</v>
       </c>
       <c r="G100" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H100" s="230" t="s">
         <v>165</v>
@@ -13931,10 +13944,10 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="228" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B101" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C101" s="228" t="s">
         <v>261</v>
@@ -13949,10 +13962,10 @@
         <v>250</v>
       </c>
       <c r="G101" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H101" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I101" s="231">
         <v>0</v>
@@ -13963,10 +13976,10 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="228" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B102" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C102" s="228" t="s">
         <v>261</v>
@@ -13981,7 +13994,7 @@
         <v>230</v>
       </c>
       <c r="G102" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H102" s="230" t="s">
         <v>165</v>
@@ -13995,10 +14008,10 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="228" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B103" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C103" s="228" t="s">
         <v>264</v>
@@ -14013,10 +14026,10 @@
         <v>190</v>
       </c>
       <c r="G103" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H103" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I103" s="231">
         <v>0</v>
@@ -14027,10 +14040,10 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="228" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B104" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C104" s="228" t="s">
         <v>264</v>
@@ -14045,7 +14058,7 @@
         <v>475</v>
       </c>
       <c r="G104" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H104" s="230" t="s">
         <v>167</v>
@@ -14059,10 +14072,10 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="228" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B105" s="228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C105" s="228" t="s">
         <v>264</v>
@@ -14077,10 +14090,10 @@
         <v>250</v>
       </c>
       <c r="G105" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H105" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I105" s="231">
         <v>0</v>
@@ -14091,10 +14104,10 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="228" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B106" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C106" s="228" t="s">
         <v>264</v>
@@ -14109,10 +14122,10 @@
         <v>280</v>
       </c>
       <c r="G106" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H106" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I106" s="231">
         <v>0</v>
@@ -14123,10 +14136,10 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="228" t="s">
+        <v>731</v>
+      </c>
+      <c r="B107" s="228" t="s">
         <v>730</v>
-      </c>
-      <c r="B107" s="228" t="s">
-        <v>729</v>
       </c>
       <c r="C107" s="228" t="s">
         <v>264</v>
@@ -14150,15 +14163,15 @@
         <v>120</v>
       </c>
       <c r="J107" s="230" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="228" t="s">
+        <v>731</v>
+      </c>
+      <c r="B108" s="228" t="s">
         <v>730</v>
-      </c>
-      <c r="B108" s="228" t="s">
-        <v>729</v>
       </c>
       <c r="C108" s="228" t="s">
         <v>261</v>
@@ -14187,10 +14200,10 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="228" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B109" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C109" s="228" t="s">
         <v>264</v>
@@ -14214,15 +14227,15 @@
         <v>60</v>
       </c>
       <c r="J109" s="230" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="228" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B110" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C110" s="228" t="s">
         <v>261</v>
@@ -14246,15 +14259,15 @@
         <v>60</v>
       </c>
       <c r="J110" s="230" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="228" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B111" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C111" s="228" t="s">
         <v>264</v>
@@ -14283,10 +14296,10 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="228" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B112" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C112" s="228" t="s">
         <v>261</v>
@@ -14315,10 +14328,10 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="228" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B113" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C113" s="228" t="s">
         <v>264</v>
@@ -14333,10 +14346,10 @@
         <v>445</v>
       </c>
       <c r="G113" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H113" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I113" s="231">
         <v>0</v>
@@ -14347,10 +14360,10 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="228" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B114" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C114" s="228" t="s">
         <v>261</v>
@@ -14365,10 +14378,10 @@
         <v>650</v>
       </c>
       <c r="G114" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H114" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I114" s="231">
         <v>0</v>
@@ -14379,10 +14392,10 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="228" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B115" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C115" s="228" t="s">
         <v>264</v>
@@ -14411,10 +14424,10 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="228" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B116" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C116" s="228" t="s">
         <v>261</v>
@@ -14443,10 +14456,10 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="228" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B117" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C117" s="228" t="s">
         <v>264</v>
@@ -14461,10 +14474,10 @@
         <v>440</v>
       </c>
       <c r="G117" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H117" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I117" s="231">
         <v>0</v>
@@ -14475,10 +14488,10 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="228" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B118" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C118" s="228" t="s">
         <v>261</v>
@@ -14493,10 +14506,10 @@
         <v>445</v>
       </c>
       <c r="G118" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H118" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I118" s="231">
         <v>0</v>
@@ -14507,10 +14520,10 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="228" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B119" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C119" s="228" t="s">
         <v>264</v>
@@ -14525,7 +14538,7 @@
         <v>665</v>
       </c>
       <c r="G119" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H119" s="230" t="s">
         <v>167</v>
@@ -14534,15 +14547,15 @@
         <v>200</v>
       </c>
       <c r="J119" s="230" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="228" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B120" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C120" s="228" t="s">
         <v>261</v>
@@ -14557,10 +14570,10 @@
         <v>340</v>
       </c>
       <c r="G120" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H120" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I120" s="231">
         <v>0</v>
@@ -14571,10 +14584,10 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="228" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B121" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C121" s="228" t="s">
         <v>264</v>
@@ -14589,10 +14602,10 @@
         <v>350</v>
       </c>
       <c r="G121" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H121" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I121" s="231">
         <v>0</v>
@@ -14603,10 +14616,10 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="228" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B122" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C122" s="228" t="s">
         <v>261</v>
@@ -14621,10 +14634,10 @@
         <v>365</v>
       </c>
       <c r="G122" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H122" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I122" s="231">
         <v>0</v>
@@ -14635,10 +14648,10 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="228" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B123" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C123" s="228" t="s">
         <v>264</v>
@@ -14653,10 +14666,10 @@
         <v>455</v>
       </c>
       <c r="G123" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H123" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I123" s="231">
         <v>0</v>
@@ -14667,10 +14680,10 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="228" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B124" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C124" s="228" t="s">
         <v>261</v>
@@ -14685,10 +14698,10 @@
         <v>485</v>
       </c>
       <c r="G124" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H124" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I124" s="231">
         <v>0</v>
@@ -14699,10 +14712,10 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="228" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B125" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C125" s="228" t="s">
         <v>264</v>
@@ -14717,10 +14730,10 @@
         <v>630</v>
       </c>
       <c r="G125" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H125" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I125" s="231">
         <v>0</v>
@@ -14731,10 +14744,10 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="228" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B126" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C126" s="228" t="s">
         <v>261</v>
@@ -14749,10 +14762,10 @@
         <v>430</v>
       </c>
       <c r="G126" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H126" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I126" s="231">
         <v>0</v>
@@ -14763,10 +14776,10 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="228" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B127" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C127" s="228" t="s">
         <v>264</v>
@@ -14781,7 +14794,7 @@
         <v>550</v>
       </c>
       <c r="G127" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H127" s="230" t="s">
         <v>167</v>
@@ -14795,10 +14808,10 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="228" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B128" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C128" s="228" t="s">
         <v>261</v>
@@ -14813,7 +14826,7 @@
         <v>335</v>
       </c>
       <c r="G128" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H128" s="230" t="s">
         <v>167</v>
@@ -14827,10 +14840,10 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="228" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B129" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C129" s="228" t="s">
         <v>264</v>
@@ -14859,10 +14872,10 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="228" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B130" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C130" s="228" t="s">
         <v>261</v>
@@ -14891,10 +14904,10 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="228" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B131" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C131" s="228" t="s">
         <v>264</v>
@@ -14909,10 +14922,10 @@
         <v>400</v>
       </c>
       <c r="G131" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H131" s="230" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I131" s="231">
         <v>180</v>
@@ -14923,10 +14936,10 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="228" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B132" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C132" s="228" t="s">
         <v>261</v>
@@ -14941,10 +14954,10 @@
         <v>285</v>
       </c>
       <c r="G132" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H132" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I132" s="231">
         <v>0</v>
@@ -14955,10 +14968,10 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="228" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B133" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C133" s="228" t="s">
         <v>264</v>
@@ -14982,15 +14995,15 @@
         <v>360</v>
       </c>
       <c r="J133" s="230" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="228" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B134" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C134" s="228" t="s">
         <v>261</v>
@@ -15019,10 +15032,10 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="228" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B135" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C135" s="228" t="s">
         <v>264</v>
@@ -15037,10 +15050,10 @@
         <v>230</v>
       </c>
       <c r="G135" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H135" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I135" s="231">
         <v>0</v>
@@ -15051,10 +15064,10 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="228" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B136" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C136" s="228" t="s">
         <v>261</v>
@@ -15069,10 +15082,10 @@
         <v>530</v>
       </c>
       <c r="G136" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H136" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I136" s="231">
         <v>0</v>
@@ -15083,10 +15096,10 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="228" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B137" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C137" s="228" t="s">
         <v>264</v>
@@ -15101,10 +15114,10 @@
         <v>595</v>
       </c>
       <c r="G137" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H137" s="230" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I137" s="231">
         <v>90</v>
@@ -15115,10 +15128,10 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="228" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B138" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C138" s="228" t="s">
         <v>261</v>
@@ -15133,10 +15146,10 @@
         <v>455</v>
       </c>
       <c r="G138" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H138" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I138" s="231">
         <v>0</v>
@@ -15147,10 +15160,10 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="228" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B139" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C139" s="228" t="s">
         <v>264</v>
@@ -15165,10 +15178,10 @@
         <v>400</v>
       </c>
       <c r="G139" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H139" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I139" s="231">
         <v>0</v>
@@ -15179,10 +15192,10 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="228" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B140" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C140" s="228" t="s">
         <v>261</v>
@@ -15197,10 +15210,10 @@
         <v>375</v>
       </c>
       <c r="G140" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H140" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I140" s="231">
         <v>0</v>
@@ -15211,10 +15224,10 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="228" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B141" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C141" s="228" t="s">
         <v>264</v>
@@ -15229,10 +15242,10 @@
         <v>400</v>
       </c>
       <c r="G141" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H141" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I141" s="231">
         <v>0</v>
@@ -15243,10 +15256,10 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="228" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B142" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C142" s="228" t="s">
         <v>261</v>
@@ -15261,10 +15274,10 @@
         <v>420</v>
       </c>
       <c r="G142" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H142" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I142" s="231">
         <v>0</v>
@@ -15275,10 +15288,10 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="228" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B143" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C143" s="228" t="s">
         <v>264</v>
@@ -15293,7 +15306,7 @@
         <v>295</v>
       </c>
       <c r="G143" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H143" s="230" t="s">
         <v>167</v>
@@ -15307,10 +15320,10 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="228" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B144" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C144" s="228" t="s">
         <v>261</v>
@@ -15325,7 +15338,7 @@
         <v>375</v>
       </c>
       <c r="G144" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H144" s="230" t="s">
         <v>180</v>
@@ -15339,10 +15352,10 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="228" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B145" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C145" s="228" t="s">
         <v>264</v>
@@ -15357,10 +15370,10 @@
         <v>280</v>
       </c>
       <c r="G145" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H145" s="230" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I145" s="231">
         <v>180</v>
@@ -15371,10 +15384,10 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="228" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B146" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C146" s="228" t="s">
         <v>261</v>
@@ -15389,7 +15402,7 @@
         <v>395</v>
       </c>
       <c r="G146" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H146" s="230" t="s">
         <v>167</v>
@@ -15403,10 +15416,10 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="228" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B147" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C147" s="228" t="s">
         <v>261</v>
@@ -15421,10 +15434,10 @@
         <v>280</v>
       </c>
       <c r="G147" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H147" s="230" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I147" s="231">
         <v>300</v>
@@ -15435,10 +15448,10 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="228" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B148" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C148" s="228" t="s">
         <v>264</v>
@@ -15453,10 +15466,10 @@
         <v>230</v>
       </c>
       <c r="G148" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H148" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I148" s="231">
         <v>0</v>
@@ -15467,10 +15480,10 @@
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="228" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B149" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C149" s="228" t="s">
         <v>261</v>
@@ -15485,7 +15498,7 @@
         <v>300</v>
       </c>
       <c r="G149" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H149" s="230" t="s">
         <v>167</v>
@@ -15494,15 +15507,15 @@
         <v>120</v>
       </c>
       <c r="J149" s="230" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="228" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B150" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C150" s="228" t="s">
         <v>264</v>
@@ -15517,24 +15530,24 @@
         <v>400</v>
       </c>
       <c r="G150" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H150" s="230" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I150" s="231">
         <v>120</v>
       </c>
       <c r="J150" s="230" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="228" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B151" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C151" s="228" t="s">
         <v>261</v>
@@ -15549,10 +15562,10 @@
         <v>350</v>
       </c>
       <c r="G151" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H151" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I151" s="231">
         <v>0</v>
@@ -15563,10 +15576,10 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="228" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B152" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C152" s="228" t="s">
         <v>264</v>
@@ -15581,7 +15594,7 @@
         <v>800</v>
       </c>
       <c r="G152" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H152" s="230" t="s">
         <v>180</v>
@@ -15595,10 +15608,10 @@
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="228" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B153" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C153" s="228" t="s">
         <v>261</v>
@@ -15613,10 +15626,10 @@
         <v>495</v>
       </c>
       <c r="G153" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H153" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I153" s="231">
         <v>0</v>
@@ -15627,10 +15640,10 @@
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="228" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B154" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C154" s="228" t="s">
         <v>264</v>
@@ -15645,10 +15658,10 @@
         <v>410</v>
       </c>
       <c r="G154" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H154" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I154" s="231">
         <v>0</v>
@@ -15659,10 +15672,10 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="228" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B155" s="228" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C155" s="228" t="s">
         <v>261</v>
@@ -15677,10 +15690,10 @@
         <v>385</v>
       </c>
       <c r="G155" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H155" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I155" s="231">
         <v>0</v>
@@ -15691,10 +15704,10 @@
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="228" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B156" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C156" s="228" t="s">
         <v>264</v>
@@ -15723,10 +15736,10 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="228" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B157" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C157" s="228" t="s">
         <v>261</v>
@@ -15755,10 +15768,10 @@
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="228" t="s">
+        <v>763</v>
+      </c>
+      <c r="B158" s="228" t="s">
         <v>762</v>
-      </c>
-      <c r="B158" s="228" t="s">
-        <v>761</v>
       </c>
       <c r="C158" s="228" t="s">
         <v>264</v>
@@ -15773,10 +15786,10 @@
         <v>185</v>
       </c>
       <c r="G158" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H158" s="230" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I158" s="231">
         <v>300</v>
@@ -15787,10 +15800,10 @@
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="228" t="s">
+        <v>763</v>
+      </c>
+      <c r="B159" s="228" t="s">
         <v>762</v>
-      </c>
-      <c r="B159" s="228" t="s">
-        <v>761</v>
       </c>
       <c r="C159" s="228" t="s">
         <v>261</v>
@@ -15805,10 +15818,10 @@
         <v>400</v>
       </c>
       <c r="G159" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H159" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I159" s="231">
         <v>0</v>
@@ -15819,10 +15832,10 @@
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" s="228" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B160" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C160" s="228" t="s">
         <v>261</v>
@@ -15837,10 +15850,10 @@
         <v>360</v>
       </c>
       <c r="G160" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H160" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I160" s="231">
         <v>0</v>
@@ -15851,10 +15864,10 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="228" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B161" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C161" s="228" t="s">
         <v>261</v>
@@ -15869,7 +15882,7 @@
         <v>340</v>
       </c>
       <c r="G161" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H161" s="230" t="s">
         <v>180</v>
@@ -15883,10 +15896,10 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="228" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B162" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C162" s="228" t="s">
         <v>264</v>
@@ -15915,10 +15928,10 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" s="228" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B163" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C163" s="228" t="s">
         <v>261</v>
@@ -15947,10 +15960,10 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="228" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B164" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C164" s="228" t="s">
         <v>264</v>
@@ -15965,24 +15978,24 @@
         <v>270</v>
       </c>
       <c r="G164" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H164" s="230" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I164" s="231">
         <v>240</v>
       </c>
       <c r="J164" s="230" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="228" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B165" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C165" s="228" t="s">
         <v>261</v>
@@ -15997,10 +16010,10 @@
         <v>125</v>
       </c>
       <c r="G165" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H165" s="230" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I165" s="231">
         <v>420</v>
@@ -16011,10 +16024,10 @@
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="228" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B166" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C166" s="228" t="s">
         <v>264</v>
@@ -16029,7 +16042,7 @@
         <v>375</v>
       </c>
       <c r="G166" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H166" s="230" t="s">
         <v>167</v>
@@ -16038,15 +16051,15 @@
         <v>150</v>
       </c>
       <c r="J166" s="230" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="228" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B167" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C167" s="228" t="s">
         <v>261</v>
@@ -16061,10 +16074,10 @@
         <v>490</v>
       </c>
       <c r="G167" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H167" s="230" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I167" s="231">
         <v>120</v>
@@ -16075,10 +16088,10 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="228" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B168" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C168" s="228" t="s">
         <v>261</v>
@@ -16093,7 +16106,7 @@
         <v>340</v>
       </c>
       <c r="G168" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H168" s="230" t="s">
         <v>167</v>
@@ -16102,15 +16115,15 @@
         <v>320</v>
       </c>
       <c r="J168" s="230" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="228" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B169" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C169" s="228" t="s">
         <v>264</v>
@@ -16125,7 +16138,7 @@
         <v>200</v>
       </c>
       <c r="G169" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H169" s="230" t="s">
         <v>180</v>
@@ -16139,10 +16152,10 @@
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" s="228" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B170" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C170" s="228" t="s">
         <v>261</v>
@@ -16157,7 +16170,7 @@
         <v>100</v>
       </c>
       <c r="G170" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H170" s="230" t="s">
         <v>167</v>
@@ -16171,10 +16184,10 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="228" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B171" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C171" s="228" t="s">
         <v>264</v>
@@ -16189,7 +16202,7 @@
         <v>260</v>
       </c>
       <c r="G171" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H171" s="230" t="s">
         <v>167</v>
@@ -16203,10 +16216,10 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" s="228" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B172" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C172" s="228" t="s">
         <v>261</v>
@@ -16221,7 +16234,7 @@
         <v>380</v>
       </c>
       <c r="G172" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H172" s="230" t="s">
         <v>167</v>
@@ -16230,15 +16243,15 @@
         <v>360</v>
       </c>
       <c r="J172" s="230" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="228" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B173" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C173" s="228" t="s">
         <v>261</v>
@@ -16253,7 +16266,7 @@
         <v>260</v>
       </c>
       <c r="G173" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H173" s="230" t="s">
         <v>165</v>
@@ -16267,10 +16280,10 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" s="228" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B174" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C174" s="228" t="s">
         <v>261</v>
@@ -16285,10 +16298,10 @@
         <v>160</v>
       </c>
       <c r="G174" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H174" s="230" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="I174" s="231">
         <v>300</v>
@@ -16299,10 +16312,10 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="228" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B175" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C175" s="228" t="s">
         <v>264</v>
@@ -16317,10 +16330,10 @@
         <v>235</v>
       </c>
       <c r="G175" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H175" s="230" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I175" s="231">
         <v>240</v>
@@ -16331,10 +16344,10 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" s="228" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B176" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C176" s="228" t="s">
         <v>261</v>
@@ -16349,10 +16362,10 @@
         <v>275</v>
       </c>
       <c r="G176" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H176" s="230" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I176" s="231">
         <v>360</v>
@@ -16363,10 +16376,10 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" s="228" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B177" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C177" s="228" t="s">
         <v>264</v>
@@ -16381,7 +16394,7 @@
         <v>180</v>
       </c>
       <c r="G177" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H177" s="230" t="s">
         <v>167</v>
@@ -16395,10 +16408,10 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" s="228" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B178" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C178" s="228" t="s">
         <v>261</v>
@@ -16413,10 +16426,10 @@
         <v>260</v>
       </c>
       <c r="G178" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H178" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I178" s="231">
         <v>0</v>
@@ -16427,10 +16440,10 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" s="228" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B179" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C179" s="228" t="s">
         <v>264</v>
@@ -16445,10 +16458,10 @@
         <v>260</v>
       </c>
       <c r="G179" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H179" s="230" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I179" s="231">
         <v>240</v>
@@ -16459,10 +16472,10 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" s="228" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B180" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C180" s="228" t="s">
         <v>261</v>
@@ -16477,10 +16490,10 @@
         <v>340</v>
       </c>
       <c r="G180" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H180" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I180" s="231">
         <v>0</v>
@@ -16491,10 +16504,10 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" s="228" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B181" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C181" s="228" t="s">
         <v>264</v>
@@ -16509,7 +16522,7 @@
         <v>240</v>
       </c>
       <c r="G181" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H181" s="230" t="s">
         <v>167</v>
@@ -16518,15 +16531,15 @@
         <v>560</v>
       </c>
       <c r="J181" s="230" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" s="228" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B182" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C182" s="228" t="s">
         <v>261</v>
@@ -16541,10 +16554,10 @@
         <v>220</v>
       </c>
       <c r="G182" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H182" s="230" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I182" s="231">
         <v>300</v>
@@ -16555,10 +16568,10 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" s="228" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B183" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C183" s="228" t="s">
         <v>264</v>
@@ -16573,10 +16586,10 @@
         <v>285</v>
       </c>
       <c r="G183" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H183" s="230" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I183" s="231">
         <v>150</v>
@@ -16587,10 +16600,10 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" s="228" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B184" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C184" s="228" t="s">
         <v>261</v>
@@ -16605,10 +16618,10 @@
         <v>300</v>
       </c>
       <c r="G184" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H184" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I184" s="231">
         <v>0</v>
@@ -16619,10 +16632,10 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" s="228" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B185" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C185" s="228" t="s">
         <v>264</v>
@@ -16646,15 +16659,15 @@
         <v>240</v>
       </c>
       <c r="J185" s="230" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" s="228" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B186" s="228" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C186" s="228" t="s">
         <v>261</v>
@@ -16683,10 +16696,10 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" s="228" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B187" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C187" s="228" t="s">
         <v>264</v>
@@ -16701,10 +16714,10 @@
         <v>155</v>
       </c>
       <c r="G187" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H187" s="230" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I187" s="231">
         <v>180</v>
@@ -16715,10 +16728,10 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" s="228" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B188" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C188" s="228" t="s">
         <v>261</v>
@@ -16733,7 +16746,7 @@
         <v>60</v>
       </c>
       <c r="G188" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H188" s="230" t="s">
         <v>165</v>
@@ -16747,10 +16760,10 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" s="228" t="s">
+        <v>787</v>
+      </c>
+      <c r="B189" s="228" t="s">
         <v>786</v>
-      </c>
-      <c r="B189" s="228" t="s">
-        <v>785</v>
       </c>
       <c r="C189" s="228" t="s">
         <v>264</v>
@@ -16779,10 +16792,10 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" s="228" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B190" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C190" s="228" t="s">
         <v>264</v>
@@ -16797,10 +16810,10 @@
         <v>360</v>
       </c>
       <c r="G190" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H190" s="230" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I190" s="231">
         <v>120</v>
@@ -16811,10 +16824,10 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" s="228" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B191" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C191" s="228" t="s">
         <v>264</v>
@@ -16829,10 +16842,10 @@
         <v>380</v>
       </c>
       <c r="G191" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H191" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I191" s="231">
         <v>0</v>
@@ -16843,10 +16856,10 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" s="228" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B192" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C192" s="228" t="s">
         <v>264</v>
@@ -16861,10 +16874,10 @@
         <v>395</v>
       </c>
       <c r="G192" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H192" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I192" s="231">
         <v>0</v>
@@ -16875,10 +16888,10 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" s="228" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B193" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C193" s="228" t="s">
         <v>264</v>
@@ -16902,15 +16915,15 @@
         <v>160</v>
       </c>
       <c r="J193" s="230" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" s="228" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B194" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C194" s="228" t="s">
         <v>264</v>
@@ -16939,10 +16952,10 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" s="228" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B195" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C195" s="228" t="s">
         <v>264</v>
@@ -16957,24 +16970,24 @@
         <v>440</v>
       </c>
       <c r="G195" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H195" s="230" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="I195" s="231">
         <v>360</v>
       </c>
       <c r="J195" s="230" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" s="228" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B196" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C196" s="228" t="s">
         <v>264</v>
@@ -17003,10 +17016,10 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" s="228" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B197" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C197" s="228" t="s">
         <v>264</v>
@@ -17035,10 +17048,10 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="228" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B198" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C198" s="228" t="s">
         <v>261</v>
@@ -17053,10 +17066,10 @@
         <v>450</v>
       </c>
       <c r="G198" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H198" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I198" s="231">
         <v>0</v>
@@ -17067,10 +17080,10 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" s="228" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B199" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C199" s="228" t="s">
         <v>261</v>
@@ -17085,10 +17098,10 @@
         <v>480</v>
       </c>
       <c r="G199" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H199" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I199" s="231">
         <v>0</v>
@@ -17099,10 +17112,10 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" s="228" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B200" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C200" s="228" t="s">
         <v>261</v>
@@ -17117,10 +17130,10 @@
         <v>450</v>
       </c>
       <c r="G200" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H200" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I200" s="231">
         <v>0</v>
@@ -17131,10 +17144,10 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="228" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B201" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C201" s="228" t="s">
         <v>264</v>
@@ -17149,7 +17162,7 @@
         <v>450</v>
       </c>
       <c r="G201" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H201" s="230" t="s">
         <v>167</v>
@@ -17163,10 +17176,10 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="228" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B202" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C202" s="228" t="s">
         <v>261</v>
@@ -17181,10 +17194,10 @@
         <v>220</v>
       </c>
       <c r="G202" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H202" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I202" s="231">
         <v>0</v>
@@ -17195,10 +17208,10 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="228" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B203" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C203" s="228" t="s">
         <v>264</v>
@@ -17213,10 +17226,10 @@
         <v>450</v>
       </c>
       <c r="G203" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H203" s="230" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I203" s="231">
         <v>60</v>
@@ -17227,10 +17240,10 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="228" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B204" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C204" s="228" t="s">
         <v>264</v>
@@ -17245,10 +17258,10 @@
         <v>150</v>
       </c>
       <c r="G204" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H204" s="230" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="I204" s="231">
         <v>360</v>
@@ -17259,10 +17272,10 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" s="228" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B205" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C205" s="228" t="s">
         <v>264</v>
@@ -17277,10 +17290,10 @@
         <v>110</v>
       </c>
       <c r="G205" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H205" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I205" s="231">
         <v>0</v>
@@ -17291,10 +17304,10 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="228" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B206" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C206" s="228" t="s">
         <v>261</v>
@@ -17309,10 +17322,10 @@
         <v>450</v>
       </c>
       <c r="G206" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H206" s="230" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="I206" s="231">
         <v>120</v>
@@ -17323,10 +17336,10 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="228" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B207" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C207" s="228" t="s">
         <v>261</v>
@@ -17355,10 +17368,10 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="228" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B208" s="228" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C208" s="228" t="s">
         <v>261</v>
@@ -17373,10 +17386,10 @@
         <v>395</v>
       </c>
       <c r="G208" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H208" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I208" s="231">
         <v>0</v>
@@ -17387,10 +17400,10 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="228" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B209" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C209" s="228" t="s">
         <v>264</v>
@@ -17405,7 +17418,7 @@
         <v>250</v>
       </c>
       <c r="G209" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H209" s="230" t="s">
         <v>183</v>
@@ -17419,10 +17432,10 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="228" t="s">
+        <v>808</v>
+      </c>
+      <c r="B210" s="228" t="s">
         <v>807</v>
-      </c>
-      <c r="B210" s="228" t="s">
-        <v>806</v>
       </c>
       <c r="C210" s="228" t="s">
         <v>264</v>
@@ -17437,7 +17450,7 @@
         <v>450</v>
       </c>
       <c r="G210" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H210" s="230" t="s">
         <v>183</v>
@@ -17451,10 +17464,10 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="228" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B211" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C211" s="228" t="s">
         <v>264</v>
@@ -17469,10 +17482,10 @@
         <v>450</v>
       </c>
       <c r="G211" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H211" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I211" s="231">
         <v>0</v>
@@ -17483,10 +17496,10 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="228" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B212" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C212" s="228" t="s">
         <v>264</v>
@@ -17501,7 +17514,7 @@
         <v>380</v>
       </c>
       <c r="G212" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H212" s="230" t="s">
         <v>176</v>
@@ -17515,10 +17528,10 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="228" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B213" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C213" s="228" t="s">
         <v>264</v>
@@ -17533,10 +17546,10 @@
         <v>410</v>
       </c>
       <c r="G213" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H213" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I213" s="231">
         <v>0</v>
@@ -17547,10 +17560,10 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="228" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B214" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C214" s="228" t="s">
         <v>264</v>
@@ -17565,24 +17578,24 @@
         <v>0</v>
       </c>
       <c r="G214" s="228" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H214" s="230" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="I214" s="231">
         <v>1</v>
       </c>
       <c r="J214" s="230" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" s="228" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B215" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C215" s="228" t="s">
         <v>264</v>
@@ -17597,10 +17610,10 @@
         <v>550</v>
       </c>
       <c r="G215" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H215" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I215" s="231">
         <v>0</v>
@@ -17611,10 +17624,10 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="228" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B216" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C216" s="228" t="s">
         <v>264</v>
@@ -17629,7 +17642,7 @@
         <v>120</v>
       </c>
       <c r="G216" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H216" s="230" t="s">
         <v>176</v>
@@ -17643,10 +17656,10 @@
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" s="228" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B217" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C217" s="228" t="s">
         <v>261</v>
@@ -17661,10 +17674,10 @@
         <v>355</v>
       </c>
       <c r="G217" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H217" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I217" s="231">
         <v>0</v>
@@ -17675,10 +17688,10 @@
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="228" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B218" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C218" s="228" t="s">
         <v>264</v>
@@ -17693,10 +17706,10 @@
         <v>300</v>
       </c>
       <c r="G218" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H218" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I218" s="231">
         <v>0</v>
@@ -17707,10 +17720,10 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="228" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B219" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C219" s="228" t="s">
         <v>264</v>
@@ -17725,7 +17738,7 @@
         <v>410</v>
       </c>
       <c r="G219" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H219" s="230" t="s">
         <v>176</v>
@@ -17739,10 +17752,10 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="228" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B220" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C220" s="228" t="s">
         <v>264</v>
@@ -17757,7 +17770,7 @@
         <v>650</v>
       </c>
       <c r="G220" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H220" s="230" t="s">
         <v>183</v>
@@ -17771,10 +17784,10 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="228" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B221" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C221" s="228" t="s">
         <v>264</v>
@@ -17789,7 +17802,7 @@
         <v>385</v>
       </c>
       <c r="G221" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H221" s="230" t="s">
         <v>165</v>
@@ -17803,10 +17816,10 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="228" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B222" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C222" s="228" t="s">
         <v>261</v>
@@ -17821,7 +17834,7 @@
         <v>220</v>
       </c>
       <c r="G222" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H222" s="230" t="s">
         <v>165</v>
@@ -17835,10 +17848,10 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="228" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B223" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C223" s="228" t="s">
         <v>264</v>
@@ -17853,7 +17866,7 @@
         <v>0</v>
       </c>
       <c r="G223" s="228" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H223" s="230" t="s">
         <v>165</v>
@@ -17862,15 +17875,15 @@
         <v>480</v>
       </c>
       <c r="J223" s="230" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="228" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B224" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C224" s="228" t="s">
         <v>264</v>
@@ -17885,7 +17898,7 @@
         <v>0</v>
       </c>
       <c r="G224" s="228" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H224" s="230" t="s">
         <v>165</v>
@@ -17894,15 +17907,15 @@
         <v>480</v>
       </c>
       <c r="J224" s="230" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="228" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B225" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C225" s="228" t="s">
         <v>264</v>
@@ -17917,7 +17930,7 @@
         <v>0</v>
       </c>
       <c r="G225" s="228" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H225" s="230" t="s">
         <v>165</v>
@@ -17926,15 +17939,15 @@
         <v>480</v>
       </c>
       <c r="J225" s="230" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="228" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B226" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C226" s="228" t="s">
         <v>264</v>
@@ -17949,24 +17962,24 @@
         <v>0</v>
       </c>
       <c r="G226" s="228" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H226" s="230" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="I226" s="231">
         <v>1</v>
       </c>
       <c r="J226" s="230" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="228" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B227" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C227" s="228" t="s">
         <v>261</v>
@@ -17981,7 +17994,7 @@
         <v>450</v>
       </c>
       <c r="G227" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H227" s="230" t="s">
         <v>165</v>
@@ -17995,10 +18008,10 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="228" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B228" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C228" s="228" t="s">
         <v>264</v>
@@ -18013,7 +18026,7 @@
         <v>250</v>
       </c>
       <c r="G228" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H228" s="230" t="s">
         <v>165</v>
@@ -18027,10 +18040,10 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="228" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B229" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C229" s="228" t="s">
         <v>261</v>
@@ -18045,10 +18058,10 @@
         <v>360</v>
       </c>
       <c r="G229" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H229" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I229" s="231">
         <v>0</v>
@@ -18059,10 +18072,10 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="228" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B230" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C230" s="228" t="s">
         <v>264</v>
@@ -18077,7 +18090,7 @@
         <v>350</v>
       </c>
       <c r="G230" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H230" s="230" t="s">
         <v>183</v>
@@ -18091,10 +18104,10 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="228" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B231" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C231" s="228" t="s">
         <v>264</v>
@@ -18109,24 +18122,24 @@
         <v>0</v>
       </c>
       <c r="G231" s="228" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H231" s="230" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="I231" s="231">
         <v>480</v>
       </c>
       <c r="J231" s="230" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" s="228" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B232" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C232" s="228" t="s">
         <v>264</v>
@@ -18141,10 +18154,10 @@
         <v>450</v>
       </c>
       <c r="G232" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H232" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I232" s="231">
         <v>0</v>
@@ -18155,10 +18168,10 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" s="228" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B233" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C233" s="228" t="s">
         <v>264</v>
@@ -18173,7 +18186,7 @@
         <v>450</v>
       </c>
       <c r="G233" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H233" s="230" t="s">
         <v>167</v>
@@ -18187,10 +18200,10 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="228" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B234" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C234" s="228" t="s">
         <v>264</v>
@@ -18205,10 +18218,10 @@
         <v>250</v>
       </c>
       <c r="G234" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H234" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I234" s="231">
         <v>0</v>
@@ -18219,10 +18232,10 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" s="228" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B235" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C235" s="228" t="s">
         <v>261</v>
@@ -18251,10 +18264,10 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" s="228" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B236" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C236" s="228" t="s">
         <v>261</v>
@@ -18269,10 +18282,10 @@
         <v>350</v>
       </c>
       <c r="G236" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H236" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I236" s="231">
         <v>0</v>
@@ -18283,10 +18296,10 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" s="228" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B237" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C237" s="228" t="s">
         <v>261</v>
@@ -18301,10 +18314,10 @@
         <v>330</v>
       </c>
       <c r="G237" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H237" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I237" s="231">
         <v>0</v>
@@ -18315,10 +18328,10 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" s="228" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B238" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C238" s="228" t="s">
         <v>264</v>
@@ -18333,10 +18346,10 @@
         <v>120</v>
       </c>
       <c r="G238" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H238" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I238" s="231">
         <v>0</v>
@@ -18347,10 +18360,10 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" s="228" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B239" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C239" s="228" t="s">
         <v>261</v>
@@ -18365,10 +18378,10 @@
         <v>395</v>
       </c>
       <c r="G239" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H239" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I239" s="231">
         <v>0</v>
@@ -18379,10 +18392,10 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" s="228" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B240" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C240" s="228" t="s">
         <v>264</v>
@@ -18397,10 +18410,10 @@
         <v>150</v>
       </c>
       <c r="G240" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H240" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I240" s="231">
         <v>0</v>
@@ -18411,10 +18424,10 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" s="228" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B241" s="228" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C241" s="228" t="s">
         <v>261</v>
@@ -18429,10 +18442,10 @@
         <v>385</v>
       </c>
       <c r="G241" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H241" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I241" s="231">
         <v>0</v>
@@ -18443,10 +18456,10 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" s="228" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B242" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C242" s="228" t="s">
         <v>261</v>
@@ -18461,10 +18474,10 @@
         <v>460</v>
       </c>
       <c r="G242" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H242" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I242" s="231">
         <v>0</v>
@@ -18475,10 +18488,10 @@
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" s="228" t="s">
+        <v>837</v>
+      </c>
+      <c r="B243" s="228" t="s">
         <v>836</v>
-      </c>
-      <c r="B243" s="228" t="s">
-        <v>835</v>
       </c>
       <c r="C243" s="228" t="s">
         <v>264</v>
@@ -18493,7 +18506,7 @@
         <v>160</v>
       </c>
       <c r="G243" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H243" s="230" t="s">
         <v>165</v>
@@ -18507,10 +18520,10 @@
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" s="228" t="s">
+        <v>837</v>
+      </c>
+      <c r="B244" s="228" t="s">
         <v>836</v>
-      </c>
-      <c r="B244" s="228" t="s">
-        <v>835</v>
       </c>
       <c r="C244" s="228" t="s">
         <v>261</v>
@@ -18525,10 +18538,10 @@
         <v>135</v>
       </c>
       <c r="G244" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H244" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I244" s="231">
         <v>0</v>
@@ -18539,10 +18552,10 @@
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" s="228" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B245" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C245" s="228" t="s">
         <v>264</v>
@@ -18557,7 +18570,7 @@
         <v>285</v>
       </c>
       <c r="G245" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H245" s="230" t="s">
         <v>165</v>
@@ -18571,10 +18584,10 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" s="228" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B246" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C246" s="228" t="s">
         <v>261</v>
@@ -18589,10 +18602,10 @@
         <v>100</v>
       </c>
       <c r="G246" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H246" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I246" s="231">
         <v>0</v>
@@ -18603,10 +18616,10 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" s="228" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B247" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C247" s="228" t="s">
         <v>264</v>
@@ -18621,10 +18634,10 @@
         <v>410</v>
       </c>
       <c r="G247" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H247" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I247" s="231">
         <v>0</v>
@@ -18635,10 +18648,10 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" s="228" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B248" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C248" s="228" t="s">
         <v>261</v>
@@ -18653,10 +18666,10 @@
         <v>465</v>
       </c>
       <c r="G248" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H248" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I248" s="231">
         <v>0</v>
@@ -18667,10 +18680,10 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" s="228" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B249" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C249" s="228" t="s">
         <v>261</v>
@@ -18685,7 +18698,7 @@
         <v>395</v>
       </c>
       <c r="G249" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H249" s="230" t="s">
         <v>165</v>
@@ -18699,10 +18712,10 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" s="228" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B250" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C250" s="228" t="s">
         <v>264</v>
@@ -18717,10 +18730,10 @@
         <v>160</v>
       </c>
       <c r="G250" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H250" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I250" s="231">
         <v>0</v>
@@ -18731,10 +18744,10 @@
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" s="228" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B251" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C251" s="228" t="s">
         <v>261</v>
@@ -18749,10 +18762,10 @@
         <v>350</v>
       </c>
       <c r="G251" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H251" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I251" s="231">
         <v>0</v>
@@ -18763,10 +18776,10 @@
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" s="228" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B252" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C252" s="228" t="s">
         <v>264</v>
@@ -18781,7 +18794,7 @@
         <v>310</v>
       </c>
       <c r="G252" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H252" s="230" t="s">
         <v>165</v>
@@ -18795,10 +18808,10 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" s="228" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B253" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C253" s="228" t="s">
         <v>261</v>
@@ -18813,10 +18826,10 @@
         <v>460</v>
       </c>
       <c r="G253" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H253" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I253" s="231">
         <v>0</v>
@@ -18827,10 +18840,10 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" s="228" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B254" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C254" s="228" t="s">
         <v>261</v>
@@ -18845,10 +18858,10 @@
         <v>470</v>
       </c>
       <c r="G254" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H254" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I254" s="231">
         <v>0</v>
@@ -18859,10 +18872,10 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" s="228" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B255" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C255" s="228" t="s">
         <v>261</v>
@@ -18877,7 +18890,7 @@
         <v>310</v>
       </c>
       <c r="G255" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H255" s="230" t="s">
         <v>165</v>
@@ -18891,10 +18904,10 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" s="228" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B256" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C256" s="228" t="s">
         <v>261</v>
@@ -18909,7 +18922,7 @@
         <v>0</v>
       </c>
       <c r="G256" s="228" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H256" s="230" t="s">
         <v>165</v>
@@ -18918,15 +18931,15 @@
         <v>480</v>
       </c>
       <c r="J256" s="230" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" s="228" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B257" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C257" s="228" t="s">
         <v>261</v>
@@ -18955,10 +18968,10 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" s="228" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B258" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C258" s="228" t="s">
         <v>261</v>
@@ -18973,10 +18986,10 @@
         <v>380</v>
       </c>
       <c r="G258" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H258" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I258" s="231">
         <v>0</v>
@@ -18987,10 +19000,10 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" s="228" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B259" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C259" s="228" t="s">
         <v>261</v>
@@ -19005,10 +19018,10 @@
         <v>450</v>
       </c>
       <c r="G259" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H259" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I259" s="231">
         <v>0</v>
@@ -19019,10 +19032,10 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" s="228" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B260" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C260" s="228" t="s">
         <v>261</v>
@@ -19037,7 +19050,7 @@
         <v>280</v>
       </c>
       <c r="G260" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H260" s="230" t="s">
         <v>165</v>
@@ -19051,10 +19064,10 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" s="228" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B261" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C261" s="228" t="s">
         <v>264</v>
@@ -19069,7 +19082,7 @@
         <v>1500</v>
       </c>
       <c r="G261" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H261" s="230" t="s">
         <v>165</v>
@@ -19083,10 +19096,10 @@
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262" s="228" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B262" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C262" s="228" t="s">
         <v>261</v>
@@ -19101,7 +19114,7 @@
         <v>280</v>
       </c>
       <c r="G262" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H262" s="230" t="s">
         <v>165</v>
@@ -19115,10 +19128,10 @@
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263" s="228" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B263" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C263" s="228" t="s">
         <v>261</v>
@@ -19133,7 +19146,7 @@
         <v>0</v>
       </c>
       <c r="G263" s="228" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H263" s="230" t="s">
         <v>165</v>
@@ -19142,15 +19155,15 @@
         <v>480</v>
       </c>
       <c r="J263" s="230" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264" s="228" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B264" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C264" s="228" t="s">
         <v>261</v>
@@ -19165,10 +19178,10 @@
         <v>395</v>
       </c>
       <c r="G264" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H264" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I264" s="231">
         <v>0</v>
@@ -19179,10 +19192,10 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265" s="228" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B265" s="228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C265" s="228" t="s">
         <v>264</v>
@@ -19197,7 +19210,7 @@
         <v>325</v>
       </c>
       <c r="G265" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H265" s="230" t="s">
         <v>165</v>
@@ -19206,15 +19219,15 @@
         <v>180</v>
       </c>
       <c r="J265" s="230" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A266" s="228" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B266" s="228" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C266" s="228" t="s">
         <v>261</v>
@@ -19229,10 +19242,10 @@
         <v>255</v>
       </c>
       <c r="G266" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H266" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I266" s="231">
         <v>0</v>
@@ -19243,10 +19256,10 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267" s="228" t="s">
+        <v>860</v>
+      </c>
+      <c r="B267" s="228" t="s">
         <v>859</v>
-      </c>
-      <c r="B267" s="228" t="s">
-        <v>858</v>
       </c>
       <c r="C267" s="228" t="s">
         <v>261</v>
@@ -19261,24 +19274,24 @@
         <v>0</v>
       </c>
       <c r="G267" s="228" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H267" s="230" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="I267" s="231">
         <v>1</v>
       </c>
       <c r="J267" s="230" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A268" s="228" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B268" s="228" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C268" s="228" t="s">
         <v>261</v>
@@ -19293,7 +19306,7 @@
         <v>265</v>
       </c>
       <c r="G268" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H268" s="230" t="s">
         <v>165</v>
@@ -19307,10 +19320,10 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269" s="228" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B269" s="228" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C269" s="228" t="s">
         <v>261</v>
@@ -19325,10 +19338,10 @@
         <v>450</v>
       </c>
       <c r="G269" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H269" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I269" s="231">
         <v>0</v>
@@ -19339,10 +19352,10 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A270" s="228" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B270" s="228" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C270" s="228" t="s">
         <v>261</v>
@@ -19357,10 +19370,10 @@
         <v>510</v>
       </c>
       <c r="G270" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H270" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I270" s="231">
         <v>0</v>
@@ -19371,10 +19384,10 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271" s="228" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B271" s="228" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C271" s="228" t="s">
         <v>261</v>
@@ -19389,7 +19402,7 @@
         <v>700</v>
       </c>
       <c r="G271" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H271" s="230" t="s">
         <v>165</v>
@@ -19403,10 +19416,10 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A272" s="228" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B272" s="228" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C272" s="228" t="s">
         <v>261</v>
@@ -19421,7 +19434,7 @@
         <v>420</v>
       </c>
       <c r="G272" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H272" s="230" t="s">
         <v>165</v>
@@ -19435,10 +19448,10 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273" s="228" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B273" s="228" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C273" s="228" t="s">
         <v>261</v>
@@ -19462,15 +19475,15 @@
         <v>90</v>
       </c>
       <c r="J273" s="230" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" s="228" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B274" s="228" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C274" s="228" t="s">
         <v>264</v>
@@ -19499,10 +19512,10 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275" s="228" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B275" s="228" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C275" s="228" t="s">
         <v>264</v>
@@ -19517,10 +19530,10 @@
         <v>550</v>
       </c>
       <c r="G275" s="228" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H275" s="230" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I275" s="231">
         <v>0</v>
@@ -19550,7 +19563,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="346" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B1" s="336"/>
       <c r="C1" s="336"/>
@@ -19562,13 +19575,13 @@
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="232"/>
       <c r="B2" s="233" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C2" s="234">
         <v>22000</v>
       </c>
       <c r="D2" s="347" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="E2" s="336"/>
       <c r="F2" s="336"/>
@@ -19576,7 +19589,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="342" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B4" s="336"/>
       <c r="C4" s="336"/>
@@ -19587,30 +19600,30 @@
     </row>
     <row r="5" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="235" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B5" s="235" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C5" s="235" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D5" s="235" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="E5" s="235" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="F5" s="235" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="G5" s="235" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="236" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B6" s="237">
         <f>COUNTIFS(OTIF_Data!$B$2:$B$275, A6, OTIF_Data!$G$2:$G$275, "&lt;&gt;Changeover")</f>
@@ -19639,7 +19652,7 @@
     </row>
     <row r="7" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="236" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B7" s="237">
         <f>COUNTIFS(OTIF_Data!$B$2:$B$275, A7, OTIF_Data!$G$2:$G$275, "&lt;&gt;Changeover")</f>
@@ -19668,7 +19681,7 @@
     </row>
     <row r="8" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="236" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B8" s="237">
         <f>COUNTIFS(OTIF_Data!$B$2:$B$275, A8, OTIF_Data!$G$2:$G$275, "&lt;&gt;Changeover")</f>
@@ -19697,7 +19710,7 @@
     </row>
     <row r="9" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="236" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B9" s="237">
         <f>COUNTIFS(OTIF_Data!$B$2:$B$275, A9, OTIF_Data!$G$2:$G$275, "&lt;&gt;Changeover")</f>
@@ -19726,7 +19739,7 @@
     </row>
     <row r="10" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="236" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B10" s="237">
         <f>COUNTIFS(OTIF_Data!$B$2:$B$275, A10, OTIF_Data!$G$2:$G$275, "&lt;&gt;Changeover")</f>
@@ -19755,7 +19768,7 @@
     </row>
     <row r="11" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="236" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B11" s="237">
         <f>COUNTIFS(OTIF_Data!$B$2:$B$275, A11, OTIF_Data!$G$2:$G$275, "&lt;&gt;Changeover")</f>
@@ -19784,7 +19797,7 @@
     </row>
     <row r="12" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="236" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B12" s="237">
         <f>COUNTIFS(OTIF_Data!$B$2:$B$275, A12, OTIF_Data!$G$2:$G$275, "&lt;&gt;Changeover")</f>
@@ -19813,7 +19826,7 @@
     </row>
     <row r="13" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="236" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B13" s="237">
         <f>COUNTIFS(OTIF_Data!$B$2:$B$275, A13, OTIF_Data!$G$2:$G$275, "&lt;&gt;Changeover")</f>
@@ -19842,7 +19855,7 @@
     </row>
     <row r="14" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="236" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B14" s="237">
         <f>COUNTIFS(OTIF_Data!$B$2:$B$275, A14, OTIF_Data!$G$2:$G$275, "&lt;&gt;Changeover")</f>
@@ -19871,7 +19884,7 @@
     </row>
     <row r="15" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="241" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B15" s="242">
         <f>SUM(B6:B14)</f>
@@ -19900,7 +19913,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="342" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B17" s="336"/>
       <c r="C17" s="336"/>
@@ -19914,19 +19927,19 @@
         <v>240</v>
       </c>
       <c r="B18" s="235" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C18" s="235" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D18" s="235" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E18" s="235" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="F18" s="235" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G18" s="235" t="s">
         <v>386</v>
@@ -19934,7 +19947,7 @@
     </row>
     <row r="19" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="245" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B19" s="237" t="s">
         <v>261</v>
@@ -19951,7 +19964,7 @@
         <v>0.81213636363636366</v>
       </c>
       <c r="F19" s="245" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="G19" s="245" t="s">
         <v>17</v>
@@ -19959,7 +19972,7 @@
     </row>
     <row r="20" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="245" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B20" s="237" t="s">
         <v>261</v>
@@ -19976,15 +19989,15 @@
         <v>0</v>
       </c>
       <c r="F20" s="245" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="G20" s="245" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="245" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B21" s="237" t="s">
         <v>261</v>
@@ -20009,7 +20022,7 @@
     </row>
     <row r="22" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="245" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B22" s="237" t="s">
         <v>261</v>
@@ -20026,7 +20039,7 @@
         <v>1.1130909090909091</v>
       </c>
       <c r="F22" s="245" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="G22" s="245" t="s">
         <v>20</v>
@@ -20034,7 +20047,7 @@
     </row>
     <row r="23" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="245" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B23" s="237" t="s">
         <v>261</v>
@@ -20051,7 +20064,7 @@
         <v>0.46609090909090911</v>
       </c>
       <c r="F23" s="245" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="G23" s="245" t="s">
         <v>14</v>
@@ -20059,7 +20072,7 @@
     </row>
     <row r="24" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="245" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B24" s="237" t="s">
         <v>261</v>
@@ -20084,7 +20097,7 @@
     </row>
     <row r="25" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="245" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B25" s="237" t="s">
         <v>261</v>
@@ -20109,7 +20122,7 @@
     </row>
     <row r="26" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="245" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B26" s="237" t="s">
         <v>261</v>
@@ -20129,12 +20142,12 @@
         <v>175</v>
       </c>
       <c r="G26" s="247" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="245" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B27" s="237" t="s">
         <v>264</v>
@@ -20159,7 +20172,7 @@
     </row>
     <row r="28" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="245" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B28" s="237" t="s">
         <v>264</v>
@@ -20176,7 +20189,7 @@
         <v>1.1609090909090909</v>
       </c>
       <c r="F28" s="245" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="G28" s="245" t="s">
         <v>20</v>
@@ -20184,7 +20197,7 @@
     </row>
     <row r="29" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="248" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B29" s="249"/>
       <c r="C29" s="250">
@@ -20204,12 +20217,12 @@
         <v>15002</v>
       </c>
       <c r="G29" s="255" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="342" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B32" s="336"/>
       <c r="C32" s="336"/>
@@ -20220,10 +20233,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="251" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B33" s="343" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C33" s="344"/>
       <c r="D33" s="344"/>
@@ -20233,10 +20246,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="251" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B34" s="343" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C34" s="344"/>
       <c r="D34" s="344"/>
@@ -20246,10 +20259,10 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="251" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B36" s="343" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C36" s="344"/>
       <c r="D36" s="344"/>
@@ -20259,10 +20272,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="251" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B37" s="343" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C37" s="344"/>
       <c r="D37" s="344"/>
@@ -20272,10 +20285,10 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="251" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B39" s="343" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C39" s="344"/>
       <c r="D39" s="344"/>
@@ -20285,10 +20298,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="251" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B40" s="343" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C40" s="344"/>
       <c r="D40" s="344"/>
@@ -20298,7 +20311,7 @@
     </row>
     <row r="42" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="348" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B42" s="336"/>
       <c r="C42" s="336"/>
@@ -20309,10 +20322,10 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="251" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B43" s="343" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C43" s="344"/>
       <c r="D43" s="344"/>
@@ -20322,10 +20335,10 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="251" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B44" s="343" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C44" s="344"/>
       <c r="D44" s="344"/>
@@ -20335,10 +20348,10 @@
     </row>
     <row r="45" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="251" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B45" s="343" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C45" s="344"/>
       <c r="D45" s="344"/>
@@ -20348,10 +20361,10 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="251" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B46" s="343" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C46" s="344"/>
       <c r="D46" s="344"/>
@@ -20433,7 +20446,7 @@
       </c>
       <c r="H1" s="179">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="I1" s="10"/>
       <c r="J1" s="173"/>
@@ -20628,11 +20641,11 @@
       </c>
       <c r="G7" s="187">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$100,MATCH(MRP!D7,Tubex_Dashboard!$F$11:$F$100,0))</f>
-        <v>169924</v>
+        <v>198008</v>
       </c>
       <c r="H7" s="188">
         <f t="shared" si="0"/>
-        <v>530076</v>
+        <v>501992</v>
       </c>
       <c r="I7" s="188"/>
     </row>
@@ -20679,11 +20692,11 @@
       </c>
       <c r="G9" s="105">
         <f>SUM(G3:G8)</f>
-        <v>278704</v>
+        <v>306788</v>
       </c>
       <c r="H9" s="105">
         <f>SUMIF(H3:H8, "&gt;0")</f>
-        <v>774412</v>
+        <v>746328</v>
       </c>
       <c r="I9" s="12"/>
       <c r="J9" s="173"/>
@@ -21186,19 +21199,19 @@
       </c>
       <c r="E22" s="148">
         <f>SUMPRODUCT((TableBOM[Item ID]=A22)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))/1000)</f>
-        <v>5104.6688000000004</v>
+        <v>4857.5296000000008</v>
       </c>
       <c r="F22" s="149">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A22,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A22,TableInventory[Item ID],0)),0)</f>
-        <v>1525</v>
+        <v>1595</v>
       </c>
       <c r="G22" s="148">
         <f t="shared" si="1"/>
-        <v>-3579.6688000000004</v>
+        <v>-3262.5296000000008</v>
       </c>
       <c r="H22" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A22)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F22*1000*SUMPRODUCT((TableBOM[Item ID]=A22)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A22)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
-        <v>173295</v>
+        <v>181250</v>
       </c>
       <c r="I22" s="150" t="str">
         <f t="shared" si="2"/>
@@ -21546,7 +21559,7 @@
       </c>
       <c r="E30" s="148">
         <f>SUMPRODUCT((TableBOM[Item ID]=A30)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))/1000)</f>
-        <v>216.88266160000003</v>
+        <v>208.23278960000002</v>
       </c>
       <c r="F30" s="148">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A30,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A30,TableInventory[Item ID],0)),0)</f>
@@ -21554,11 +21567,11 @@
       </c>
       <c r="G30" s="148">
         <f t="shared" si="1"/>
-        <v>-16.882661600000034</v>
+        <v>-8.232789600000018</v>
       </c>
       <c r="H30" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A30)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F30*1000*SUMPRODUCT((TableBOM[Item ID]=A30)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A30)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
-        <v>714130</v>
+        <v>716821</v>
       </c>
       <c r="I30" s="150" t="str">
         <f t="shared" si="2"/>
@@ -21730,7 +21743,7 @@
       </c>
       <c r="E34" s="148">
         <f>SUMPRODUCT((TableBOM[Item ID]=A34)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))/1000)</f>
-        <v>582.79430000000002</v>
+        <v>562.09639200000004</v>
       </c>
       <c r="F34" s="148">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A34,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A34,TableInventory[Item ID],0)),0)</f>
@@ -21738,11 +21751,11 @@
       </c>
       <c r="G34" s="148">
         <f t="shared" si="1"/>
-        <v>-432.79430000000002</v>
+        <v>-412.09639200000004</v>
       </c>
       <c r="H34" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A34)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F34*1000*SUMPRODUCT((TableBOM[Item ID]=A34)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A34)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
-        <v>199319</v>
+        <v>199164</v>
       </c>
       <c r="I34" s="150" t="str">
         <f t="shared" si="2"/>
@@ -22058,7 +22071,7 @@
       </c>
       <c r="E42" s="148">
         <f>SUMPRODUCT((TableBOM[Item ID]=A42)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))/1000)</f>
-        <v>302.56212800000003</v>
+        <v>293.91225600000001</v>
       </c>
       <c r="F42" s="148">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A42,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A42,TableInventory[Item ID],0)),0)</f>
@@ -22066,11 +22079,11 @@
       </c>
       <c r="G42" s="148">
         <f t="shared" si="1"/>
-        <v>177.43787199999997</v>
+        <v>186.08774399999999</v>
       </c>
       <c r="H42" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A42)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F42*1000*SUMPRODUCT((TableBOM[Item ID]=A42)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A42)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
-        <v>1193665</v>
+        <v>1182929</v>
       </c>
       <c r="I42" s="150" t="str">
         <f t="shared" si="2"/>
@@ -22652,7 +22665,7 @@
       </c>
       <c r="E57" s="148">
         <f>SUMPRODUCT((TableBOM[Item ID]=A57)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))/1000)</f>
-        <v>540677.52</v>
+        <v>512031.84</v>
       </c>
       <c r="F57" s="148">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A57,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A57,TableInventory[Item ID],0)),0)</f>
@@ -22660,7 +22673,7 @@
       </c>
       <c r="G57" s="148">
         <f t="shared" si="3"/>
-        <v>-488453.52</v>
+        <v>-459807.84</v>
       </c>
       <c r="H57" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A57)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F57*1000*SUMPRODUCT((TableBOM[Item ID]=A57)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A57)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
@@ -23146,7 +23159,7 @@
       </c>
       <c r="E70" s="148">
         <f>SUMPRODUCT((TableBOM[Item ID]=A70)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))/1000)</f>
-        <v>2680.99405376</v>
+        <v>2551.1965459200001</v>
       </c>
       <c r="F70" s="148">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A70,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A70,TableInventory[Item ID],0)),0)</f>
@@ -23154,7 +23167,7 @@
       </c>
       <c r="G70" s="148">
         <f t="shared" si="3"/>
-        <v>-1890.99405376</v>
+        <v>-1761.1965459200001</v>
       </c>
       <c r="H70" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A70)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F70*1000*SUMPRODUCT((TableBOM[Item ID]=A70)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A70)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
@@ -23298,7 +23311,7 @@
       </c>
       <c r="E74" s="148">
         <f>SUMPRODUCT((TableBOM[Item ID]=A74)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))/1000)</f>
-        <v>6.7534037120000008</v>
+        <v>6.4963789439999999</v>
       </c>
       <c r="F74" s="148">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A74,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A74,TableInventory[Item ID],0)),0)</f>
@@ -23306,11 +23319,11 @@
       </c>
       <c r="G74" s="148">
         <f t="shared" si="3"/>
-        <v>18.746596287999999</v>
+        <v>19.003621056</v>
       </c>
       <c r="H74" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A74)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F74*1000*SUMPRODUCT((TableBOM[Item ID]=A74)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A74)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
-        <v>2735288</v>
+        <v>2733271</v>
       </c>
       <c r="I74" s="150" t="str">
         <f t="shared" si="4"/>
@@ -23382,7 +23395,7 @@
       </c>
       <c r="E76" s="148">
         <f>SUMPRODUCT((TableBOM[Item ID]=A76)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))/1000)</f>
-        <v>132.81653440000002</v>
+        <v>127.99732</v>
       </c>
       <c r="F76" s="148">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A76,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A76,TableInventory[Item ID],0)),0)</f>
@@ -23390,11 +23403,11 @@
       </c>
       <c r="G76" s="148">
         <f t="shared" ref="G76:G107" si="5">F76-E76</f>
-        <v>173.18346559999998</v>
+        <v>178.00268</v>
       </c>
       <c r="H76" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A76)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F76*1000*SUMPRODUCT((TableBOM[Item ID]=A76)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A76)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
-        <v>1784191</v>
+        <v>1784228</v>
       </c>
       <c r="I76" s="150" t="str">
         <f t="shared" ref="I76:I93" si="6">IF(E76=0,"Not needed",IF(G76&lt;0,"SHORTAGE",IF(G76&lt;E76*0.1,"LOW","OK")))</f>
@@ -24175,11 +24188,11 @@
       </c>
       <c r="G99" s="192">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$100,MATCH(MRP!D99,Tubex_Dashboard!$F$11:$F$100,0))</f>
-        <v>32880</v>
+        <v>36840</v>
       </c>
       <c r="H99" s="193">
         <f>F99-G99</f>
-        <v>27280</v>
+        <v>23320</v>
       </c>
       <c r="I99" s="194"/>
     </row>
@@ -24263,11 +24276,11 @@
       </c>
       <c r="G102" s="192">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$100,MATCH(MRP!D102,Tubex_Dashboard!$F$11:$F$100,0))</f>
-        <v>23520</v>
+        <v>27120</v>
       </c>
       <c r="H102" s="193">
         <f>F102-G102</f>
-        <v>23480</v>
+        <v>19880</v>
       </c>
       <c r="I102" s="194"/>
     </row>
@@ -24285,11 +24298,11 @@
       </c>
       <c r="G103" s="105">
         <f>SUM(G98:G102)</f>
-        <v>259620</v>
+        <v>267180</v>
       </c>
       <c r="H103" s="105">
         <f>SUMIF(H98:H102, "&gt;0")</f>
-        <v>635207</v>
+        <v>627647</v>
       </c>
       <c r="I103" s="12"/>
       <c r="J103" s="173"/>
@@ -24362,7 +24375,7 @@
       </c>
       <c r="E106" s="149">
         <f>SUMPRODUCT((TableBOM[Item ID]=A106)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))/1000)</f>
-        <v>15910.847999999998</v>
+        <v>15734.649599999997</v>
       </c>
       <c r="F106" s="149">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A106,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A106,TableInventory[Item ID],0)),0)</f>
@@ -24370,11 +24383,11 @@
       </c>
       <c r="G106" s="149">
         <f t="shared" ref="G106:G112" si="7">F106-E106</f>
-        <v>-15145.847999999998</v>
+        <v>-14969.649599999997</v>
       </c>
       <c r="H106" s="158">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A106)*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F106*1000*SUMPRODUCT((TableBOM[Item ID]=A106)*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102)))/SUMPRODUCT((TableBOM[Item ID]=A106)*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
-        <v>30541</v>
+        <v>30515</v>
       </c>
       <c r="I106" s="152" t="str">
         <f t="shared" ref="I106:I112" si="8">IF(E106=0,"Not needed",IF(G106&lt;0,"SHORTAGE",IF(G106&lt;E106*0.1,"LOW","OK")))</f>
@@ -24400,7 +24413,7 @@
       </c>
       <c r="E107" s="149">
         <f>SUMPRODUCT((TableBOM[Item ID]=A107)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))/1000)</f>
-        <v>61.987299999999998</v>
+        <v>52.713700000000003</v>
       </c>
       <c r="F107" s="149">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A107,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A107,TableInventory[Item ID],0)),0)</f>
@@ -24408,7 +24421,7 @@
       </c>
       <c r="G107" s="149">
         <f t="shared" si="7"/>
-        <v>-61.987299999999998</v>
+        <v>-52.713700000000003</v>
       </c>
       <c r="H107" s="158">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A107)*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F107*1000*SUMPRODUCT((TableBOM[Item ID]=A107)*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102)))/SUMPRODUCT((TableBOM[Item ID]=A107)*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
@@ -24514,7 +24527,7 @@
       </c>
       <c r="E110" s="149">
         <f>SUMPRODUCT((TableBOM[Item ID]=A110)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))/1000)</f>
-        <v>6014.082862799999</v>
+        <v>5976.1343807999992</v>
       </c>
       <c r="F110" s="149">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A110,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A110,TableInventory[Item ID],0)),0)</f>
@@ -24522,11 +24535,11 @@
       </c>
       <c r="G110" s="149">
         <f t="shared" si="7"/>
-        <v>-5686.082862799999</v>
+        <v>-5648.1343807999992</v>
       </c>
       <c r="H110" s="158">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A110)*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F110*1000*SUMPRODUCT((TableBOM[Item ID]=A110)*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102)))/SUMPRODUCT((TableBOM[Item ID]=A110)*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
-        <v>33363</v>
+        <v>33357</v>
       </c>
       <c r="I110" s="152" t="str">
         <f t="shared" si="8"/>
@@ -24552,7 +24565,7 @@
       </c>
       <c r="E111" s="17">
         <f>SUMPRODUCT((TableBOM[Item ID]=A111)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))/1000)</f>
-        <v>225.007666</v>
+        <v>190.50904600000001</v>
       </c>
       <c r="F111" s="17">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A111,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A111,TableInventory[Item ID],0)),0)</f>
@@ -24560,7 +24573,7 @@
       </c>
       <c r="G111" s="17">
         <f t="shared" si="7"/>
-        <v>-75.007666</v>
+        <v>-40.509046000000012</v>
       </c>
       <c r="H111" s="160">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A111)*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F111*1000*SUMPRODUCT((TableBOM[Item ID]=A111)*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102)))/SUMPRODUCT((TableBOM[Item ID]=A111)*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
@@ -24590,7 +24603,7 @@
       </c>
       <c r="E112" s="149">
         <f>SUMPRODUCT((TableBOM[Item ID]=A112)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))/1000)</f>
-        <v>3.6524402499999997</v>
+        <v>3.60897025</v>
       </c>
       <c r="F112" s="149">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A112,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A112,TableInventory[Item ID],0)),0)</f>
@@ -24598,7 +24611,7 @@
       </c>
       <c r="G112" s="149">
         <f t="shared" si="7"/>
-        <v>-3.6524402499999997</v>
+        <v>-3.60897025</v>
       </c>
       <c r="H112" s="158">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A112)*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F112*1000*SUMPRODUCT((TableBOM[Item ID]=A112)*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102)))/SUMPRODUCT((TableBOM[Item ID]=A112)*((SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))&gt;0)*(SUMIF($D$98:$D$102,TableBOM[Product ID],$H$98:$H$102))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
@@ -29097,23 +29110,25 @@
         <v>8006</v>
       </c>
       <c r="G100" s="262">
-        <v>6120</v>
+        <v>9000</v>
       </c>
       <c r="H100" s="262">
         <v>6120</v>
       </c>
       <c r="I100" s="262">
-        <v>0</v>
+        <v>2880</v>
       </c>
       <c r="J100" s="263">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="K100" s="260"/>
       <c r="L100" s="260"/>
       <c r="M100" s="260"/>
       <c r="N100" s="260"/>
-      <c r="O100" s="260"/>
+      <c r="O100" s="260">
+        <v>650</v>
+      </c>
       <c r="P100" s="260"/>
       <c r="Q100" s="260"/>
       <c r="R100" s="260"/>
@@ -29125,32 +29140,32 @@
         <v>46287</v>
       </c>
       <c r="B101" s="260" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C101" s="260" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D101" s="260" t="s">
-        <v>20</v>
-      </c>
-      <c r="E101" s="260">
-        <v>30</v>
+        <v>139</v>
+      </c>
+      <c r="E101" s="260" t="s">
+        <v>138</v>
       </c>
       <c r="F101" s="260">
-        <v>6206</v>
+        <v>8005</v>
       </c>
       <c r="G101" s="262">
-        <v>24000</v>
+        <v>4530</v>
       </c>
       <c r="H101" s="262">
-        <v>23850</v>
+        <v>3960</v>
       </c>
       <c r="I101" s="262">
-        <v>150</v>
+        <v>570</v>
       </c>
       <c r="J101" s="263">
         <f t="shared" si="3"/>
-        <v>6.2500000000000003E-3</v>
+        <v>0.12582781456953643</v>
       </c>
       <c r="K101" s="260"/>
       <c r="L101" s="260"/>
@@ -29168,7 +29183,7 @@
         <v>46287</v>
       </c>
       <c r="B102" s="260" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C102" s="260" t="s">
         <v>19</v>
@@ -29183,23 +29198,21 @@
         <v>6206</v>
       </c>
       <c r="G102" s="262">
-        <v>5185</v>
+        <v>24000</v>
       </c>
       <c r="H102" s="262">
-        <v>4990</v>
+        <v>23850</v>
       </c>
       <c r="I102" s="262">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c r="J102" s="263">
         <f t="shared" si="3"/>
-        <v>3.7608486017357765E-2</v>
+        <v>6.2500000000000003E-3</v>
       </c>
       <c r="K102" s="260"/>
       <c r="L102" s="260"/>
-      <c r="M102" s="260">
-        <v>360</v>
-      </c>
+      <c r="M102" s="260"/>
       <c r="N102" s="260"/>
       <c r="O102" s="260"/>
       <c r="P102" s="260"/>
@@ -29208,12 +29221,272 @@
       <c r="S102" s="260"/>
       <c r="T102" s="260"/>
     </row>
-    <row r="103" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="261">
+        <v>46287</v>
+      </c>
+      <c r="B103" s="260" t="s">
+        <v>261</v>
+      </c>
+      <c r="C103" s="260" t="s">
+        <v>19</v>
+      </c>
+      <c r="D103" s="260" t="s">
+        <v>20</v>
+      </c>
+      <c r="E103" s="260">
+        <v>30</v>
+      </c>
+      <c r="F103" s="260">
+        <v>6206</v>
+      </c>
+      <c r="G103" s="262">
+        <v>5185</v>
+      </c>
+      <c r="H103" s="262">
+        <v>4990</v>
+      </c>
+      <c r="I103" s="262">
+        <v>195</v>
+      </c>
+      <c r="J103" s="263">
+        <f t="shared" si="3"/>
+        <v>3.7608486017357765E-2</v>
+      </c>
+      <c r="K103" s="260"/>
+      <c r="L103" s="260"/>
+      <c r="M103" s="260">
+        <v>360</v>
+      </c>
+      <c r="N103" s="260"/>
+      <c r="O103" s="260"/>
+      <c r="P103" s="260"/>
+      <c r="Q103" s="260"/>
+      <c r="R103" s="260"/>
+      <c r="S103" s="260"/>
+      <c r="T103" s="260"/>
+    </row>
+    <row r="104" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="261">
+        <v>46288</v>
+      </c>
+      <c r="B104" s="260" t="s">
+        <v>257</v>
+      </c>
+      <c r="C104" s="260" t="s">
+        <v>19</v>
+      </c>
+      <c r="D104" s="260" t="s">
+        <v>20</v>
+      </c>
+      <c r="E104" s="260">
+        <v>30</v>
+      </c>
+      <c r="F104" s="260">
+        <v>6206</v>
+      </c>
+      <c r="G104" s="262">
+        <v>28000</v>
+      </c>
+      <c r="H104" s="262">
+        <v>27480</v>
+      </c>
+      <c r="I104" s="262">
+        <v>520</v>
+      </c>
+      <c r="J104" s="263">
+        <f t="shared" si="3"/>
+        <v>1.8571428571428572E-2</v>
+      </c>
+      <c r="K104" s="260"/>
+      <c r="L104" s="260"/>
+      <c r="M104" s="260"/>
+      <c r="N104" s="260"/>
+      <c r="O104" s="260"/>
+      <c r="P104" s="260"/>
+      <c r="Q104" s="260"/>
+      <c r="R104" s="260"/>
+      <c r="S104" s="260"/>
+      <c r="T104" s="260"/>
+    </row>
+    <row r="105" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="261">
+        <v>46288</v>
+      </c>
+      <c r="B105" s="260" t="s">
+        <v>258</v>
+      </c>
+      <c r="C105" s="260" t="s">
+        <v>19</v>
+      </c>
+      <c r="D105" s="260" t="s">
+        <v>20</v>
+      </c>
+      <c r="E105" s="260">
+        <v>30</v>
+      </c>
+      <c r="F105" s="260">
+        <v>6206</v>
+      </c>
+      <c r="G105" s="262">
+        <v>25000</v>
+      </c>
+      <c r="H105" s="262">
+        <v>24980</v>
+      </c>
+      <c r="I105" s="262">
+        <v>20</v>
+      </c>
+      <c r="J105" s="263">
+        <f t="shared" si="3"/>
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="K105" s="260"/>
+      <c r="L105" s="260"/>
+      <c r="M105" s="260"/>
+      <c r="N105" s="260"/>
+      <c r="O105" s="260"/>
+      <c r="P105" s="260"/>
+      <c r="Q105" s="260"/>
+      <c r="R105" s="260"/>
+      <c r="S105" s="260"/>
+      <c r="T105" s="260"/>
+    </row>
+    <row r="106" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="261">
+        <v>46288</v>
+      </c>
+      <c r="B106" s="260" t="s">
+        <v>259</v>
+      </c>
+      <c r="C106" s="260" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" s="260" t="s">
+        <v>147</v>
+      </c>
+      <c r="E106" s="260" t="s">
+        <v>146</v>
+      </c>
+      <c r="F106" s="260">
+        <v>8006</v>
+      </c>
+      <c r="G106" s="262">
+        <v>5840</v>
+      </c>
+      <c r="H106" s="262">
+        <v>3600</v>
+      </c>
+      <c r="I106" s="262">
+        <v>2240</v>
+      </c>
+      <c r="J106" s="263">
+        <f t="shared" si="3"/>
+        <v>0.38356164383561642</v>
+      </c>
+      <c r="K106" s="260"/>
+      <c r="L106" s="260"/>
+      <c r="M106" s="260"/>
+      <c r="N106" s="260"/>
+      <c r="O106" s="260">
+        <v>480</v>
+      </c>
+      <c r="P106" s="260"/>
+      <c r="Q106" s="260"/>
+      <c r="R106" s="260"/>
+      <c r="S106" s="260">
+        <v>240</v>
+      </c>
+      <c r="T106" s="260"/>
+    </row>
+    <row r="107" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="261">
+        <v>46288</v>
+      </c>
+      <c r="B107" s="260" t="s">
+        <v>260</v>
+      </c>
+      <c r="C107" s="260" t="s">
+        <v>19</v>
+      </c>
+      <c r="D107" s="260" t="s">
+        <v>20</v>
+      </c>
+      <c r="E107" s="260">
+        <v>30</v>
+      </c>
+      <c r="F107" s="260">
+        <v>6206</v>
+      </c>
+      <c r="G107" s="262">
+        <v>21000</v>
+      </c>
+      <c r="H107" s="262">
+        <v>20870</v>
+      </c>
+      <c r="I107" s="262">
+        <v>130</v>
+      </c>
+      <c r="J107" s="263">
+        <f t="shared" si="3"/>
+        <v>6.1904761904761907E-3</v>
+      </c>
+      <c r="K107" s="260">
+        <v>60</v>
+      </c>
+      <c r="L107" s="260"/>
+      <c r="M107" s="260"/>
+      <c r="N107" s="260"/>
+      <c r="O107" s="260"/>
+      <c r="P107" s="260"/>
+      <c r="Q107" s="260"/>
+      <c r="R107" s="260"/>
+      <c r="S107" s="260"/>
+      <c r="T107" s="260"/>
+    </row>
+    <row r="108" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="261">
+        <v>46288</v>
+      </c>
+      <c r="B108" s="260" t="s">
+        <v>261</v>
+      </c>
+      <c r="C108" s="260" t="s">
+        <v>19</v>
+      </c>
+      <c r="D108" s="260" t="s">
+        <v>20</v>
+      </c>
+      <c r="E108" s="260">
+        <v>30</v>
+      </c>
+      <c r="F108" s="260">
+        <v>6206</v>
+      </c>
+      <c r="G108" s="262">
+        <v>28734</v>
+      </c>
+      <c r="H108" s="262">
+        <v>28084</v>
+      </c>
+      <c r="I108" s="262">
+        <v>650</v>
+      </c>
+      <c r="J108" s="263">
+        <f t="shared" si="3"/>
+        <v>2.2621284888981696E-2</v>
+      </c>
+      <c r="K108" s="260"/>
+      <c r="L108" s="260"/>
+      <c r="M108" s="260"/>
+      <c r="N108" s="260"/>
+      <c r="O108" s="260"/>
+      <c r="P108" s="260"/>
+      <c r="Q108" s="260"/>
+      <c r="R108" s="260"/>
+      <c r="S108" s="260"/>
+      <c r="T108" s="260"/>
+    </row>
     <row r="109" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="110" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="111" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -44410,7 +44683,7 @@
       </c>
       <c r="J1" s="180">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="46" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -44668,11 +44941,11 @@
         <v>1500</v>
       </c>
       <c r="I9" s="258">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="J9" s="175">
         <f>IFERROR(IF(H9+I9="","-",ROUND((H9+I9)/(IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A9,TableBOM[Per 1000 Units])&gt;0,AVERAGEIF(TableBOM[Item ID],A9,TableBOM[Per 1000 Units]),AVERAGEIF(TableBOM[Material Category],B9,TableBOM[Per 1000 Units])),AVERAGEIF(TableBOM[Material Category],B9,TableBOM[Per 1000 Units]))/1000),0)),"-")</f>
-        <v>190625</v>
+        <v>199375</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44756,7 +45029,7 @@
       <c r="I13" s="49"/>
       <c r="J13" s="180">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -47694,7 +47967,7 @@
       <c r="I95" s="49"/>
       <c r="J95" s="181">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -55040,14 +55313,14 @@
   </autoFilter>
   <mergeCells count="9">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A92:K92"/>
-    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A65:K65"/>
     <mergeCell ref="A81:K81"/>
+    <mergeCell ref="A75:K75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -55199,7 +55472,7 @@
         <v>592</v>
       </c>
       <c r="F6" s="266">
-        <v>13000</v>
+        <v>35000</v>
       </c>
       <c r="G6" s="264" t="s">
         <v>589</v>
@@ -55469,7 +55742,7 @@
         <v>592</v>
       </c>
       <c r="F15" s="266">
-        <v>57970</v>
+        <v>35970</v>
       </c>
       <c r="G15" s="264" t="s">
         <v>589</v>
@@ -55487,25 +55760,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="264">
-        <v>6515</v>
+        <v>6206</v>
       </c>
       <c r="C16" s="265" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D16" s="265" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E16" s="264" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="F16" s="266">
-        <v>10000</v>
+        <v>28082</v>
       </c>
       <c r="G16" s="264" t="s">
         <v>589</v>
       </c>
       <c r="H16" s="267" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="I16" s="268"/>
       <c r="J16" s="269"/>
@@ -55513,29 +55786,29 @@
       <c r="L16" s="269"/>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="270">
+      <c r="A17" s="264">
         <v>14</v>
       </c>
-      <c r="B17" s="270">
-        <v>6530</v>
-      </c>
-      <c r="C17" s="271" t="s">
-        <v>223</v>
-      </c>
-      <c r="D17" s="271" t="s">
-        <v>224</v>
-      </c>
-      <c r="E17" s="270" t="s">
-        <v>593</v>
-      </c>
-      <c r="F17" s="272">
-        <v>11340</v>
-      </c>
-      <c r="G17" s="270" t="s">
+      <c r="B17" s="264">
+        <v>6515</v>
+      </c>
+      <c r="C17" s="265" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="265" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="264" t="s">
         <v>599</v>
       </c>
-      <c r="H17" s="273" t="s">
-        <v>600</v>
+      <c r="F17" s="266">
+        <v>10000</v>
+      </c>
+      <c r="G17" s="264" t="s">
+        <v>589</v>
+      </c>
+      <c r="H17" s="267" t="s">
+        <v>597</v>
       </c>
       <c r="I17" s="268"/>
       <c r="J17" s="269"/>
@@ -55543,29 +55816,29 @@
       <c r="L17" s="269"/>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="264">
+      <c r="A18" s="270">
         <v>15</v>
       </c>
-      <c r="B18" s="264">
-        <v>5699</v>
-      </c>
-      <c r="C18" s="265" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="265" t="s">
-        <v>195</v>
-      </c>
-      <c r="E18" s="264" t="s">
+      <c r="B18" s="270">
+        <v>6530</v>
+      </c>
+      <c r="C18" s="271" t="s">
+        <v>223</v>
+      </c>
+      <c r="D18" s="271" t="s">
+        <v>224</v>
+      </c>
+      <c r="E18" s="270" t="s">
+        <v>593</v>
+      </c>
+      <c r="F18" s="272">
+        <v>11340</v>
+      </c>
+      <c r="G18" s="270" t="s">
+        <v>600</v>
+      </c>
+      <c r="H18" s="273" t="s">
         <v>601</v>
-      </c>
-      <c r="F18" s="266">
-        <v>14790</v>
-      </c>
-      <c r="G18" s="264" t="s">
-        <v>589</v>
-      </c>
-      <c r="H18" s="267" t="s">
-        <v>602</v>
       </c>
       <c r="I18" s="268"/>
       <c r="J18" s="269"/>
@@ -55577,25 +55850,25 @@
         <v>16</v>
       </c>
       <c r="B19" s="264">
-        <v>5731</v>
+        <v>5699</v>
       </c>
       <c r="C19" s="265" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="265" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E19" s="264" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F19" s="266">
-        <v>13770</v>
+        <v>14790</v>
       </c>
       <c r="G19" s="264" t="s">
         <v>589</v>
       </c>
       <c r="H19" s="267" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I19" s="268"/>
       <c r="J19" s="269"/>
@@ -55603,29 +55876,29 @@
       <c r="L19" s="269"/>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="270">
+      <c r="A20" s="264">
         <v>17</v>
       </c>
-      <c r="B20" s="270">
-        <v>6624</v>
-      </c>
-      <c r="C20" s="271" t="s">
+      <c r="B20" s="264">
+        <v>5731</v>
+      </c>
+      <c r="C20" s="265" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="271" t="s">
-        <v>191</v>
-      </c>
-      <c r="E20" s="270" t="s">
+      <c r="D20" s="265" t="s">
+        <v>196</v>
+      </c>
+      <c r="E20" s="264" t="s">
+        <v>602</v>
+      </c>
+      <c r="F20" s="266">
+        <v>13770</v>
+      </c>
+      <c r="G20" s="264" t="s">
+        <v>589</v>
+      </c>
+      <c r="H20" s="267" t="s">
         <v>603</v>
-      </c>
-      <c r="F20" s="272">
-        <v>15876</v>
-      </c>
-      <c r="G20" s="270" t="s">
-        <v>599</v>
-      </c>
-      <c r="H20" s="273" t="s">
-        <v>602</v>
       </c>
       <c r="I20" s="268"/>
       <c r="J20" s="269"/>
@@ -55637,25 +55910,25 @@
         <v>18</v>
       </c>
       <c r="B21" s="270">
-        <v>5731</v>
+        <v>6624</v>
       </c>
       <c r="C21" s="271" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="271" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E21" s="270" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="F21" s="272">
-        <v>33660</v>
+        <v>15876</v>
       </c>
       <c r="G21" s="270" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H21" s="273" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I21" s="268"/>
       <c r="J21" s="269"/>
@@ -55663,14 +55936,30 @@
       <c r="L21" s="269"/>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="274"/>
-      <c r="B22" s="274"/>
-      <c r="C22" s="275"/>
-      <c r="D22" s="275"/>
-      <c r="E22" s="274"/>
-      <c r="F22" s="276"/>
-      <c r="G22" s="274"/>
-      <c r="H22" s="277"/>
+      <c r="A22" s="270">
+        <v>19</v>
+      </c>
+      <c r="B22" s="270">
+        <v>5731</v>
+      </c>
+      <c r="C22" s="271" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="271" t="s">
+        <v>196</v>
+      </c>
+      <c r="E22" s="270" t="s">
+        <v>602</v>
+      </c>
+      <c r="F22" s="272">
+        <v>33660</v>
+      </c>
+      <c r="G22" s="270" t="s">
+        <v>600</v>
+      </c>
+      <c r="H22" s="273" t="s">
+        <v>603</v>
+      </c>
       <c r="I22" s="268"/>
       <c r="J22" s="269"/>
       <c r="K22" s="269"/>
@@ -56779,7 +57068,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="339" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B1" s="340"/>
       <c r="C1" s="340"/>
@@ -56790,140 +57079,140 @@
     </row>
     <row r="2" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="211" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B2" s="211" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="212" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D2" s="212" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E2" s="212" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F2" s="211" t="s">
         <v>32</v>
       </c>
       <c r="G2" s="211" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="260.10000000000002" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="213" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B3" s="214" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C3" s="215" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D3" s="216" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E3" s="217" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F3" s="218" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G3" s="219" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="230.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="220" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B4" s="221" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C4" s="222" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D4" s="223" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E4" s="224" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F4" s="225" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G4" s="226" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="230.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="213" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B5" s="214" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C5" s="215" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D5" s="216" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E5" s="217" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F5" s="218" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G5" s="219" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="260.10000000000002" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="220" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B6" s="221" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C6" s="222" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D6" s="223" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E6" s="224" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F6" s="225" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G6" s="226" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="260.10000000000002" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="213" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B7" s="214" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C7" s="215" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D7" s="216" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E7" s="217" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F7" s="218" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G7" s="219" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="240" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/Tubex_Sep26.xlsx
+++ b/Tubex_Sep26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_D15FADB0A5B5DBFA451313CDACCE3ADB82CCEB8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_5F2603F6BABD1BF2F00BD720E40ED6DA951C73A9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5551,8 +5551,8 @@
     <col min="13" max="13" width="14.7109375" style="90" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" style="90" customWidth="1"/>
     <col min="15" max="15" width="9.5703125" style="90" customWidth="1"/>
-    <col min="16" max="219" width="8.7109375" style="90" customWidth="1"/>
-    <col min="220" max="16384" width="8.7109375" style="90"/>
+    <col min="16" max="220" width="8.7109375" style="90" customWidth="1"/>
+    <col min="221" max="16384" width="8.7109375" style="90"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -21203,15 +21203,15 @@
       </c>
       <c r="F22" s="149">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A22,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A22,TableInventory[Item ID],0)),0)</f>
-        <v>1595</v>
+        <v>1345</v>
       </c>
       <c r="G22" s="148">
         <f t="shared" si="1"/>
-        <v>-3262.5296000000008</v>
+        <v>-3512.5296000000008</v>
       </c>
       <c r="H22" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A22)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F22*1000*SUMPRODUCT((TableBOM[Item ID]=A22)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A22)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
-        <v>181250</v>
+        <v>152841</v>
       </c>
       <c r="I22" s="150" t="str">
         <f t="shared" si="2"/>
@@ -21563,15 +21563,15 @@
       </c>
       <c r="F30" s="148">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A30,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A30,TableInventory[Item ID],0)),0)</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G30" s="148">
         <f t="shared" si="1"/>
-        <v>-8.232789600000018</v>
+        <v>-58.232789600000018</v>
       </c>
       <c r="H30" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A30)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F30*1000*SUMPRODUCT((TableBOM[Item ID]=A30)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A30)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
-        <v>716821</v>
+        <v>537616</v>
       </c>
       <c r="I30" s="150" t="str">
         <f t="shared" si="2"/>
@@ -22669,15 +22669,15 @@
       </c>
       <c r="F57" s="148">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A57,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A57,TableInventory[Item ID],0)),0)</f>
-        <v>52224</v>
+        <v>22224</v>
       </c>
       <c r="G57" s="148">
         <f t="shared" si="3"/>
-        <v>-459807.84</v>
+        <v>-489807.84</v>
       </c>
       <c r="H57" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A57)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F57*1000*SUMPRODUCT((TableBOM[Item ID]=A57)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A57)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
-        <v>51200</v>
+        <v>21788</v>
       </c>
       <c r="I57" s="150" t="str">
         <f t="shared" si="4"/>
@@ -23163,15 +23163,15 @@
       </c>
       <c r="F70" s="148">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A70,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A70,TableInventory[Item ID],0)),0)</f>
-        <v>790</v>
+        <v>540</v>
       </c>
       <c r="G70" s="148">
         <f t="shared" si="3"/>
-        <v>-1761.1965459200001</v>
+        <v>-2011.1965459200001</v>
       </c>
       <c r="H70" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A70)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F70*1000*SUMPRODUCT((TableBOM[Item ID]=A70)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A70)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
-        <v>170929</v>
+        <v>116838</v>
       </c>
       <c r="I70" s="150" t="str">
         <f t="shared" si="4"/>
@@ -23399,15 +23399,15 @@
       </c>
       <c r="F76" s="148">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A76,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A76,TableInventory[Item ID],0)),0)</f>
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="G76" s="148">
         <f t="shared" ref="G76:G107" si="5">F76-E76</f>
-        <v>178.00268</v>
+        <v>172.00268</v>
       </c>
       <c r="H76" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A76)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F76*1000*SUMPRODUCT((TableBOM[Item ID]=A76)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A76)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
-        <v>1784228</v>
+        <v>1749243</v>
       </c>
       <c r="I76" s="150" t="str">
         <f t="shared" ref="I76:I93" si="6">IF(E76=0,"Not needed",IF(G76&lt;0,"SHORTAGE",IF(G76&lt;E76*0.1,"LOW","OK")))</f>
@@ -44934,18 +44934,18 @@
         <v>1775</v>
       </c>
       <c r="G9" s="258">
-        <v>275</v>
+        <v>525</v>
       </c>
       <c r="H9" s="259">
         <f t="shared" si="0"/>
-        <v>1500</v>
+        <v>1250</v>
       </c>
       <c r="I9" s="258">
         <v>95</v>
       </c>
       <c r="J9" s="175">
         <f>IFERROR(IF(H9+I9="","-",ROUND((H9+I9)/(IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A9,TableBOM[Per 1000 Units])&gt;0,AVERAGEIF(TableBOM[Item ID],A9,TableBOM[Per 1000 Units]),AVERAGEIF(TableBOM[Material Category],B9,TableBOM[Per 1000 Units])),AVERAGEIF(TableBOM[Material Category],B9,TableBOM[Per 1000 Units]))/1000),0)),"-")</f>
-        <v>199375</v>
+        <v>168125</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45220,16 +45220,16 @@
         <v>300</v>
       </c>
       <c r="G19" s="117">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="H19" s="118">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I19" s="117"/>
       <c r="J19" s="177">
         <f>IFERROR(IF(H19+I19="","-",ROUND((H19+I19)/(IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A19,TableBOM[Per 1000 Units])&gt;0,AVERAGEIF(TableBOM[Item ID],A19,TableBOM[Per 1000 Units]),AVERAGEIF(TableBOM[Material Category],B19,TableBOM[Per 1000 Units])),AVERAGEIF(TableBOM[Material Category],B19,TableBOM[Per 1000 Units]))/1000),0)),"-")</f>
-        <v>768608</v>
+        <v>576456</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46233,16 +46233,16 @@
         <v>200000</v>
       </c>
       <c r="G47" s="117">
-        <v>267776</v>
+        <v>297776</v>
       </c>
       <c r="H47" s="118">
         <f t="shared" ref="H47:H78" si="2">E47+F47-G47</f>
-        <v>52224</v>
+        <v>22224</v>
       </c>
       <c r="I47" s="117"/>
       <c r="J47" s="177">
         <f>IFERROR(IF(H47+I47="","-",ROUND((H47+I47)/(IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A47,TableBOM[Per 1000 Units])&gt;0,AVERAGEIF(TableBOM[Item ID],A47,TableBOM[Per 1000 Units]),AVERAGEIF(TableBOM[Material Category],B47,TableBOM[Per 1000 Units])),AVERAGEIF(TableBOM[Material Category],B47,TableBOM[Per 1000 Units]))/1000),0)),"-")</f>
-        <v>52224</v>
+        <v>22224</v>
       </c>
       <c r="K47" s="130"/>
       <c r="L47" s="119"/>
@@ -46661,16 +46661,16 @@
         <v>690</v>
       </c>
       <c r="G58" s="117">
-        <v>996</v>
+        <v>1246</v>
       </c>
       <c r="H58" s="118">
         <f t="shared" si="2"/>
-        <v>790</v>
+        <v>540</v>
       </c>
       <c r="I58" s="117"/>
       <c r="J58" s="177">
         <f>IFERROR(IF(H58+I58="","-",ROUND((H58+I58)/(IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A58,TableBOM[Per 1000 Units])&gt;0,AVERAGEIF(TableBOM[Item ID],A58,TableBOM[Per 1000 Units]),AVERAGEIF(TableBOM[Material Category],B58,TableBOM[Per 1000 Units])),AVERAGEIF(TableBOM[Material Category],B58,TableBOM[Per 1000 Units]))/1000),0)),"-")</f>
-        <v>235600</v>
+        <v>161043</v>
       </c>
       <c r="K58" s="130"/>
       <c r="L58" s="119"/>
@@ -46813,16 +46813,16 @@
         <v>0</v>
       </c>
       <c r="G62" s="117">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H62" s="118">
         <f t="shared" si="2"/>
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="I62" s="117"/>
       <c r="J62" s="177">
         <f>IFERROR(IF(H62+I62="","-",ROUND((H62+I62)/(IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A62,TableBOM[Per 1000 Units])&gt;0,AVERAGEIF(TableBOM[Item ID],A62,TableBOM[Per 1000 Units]),AVERAGEIF(TableBOM[Material Category],B62,TableBOM[Per 1000 Units])),AVERAGEIF(TableBOM[Material Category],B62,TableBOM[Per 1000 Units]))/1000),0)),"-")</f>
-        <v>896112</v>
+        <v>878542</v>
       </c>
       <c r="K62" s="131"/>
       <c r="L62" s="120"/>
@@ -55313,14 +55313,14 @@
   </autoFilter>
   <mergeCells count="9">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A75:K75"/>
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A92:K92"/>
+    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A65:K65"/>
     <mergeCell ref="A81:K81"/>
-    <mergeCell ref="A75:K75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Tubex_Sep26.xlsx
+++ b/Tubex_Sep26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_E57EDDB8E916FC0CCC93F66F3855FDF1A1F2C4F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_45550E76BB326ABFB74573A29A6CB8D7F84CC5F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6045" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6135" uniqueCount="905">
   <si>
     <t>SEPTEMBER 2026 Tube Required Orders</t>
   </si>
@@ -577,6 +577,9 @@
     <t>Dispatch</t>
   </si>
   <si>
+    <t>Compressor Issue</t>
+  </si>
+  <si>
     <t>Changeover</t>
   </si>
   <si>
@@ -592,21 +595,21 @@
     <t>PF Machine Downtime – MTD (PET)</t>
   </si>
   <si>
+    <t>Mega Grey</t>
+  </si>
+  <si>
+    <t>M.G</t>
+  </si>
+  <si>
     <t>Electrical</t>
   </si>
   <si>
-    <t>Mega Grey</t>
-  </si>
-  <si>
-    <t>M.G</t>
+    <t>PET BOTTLE SMALL (130ML) TRANSPARENT</t>
   </si>
   <si>
     <t>Power Shutdown</t>
   </si>
   <si>
-    <t>Compressor Issue</t>
-  </si>
-  <si>
     <t>TRANSPARENT BOTTLE 150ML</t>
   </si>
   <si>
@@ -742,9 +745,6 @@
     <t>WHITE SMALL BOTTLE 120ML</t>
   </si>
   <si>
-    <t>PET BOTTLE SMALL (130ML) TRANSPARENT</t>
-  </si>
-  <si>
     <t>PET BOTTLE LARGE 200ML WHITE</t>
   </si>
   <si>
@@ -1780,7 +1780,7 @@
     <t>Top 10 inks = 81.7% of all consumption. Remaining 15 inks share 18.3%.  Source: ERP ST_Stk_Cons_YFI.rpt · May 2025–Apr 2026 · 8,617,293 pcs produced.</t>
   </si>
   <si>
-    <t>FG STOCK IN HAND — Last Updated: 24-Sep-2026</t>
+    <t>FG STOCK IN HAND — Last Updated: 01-Oct-2026</t>
   </si>
   <si>
     <t>Shows latest date only from FG Stock In hand (Production.xlsx). Older dates are discarded. Re-run update_production.py to refresh.</t>
@@ -1813,15 +1813,21 @@
     <t>Ready for dispatch</t>
   </si>
   <si>
+    <t>130ml</t>
+  </si>
+  <si>
+    <t>120ml</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
     <t>25</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
     <t>Samsol 45 - No Order</t>
   </si>
   <si>
@@ -1837,22 +1843,16 @@
     <t>Inprogress On Latex</t>
   </si>
   <si>
-    <t>32</t>
+    <t>20.5</t>
+  </si>
+  <si>
+    <t>Order Cancel</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>Not Ready</t>
-  </si>
-  <si>
-    <t>Inprogress on Capping</t>
-  </si>
-  <si>
-    <t>20.5</t>
-  </si>
-  <si>
-    <t>Order Cancel</t>
-  </si>
-  <si>
-    <t>19</t>
   </si>
   <si>
     <t>ALPHA CONTAINERS — STRATEGIC ROADMAP &amp; AGENTIC IMPLEMENTATION SPECIFICATIONS</t>
@@ -4998,7 +4998,7 @@
     <xf numFmtId="168" fontId="53" fillId="20" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="54" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="55" fillId="23" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5031,12 +5031,6 @@
     <xf numFmtId="166" fontId="45" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="45" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="54" fillId="22" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="37" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5071,6 +5065,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="54" fillId="22" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="37" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="62" fillId="24" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5569,8 +5569,8 @@
     <col min="13" max="13" width="14.7109375" style="90" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" style="90" customWidth="1"/>
     <col min="15" max="15" width="9.5703125" style="90" customWidth="1"/>
-    <col min="16" max="225" width="8.7109375" style="90" customWidth="1"/>
-    <col min="226" max="16384" width="8.7109375" style="90"/>
+    <col min="16" max="226" width="8.7109375" style="90" customWidth="1"/>
+    <col min="227" max="16384" width="8.7109375" style="90"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -5605,22 +5605,22 @@
     </row>
     <row r="2" spans="1:29" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="87"/>
-      <c r="B2" s="331" t="s">
+      <c r="B2" s="329" t="s">
         <v>152</v>
       </c>
-      <c r="C2" s="324"/>
-      <c r="D2" s="324"/>
-      <c r="E2" s="325"/>
-      <c r="F2" s="324"/>
-      <c r="G2" s="326"/>
-      <c r="H2" s="324"/>
-      <c r="I2" s="324"/>
-      <c r="J2" s="324"/>
-      <c r="K2" s="324"/>
-      <c r="L2" s="324"/>
-      <c r="M2" s="324"/>
-      <c r="N2" s="324"/>
-      <c r="O2" s="324"/>
+      <c r="C2" s="322"/>
+      <c r="D2" s="322"/>
+      <c r="E2" s="323"/>
+      <c r="F2" s="322"/>
+      <c r="G2" s="324"/>
+      <c r="H2" s="322"/>
+      <c r="I2" s="322"/>
+      <c r="J2" s="322"/>
+      <c r="K2" s="322"/>
+      <c r="L2" s="322"/>
+      <c r="M2" s="322"/>
+      <c r="N2" s="322"/>
+      <c r="O2" s="322"/>
       <c r="P2" s="87"/>
       <c r="Q2" s="87"/>
       <c r="R2" s="87"/>
@@ -5638,25 +5638,25 @@
     </row>
     <row r="3" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="87"/>
-      <c r="B3" s="323" t="s">
+      <c r="B3" s="321" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="324"/>
-      <c r="D3" s="324"/>
-      <c r="E3" s="325"/>
-      <c r="F3" s="324"/>
-      <c r="G3" s="326"/>
-      <c r="H3" s="328">
+      <c r="C3" s="322"/>
+      <c r="D3" s="322"/>
+      <c r="E3" s="323"/>
+      <c r="F3" s="322"/>
+      <c r="G3" s="324"/>
+      <c r="H3" s="326">
         <f ca="1">TODAY()</f>
         <v>46302</v>
       </c>
-      <c r="I3" s="324"/>
-      <c r="J3" s="324"/>
-      <c r="K3" s="324"/>
-      <c r="L3" s="324"/>
-      <c r="M3" s="324"/>
-      <c r="N3" s="324"/>
-      <c r="O3" s="324"/>
+      <c r="I3" s="322"/>
+      <c r="J3" s="322"/>
+      <c r="K3" s="322"/>
+      <c r="L3" s="322"/>
+      <c r="M3" s="322"/>
+      <c r="N3" s="322"/>
+      <c r="O3" s="322"/>
       <c r="P3" s="87"/>
       <c r="Q3" s="87"/>
       <c r="R3" s="87"/>
@@ -5709,28 +5709,28 @@
       </c>
       <c r="C5" s="144">
         <f>MAX(Production_Log!$A$3:$A$8961)</f>
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="D5" s="92" t="s">
         <v>155</v>
       </c>
       <c r="E5" s="92"/>
       <c r="F5" s="93"/>
-      <c r="G5" s="330" t="s">
+      <c r="G5" s="328" t="s">
         <v>156</v>
       </c>
-      <c r="H5" s="324"/>
+      <c r="H5" s="322"/>
       <c r="I5" s="94"/>
-      <c r="J5" s="330" t="s">
+      <c r="J5" s="328" t="s">
         <v>157</v>
       </c>
-      <c r="K5" s="324"/>
+      <c r="K5" s="322"/>
       <c r="L5" s="112"/>
-      <c r="M5" s="332" t="s">
+      <c r="M5" s="330" t="s">
         <v>158</v>
       </c>
-      <c r="N5" s="333"/>
-      <c r="O5" s="333"/>
+      <c r="N5" s="331"/>
+      <c r="O5" s="331"/>
       <c r="P5" s="284"/>
       <c r="Q5" s="284"/>
       <c r="R5" s="284"/>
@@ -5748,28 +5748,28 @@
     </row>
     <row r="6" spans="1:29" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="87"/>
-      <c r="B6" s="327">
+      <c r="B6" s="325">
         <f>SUMPRODUCT((Production_Log!$A$3:$A$8961=MAX(Production_Log!$A$3:$A$8961))*(LEFT(Production_Log!$B$3:$B$8961,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8961)))*Production_Log!$H$3:$H$8961)</f>
-        <v>28084</v>
-      </c>
-      <c r="C6" s="324"/>
+        <v>15470</v>
+      </c>
+      <c r="C6" s="322"/>
       <c r="D6" s="95">
         <f>SUMIF($B$11:$B$67,"TUBE",$H$11:$H$67)</f>
-        <v>306788</v>
-      </c>
-      <c r="E6" s="327"/>
-      <c r="F6" s="324"/>
+        <v>419362</v>
+      </c>
+      <c r="E6" s="325"/>
+      <c r="F6" s="322"/>
       <c r="G6" s="96">
         <f t="array" ref="G6">IFERROR(SUMPRODUCT((Production_Log!$F$3:$F$8961&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8961,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8961)))*Production_Log!$I$3:$I$8961)/SUMPRODUCT((Production_Log!$F$3:$F$8961&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8961,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8961)))*(Production_Log!$H$3:$H$8961+Production_Log!$I$3:$I$8961)),"-")</f>
-        <v>2.3910048583691532E-2</v>
+        <v>2.4029118870247411E-2</v>
       </c>
       <c r="H6" s="96"/>
       <c r="I6" s="94"/>
-      <c r="J6" s="327">
+      <c r="J6" s="325">
         <f>SUMIF($B$11:$B$67,"TUBE",$K$11:$K$67)</f>
         <v>491479</v>
       </c>
-      <c r="K6" s="324"/>
+      <c r="K6" s="322"/>
       <c r="L6" s="97"/>
       <c r="M6" s="286" t="s">
         <v>26</v>
@@ -5802,17 +5802,17 @@
       </c>
       <c r="C7" s="145">
         <f>MAX(Production_Log!$A$3:$A$8961)</f>
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="D7" s="98" t="s">
         <v>162</v>
       </c>
       <c r="E7" s="98"/>
       <c r="F7" s="99"/>
-      <c r="G7" s="329" t="s">
+      <c r="G7" s="327" t="s">
         <v>163</v>
       </c>
-      <c r="H7" s="324"/>
+      <c r="H7" s="322"/>
       <c r="I7" s="100"/>
       <c r="J7" s="99" t="s">
         <v>157</v>
@@ -5827,8 +5827,8 @@
         <v>34</v>
       </c>
       <c r="O7" s="290">
-        <f>IFERROR(N7/$N$12,"")</f>
-        <v>0.45333333333333331</v>
+        <f t="shared" ref="O7:O12" si="0">IFERROR(N7/$N$13,"")</f>
+        <v>0.35416666666666669</v>
       </c>
       <c r="P7" s="284"/>
       <c r="Q7" s="284"/>
@@ -5847,39 +5847,39 @@
     </row>
     <row r="8" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="87"/>
-      <c r="B8" s="334">
+      <c r="B8" s="332">
         <f>SUMPRODUCT((Production_Log!$A$3:$A$8961=MAX(Production_Log!$A$3:$A$8961))*(Production_Log!$B$3:$B$8961="PF Machine")*Production_Log!$H$3:$H$8961)</f>
-        <v>3600</v>
-      </c>
-      <c r="C8" s="324"/>
+        <v>11500</v>
+      </c>
+      <c r="C8" s="322"/>
       <c r="D8" s="101">
         <f>SUMIF($B$11:$B$67,"PET",$H$11:$H$67)</f>
-        <v>267180</v>
-      </c>
-      <c r="E8" s="334"/>
-      <c r="F8" s="324"/>
+        <v>322360</v>
+      </c>
+      <c r="E8" s="332"/>
+      <c r="F8" s="322"/>
       <c r="G8" s="102">
         <f t="array" ref="G8">IFERROR(SUMPRODUCT((Production_Log!$B$3:$B$8961="PF Machine")*Production_Log!$I$3:$I$8961)/SUMPRODUCT((Production_Log!$B$3:$B$8961="PF Machine")*(Production_Log!$H$3:$H$8961+Production_Log!$I$3:$I$8961)),0)</f>
-        <v>0.19941269888832289</v>
+        <v>0.21368130139208363</v>
       </c>
       <c r="H8" s="102"/>
       <c r="I8" s="100"/>
-      <c r="J8" s="334">
+      <c r="J8" s="332">
         <f>SUMIF($B$11:$B$67,"PET",$K$11:$K$67)</f>
         <v>285400</v>
       </c>
-      <c r="K8" s="324"/>
+      <c r="K8" s="322"/>
       <c r="L8" s="103"/>
       <c r="M8" s="288" t="s">
         <v>165</v>
       </c>
       <c r="N8" s="289">
         <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,5)="Press")+(LEFT(Production_Log!$B$3:$B$1000,5)="Print")+(LEFT(Production_Log!$B$3:$B$1000,5)="PLINE"))*Production_Log!$M$3:$M$1000)/60</f>
-        <v>16.833333333333332</v>
+        <v>19.833333333333332</v>
       </c>
       <c r="O8" s="290">
-        <f>IFERROR(N8/$N$12,"")</f>
-        <v>0.22444444444444442</v>
+        <f t="shared" si="0"/>
+        <v>0.20659722222222221</v>
       </c>
       <c r="P8" s="284"/>
       <c r="Q8" s="284"/>
@@ -5898,29 +5898,29 @@
     </row>
     <row r="9" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="87"/>
-      <c r="B9" s="335" t="s">
+      <c r="B9" s="333" t="s">
         <v>166</v>
       </c>
-      <c r="C9" s="336"/>
-      <c r="D9" s="336"/>
-      <c r="E9" s="336"/>
-      <c r="F9" s="336"/>
-      <c r="G9" s="336"/>
-      <c r="H9" s="336"/>
-      <c r="I9" s="336"/>
-      <c r="J9" s="336"/>
-      <c r="K9" s="336"/>
-      <c r="L9" s="336"/>
+      <c r="C9" s="334"/>
+      <c r="D9" s="334"/>
+      <c r="E9" s="334"/>
+      <c r="F9" s="334"/>
+      <c r="G9" s="334"/>
+      <c r="H9" s="334"/>
+      <c r="I9" s="334"/>
+      <c r="J9" s="334"/>
+      <c r="K9" s="334"/>
+      <c r="L9" s="334"/>
       <c r="M9" s="288" t="s">
         <v>167</v>
       </c>
       <c r="N9" s="289">
         <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,5)="Press")+(LEFT(Production_Log!$B$3:$B$1000,5)="Print")+(LEFT(Production_Log!$B$3:$B$1000,5)="PLINE"))*Production_Log!$K$3:$K$1000)/60</f>
-        <v>11.666666666666666</v>
+        <v>17.666666666666668</v>
       </c>
       <c r="O9" s="290">
-        <f>IFERROR(N9/$N$12,"")</f>
-        <v>0.15555555555555556</v>
+        <f t="shared" si="0"/>
+        <v>0.18402777777777779</v>
       </c>
       <c r="P9" s="284"/>
       <c r="Q9" s="284"/>
@@ -5976,12 +5976,12 @@
         <v>175</v>
       </c>
       <c r="N10" s="289">
-        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,5)="Press")+(LEFT(Production_Log!$B$3:$B$1000,5)="Print")+(LEFT(Production_Log!$B$3:$B$1000,5)="PLINE"))*Production_Log!$N$3:$N$1000)/60</f>
-        <v>7.5</v>
+        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,5)="Press")+(LEFT(Production_Log!$B$3:$B$1000,5)="Print")+(LEFT(Production_Log!$B$3:$B$1000,5)="PLINE"))*Production_Log!$S$3:$S$1000)/60</f>
+        <v>12</v>
       </c>
       <c r="O10" s="290">
-        <f>IFERROR(N10/$N$12,"")</f>
-        <v>0.1</v>
+        <f t="shared" si="0"/>
+        <v>0.125</v>
       </c>
       <c r="P10" s="284"/>
       <c r="Q10" s="284"/>
@@ -6024,11 +6024,11 @@
         <v>0</v>
       </c>
       <c r="I11" s="296">
-        <f t="shared" ref="I11:I17" si="0">G11-H11</f>
+        <f t="shared" ref="I11:I17" si="1">G11-H11</f>
         <v>22000</v>
       </c>
       <c r="J11" s="298">
-        <f t="shared" ref="J11:J42" si="1">IF(G11=0,"-",H11/G11)</f>
+        <f t="shared" ref="J11:J42" si="2">IF(G11=0,"-",H11/G11)</f>
         <v>0</v>
       </c>
       <c r="K11" s="297"/>
@@ -6037,12 +6037,12 @@
         <v>176</v>
       </c>
       <c r="N11" s="289">
-        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,5)="Press")+(LEFT(Production_Log!$B$3:$B$1000,5)="Print")+(LEFT(Production_Log!$B$3:$B$1000,5)="PLINE"))*Production_Log!$O$3:$O$1000)/60</f>
-        <v>5</v>
+        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,5)="Press")+(LEFT(Production_Log!$B$3:$B$1000,5)="Print")+(LEFT(Production_Log!$B$3:$B$1000,5)="PLINE"))*Production_Log!$N$3:$N$1000)/60</f>
+        <v>7.5</v>
       </c>
       <c r="O11" s="290">
-        <f>IFERROR(N11/$N$12,"")</f>
-        <v>6.6666666666666666E-2</v>
+        <f t="shared" si="0"/>
+        <v>7.8125E-2</v>
       </c>
       <c r="P11" s="284"/>
       <c r="Q11" s="284"/>
@@ -6085,26 +6085,27 @@
         <v>41664</v>
       </c>
       <c r="I12" s="296">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-1664</v>
       </c>
       <c r="J12" s="298">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0416000000000001</v>
       </c>
       <c r="K12" s="297">
         <v>40656</v>
       </c>
       <c r="L12" s="299"/>
-      <c r="M12" s="301" t="s">
+      <c r="M12" s="288" t="s">
         <v>177</v>
       </c>
-      <c r="N12" s="302">
-        <f>SUM(N7:N11)</f>
-        <v>75</v>
-      </c>
-      <c r="O12" s="303" t="s">
-        <v>178</v>
+      <c r="N12" s="289">
+        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,5)="Press")+(LEFT(Production_Log!$B$3:$B$1000,5)="Print")+(LEFT(Production_Log!$B$3:$B$1000,5)="PLINE"))*Production_Log!$O$3:$O$1000)/60</f>
+        <v>5</v>
+      </c>
+      <c r="O12" s="290">
+        <f t="shared" si="0"/>
+        <v>5.2083333333333336E-2</v>
       </c>
       <c r="P12" s="284"/>
       <c r="Q12" s="284"/>
@@ -6147,20 +6148,27 @@
         <v>21840</v>
       </c>
       <c r="I13" s="296">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-1840</v>
       </c>
       <c r="J13" s="298">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0920000000000001</v>
       </c>
       <c r="K13" s="297">
         <v>20769</v>
       </c>
       <c r="L13" s="299"/>
-      <c r="M13" s="304"/>
-      <c r="N13" s="300"/>
-      <c r="O13" s="300"/>
+      <c r="M13" s="301" t="s">
+        <v>178</v>
+      </c>
+      <c r="N13" s="302">
+        <f>SUM(N7:N12)</f>
+        <v>96</v>
+      </c>
+      <c r="O13" s="303" t="s">
+        <v>179</v>
+      </c>
       <c r="P13" s="284"/>
       <c r="Q13" s="284"/>
       <c r="R13" s="285"/>
@@ -6202,22 +6210,20 @@
         <v>17612</v>
       </c>
       <c r="I14" s="296">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>50000</v>
       </c>
       <c r="J14" s="298">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.26048630420635388</v>
       </c>
       <c r="K14" s="297">
         <v>25754</v>
       </c>
       <c r="L14" s="299"/>
-      <c r="M14" s="321" t="s">
-        <v>179</v>
-      </c>
-      <c r="N14" s="322"/>
-      <c r="O14" s="322"/>
+      <c r="M14" s="304"/>
+      <c r="N14" s="300"/>
+      <c r="O14" s="300"/>
       <c r="P14" s="284"/>
       <c r="Q14" s="284"/>
       <c r="R14" s="284"/>
@@ -6233,7 +6239,7 @@
       <c r="AB14" s="89"/>
       <c r="AC14" s="89"/>
     </row>
-    <row r="15" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="292" t="s">
         <v>154</v>
       </c>
@@ -6255,29 +6261,25 @@
       </c>
       <c r="H15" s="297">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$1000=F15)*((LEFT(Production_Log!$B$3:$B$1000,5)="Print")+(LEFT(Production_Log!$B$3:$B$1000,5)="PLINE"))*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$1000)))*Production_Log!$H$3:$H$1000)</f>
-        <v>198008</v>
+        <v>310582</v>
       </c>
       <c r="I15" s="296">
-        <f t="shared" si="0"/>
-        <v>501992</v>
+        <f t="shared" si="1"/>
+        <v>389418</v>
       </c>
       <c r="J15" s="298">
-        <f t="shared" si="1"/>
-        <v>0.28286857142857141</v>
+        <f t="shared" si="2"/>
+        <v>0.44368857142857143</v>
       </c>
       <c r="K15" s="297">
         <v>303212</v>
       </c>
       <c r="L15" s="299"/>
-      <c r="M15" s="305" t="s">
-        <v>26</v>
-      </c>
-      <c r="N15" s="306" t="s">
-        <v>159</v>
-      </c>
-      <c r="O15" s="307" t="s">
-        <v>160</v>
-      </c>
+      <c r="M15" s="335" t="s">
+        <v>180</v>
+      </c>
+      <c r="N15" s="336"/>
+      <c r="O15" s="336"/>
       <c r="P15" s="300"/>
       <c r="Q15" s="300"/>
       <c r="R15" s="300"/>
@@ -6312,27 +6314,25 @@
         <v>27664</v>
       </c>
       <c r="I16" s="296">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>172336</v>
       </c>
       <c r="J16" s="298">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.13832</v>
       </c>
       <c r="K16" s="297">
         <v>26416</v>
       </c>
       <c r="L16" s="299"/>
-      <c r="M16" s="288" t="s">
-        <v>180</v>
-      </c>
-      <c r="N16" s="289">
-        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,2)="PF")+(LEFT(Production_Log!$B$3:$B$1000,3)="PET"))*Production_Log!$L$3:$L$1000)/60</f>
-        <v>52.833333333333336</v>
-      </c>
-      <c r="O16" s="290">
-        <f t="shared" ref="O16:O21" si="2">IFERROR(N16/$N$22,"")</f>
-        <v>0.3192346424974824</v>
+      <c r="M16" s="305" t="s">
+        <v>26</v>
+      </c>
+      <c r="N16" s="306" t="s">
+        <v>159</v>
+      </c>
+      <c r="O16" s="307" t="s">
+        <v>160</v>
       </c>
       <c r="P16" s="284"/>
       <c r="Q16" s="284"/>
@@ -6375,11 +6375,11 @@
         <v>0</v>
       </c>
       <c r="I17" s="296">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J17" s="298" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="K17" s="297">
@@ -6387,15 +6387,15 @@
       </c>
       <c r="L17" s="299"/>
       <c r="M17" s="288" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="N17" s="289">
-        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,2)="PF")+(LEFT(Production_Log!$B$3:$B$1000,3)="PET"))*Production_Log!$K$3:$K$1000)/60</f>
-        <v>31.833333333333332</v>
+        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,2)="PF")+(LEFT(Production_Log!$B$3:$B$1000,3)="PET"))*Production_Log!$L$3:$L$1000)/60</f>
+        <v>59.5</v>
       </c>
       <c r="O17" s="290">
-        <f t="shared" si="2"/>
-        <v>0.19234642497482377</v>
+        <f t="shared" ref="O17:O22" si="3">IFERROR(N17/$N$23,"")</f>
+        <v>0.30126582278481012</v>
       </c>
       <c r="P17" s="284"/>
       <c r="Q17" s="284"/>
@@ -6417,7 +6417,7 @@
       <c r="B18" s="308"/>
       <c r="C18" s="309"/>
       <c r="D18" s="310" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E18" s="308"/>
       <c r="F18" s="309"/>
@@ -6427,15 +6427,15 @@
       </c>
       <c r="H18" s="311">
         <f>SUM(H11:H17)</f>
-        <v>306788</v>
+        <v>419362</v>
       </c>
       <c r="I18" s="311">
         <f>SUMIF(I11:I17,"&gt;"&amp;0)</f>
-        <v>746328</v>
+        <v>633754</v>
       </c>
       <c r="J18" s="312">
-        <f t="shared" si="1"/>
-        <v>0.29228705464495452</v>
+        <f t="shared" si="2"/>
+        <v>0.3995400205028144</v>
       </c>
       <c r="K18" s="311">
         <f>SUM(K11:K17)</f>
@@ -6443,15 +6443,15 @@
       </c>
       <c r="L18" s="311"/>
       <c r="M18" s="288" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="N18" s="289">
-        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,2)="PF")+(LEFT(Production_Log!$B$3:$B$1000,3)="PET"))*Production_Log!$P$3:$P$1000)/60</f>
-        <v>21.833333333333332</v>
+        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,2)="PF")+(LEFT(Production_Log!$B$3:$B$1000,3)="PET"))*Production_Log!$K$3:$K$1000)/60</f>
+        <v>34.666666666666664</v>
       </c>
       <c r="O18" s="290">
-        <f t="shared" si="2"/>
-        <v>0.13192346424974824</v>
+        <f t="shared" si="3"/>
+        <v>0.17552742616033754</v>
       </c>
       <c r="P18" s="284"/>
       <c r="Q18" s="284"/>
@@ -6494,25 +6494,25 @@
         <v>0</v>
       </c>
       <c r="I19" s="296">
-        <f t="shared" ref="I19:I24" si="3">G19-H19</f>
+        <f t="shared" ref="I19:I25" si="4">G19-H19</f>
         <v>25000</v>
       </c>
       <c r="J19" s="298">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K19" s="297"/>
       <c r="L19" s="299"/>
       <c r="M19" s="288" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="N19" s="289">
-        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,2)="PF")+(LEFT(Production_Log!$B$3:$B$1000,3)="PET"))*Production_Log!$S$3:$S$1000)/60</f>
-        <v>21</v>
+        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,2)="PF")+(LEFT(Production_Log!$B$3:$B$1000,3)="PET"))*Production_Log!$N$3:$N$1000)/60</f>
+        <v>29.666666666666668</v>
       </c>
       <c r="O19" s="290">
-        <f t="shared" si="2"/>
-        <v>0.12688821752265861</v>
+        <f t="shared" si="3"/>
+        <v>0.15021097046413504</v>
       </c>
       <c r="P19" s="284"/>
       <c r="Q19" s="284"/>
@@ -6552,15 +6552,15 @@
       </c>
       <c r="H20" s="297">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$1000=F20)*Production_Log!$H$3:$H$1000)</f>
-        <v>36840</v>
+        <v>64920</v>
       </c>
       <c r="I20" s="296">
-        <f t="shared" si="3"/>
-        <v>23320</v>
+        <f t="shared" si="4"/>
+        <v>-4760</v>
       </c>
       <c r="J20" s="298">
-        <f t="shared" si="1"/>
-        <v>0.6123670212765957</v>
+        <f t="shared" si="2"/>
+        <v>1.0791223404255319</v>
       </c>
       <c r="K20" s="297">
         <v>52080</v>
@@ -6570,12 +6570,12 @@
         <v>175</v>
       </c>
       <c r="N20" s="289">
-        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,2)="PF")+(LEFT(Production_Log!$B$3:$B$1000,3)="PET"))*Production_Log!$N$3:$N$1000)/60</f>
-        <v>19.166666666666668</v>
+        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,2)="PF")+(LEFT(Production_Log!$B$3:$B$1000,3)="PET"))*Production_Log!$S$3:$S$1000)/60</f>
+        <v>29</v>
       </c>
       <c r="O20" s="290">
-        <f t="shared" si="2"/>
-        <v>0.11581067472306143</v>
+        <f t="shared" si="3"/>
+        <v>0.14683544303797469</v>
       </c>
       <c r="P20" s="284"/>
       <c r="Q20" s="284"/>
@@ -6618,25 +6618,25 @@
         <v>0</v>
       </c>
       <c r="I21" s="296">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9480</v>
       </c>
       <c r="J21" s="298">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K21" s="297"/>
       <c r="L21" s="299"/>
       <c r="M21" s="288" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N21" s="289">
         <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,2)="PF")+(LEFT(Production_Log!$B$3:$B$1000,3)="PET"))*Production_Log!$O$3:$O$1000)/60</f>
-        <v>18.833333333333332</v>
+        <v>22.833333333333332</v>
       </c>
       <c r="O21" s="290">
-        <f t="shared" si="2"/>
-        <v>0.11379657603222557</v>
+        <f t="shared" si="3"/>
+        <v>0.11561181434599156</v>
       </c>
       <c r="P21" s="284"/>
       <c r="Q21" s="284"/>
@@ -6659,46 +6659,45 @@
         <v>161</v>
       </c>
       <c r="C22" s="293" t="s">
-        <v>135</v>
+        <v>11</v>
       </c>
       <c r="D22" s="294" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E22" s="295" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F22" s="296">
-        <v>8001</v>
+        <v>8010</v>
       </c>
       <c r="G22" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F22,MRP!$D$3:$D$150,0)),0)</f>
-        <v>753187</v>
+        <v>0</v>
       </c>
       <c r="H22" s="297">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$1000=F22)*Production_Log!$H$3:$H$1000)</f>
-        <v>203220</v>
+        <v>11500</v>
       </c>
       <c r="I22" s="296">
+        <f t="shared" si="4"/>
+        <v>-11500</v>
+      </c>
+      <c r="J22" s="298" t="str">
+        <f t="shared" si="2"/>
+        <v>-</v>
+      </c>
+      <c r="K22" s="297"/>
+      <c r="L22" s="299"/>
+      <c r="M22" s="288" t="s">
+        <v>185</v>
+      </c>
+      <c r="N22" s="289">
+        <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$1000,2)="PF")+(LEFT(Production_Log!$B$3:$B$1000,3)="PET"))*Production_Log!$P$3:$P$1000)/60</f>
+        <v>21.833333333333332</v>
+      </c>
+      <c r="O22" s="290">
         <f t="shared" si="3"/>
-        <v>549967</v>
-      </c>
-      <c r="J22" s="298">
-        <f t="shared" si="1"/>
-        <v>0.26981347261702604</v>
-      </c>
-      <c r="K22" s="297">
-        <v>190440</v>
-      </c>
-      <c r="L22" s="299"/>
-      <c r="M22" s="301" t="s">
-        <v>177</v>
-      </c>
-      <c r="N22" s="302">
-        <f>SUM(N16:N21)</f>
-        <v>165.5</v>
-      </c>
-      <c r="O22" s="303" t="s">
-        <v>178</v>
+        <v>0.11054852320675104</v>
       </c>
       <c r="P22" s="284"/>
       <c r="Q22" s="284"/>
@@ -6714,40 +6713,47 @@
         <v>161</v>
       </c>
       <c r="C23" s="293" t="s">
+        <v>135</v>
+      </c>
+      <c r="D23" s="294" t="s">
         <v>186</v>
-      </c>
-      <c r="D23" s="294" t="s">
-        <v>144</v>
       </c>
       <c r="E23" s="295" t="s">
         <v>143</v>
       </c>
       <c r="F23" s="296">
-        <v>8017</v>
+        <v>8001</v>
       </c>
       <c r="G23" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F23,MRP!$D$3:$D$150,0)),0)</f>
-        <v>0</v>
+        <v>753187</v>
       </c>
       <c r="H23" s="297">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$1000=F23)*Production_Log!$H$3:$H$1000)</f>
-        <v>0</v>
+        <v>203220</v>
       </c>
       <c r="I23" s="296">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="298" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+        <f t="shared" si="4"/>
+        <v>549967</v>
+      </c>
+      <c r="J23" s="298">
+        <f t="shared" si="2"/>
+        <v>0.26981347261702604</v>
       </c>
       <c r="K23" s="297">
-        <v>160</v>
+        <v>190440</v>
       </c>
       <c r="L23" s="299"/>
-      <c r="M23" s="314"/>
-      <c r="N23" s="315"/>
-      <c r="O23" s="316"/>
+      <c r="M23" s="301" t="s">
+        <v>178</v>
+      </c>
+      <c r="N23" s="302">
+        <f>SUM(N17:N22)</f>
+        <v>197.5</v>
+      </c>
+      <c r="O23" s="303" t="s">
+        <v>179</v>
+      </c>
       <c r="P23" s="284"/>
       <c r="Q23" s="284"/>
       <c r="R23" s="284"/>
@@ -6769,35 +6775,35 @@
         <v>161</v>
       </c>
       <c r="C24" s="293" t="s">
-        <v>13</v>
+        <v>187</v>
       </c>
       <c r="D24" s="294" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E24" s="295" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F24" s="296">
-        <v>8006</v>
+        <v>8017</v>
       </c>
       <c r="G24" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F24,MRP!$D$3:$D$150,0)),0)</f>
-        <v>47000</v>
+        <v>0</v>
       </c>
       <c r="H24" s="297">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$1000=F24)*Production_Log!$H$3:$H$1000)</f>
-        <v>27120</v>
+        <v>0</v>
       </c>
       <c r="I24" s="296">
-        <f t="shared" si="3"/>
-        <v>19880</v>
-      </c>
-      <c r="J24" s="298">
-        <f t="shared" si="1"/>
-        <v>0.57702127659574465</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="298" t="str">
+        <f t="shared" si="2"/>
+        <v>-</v>
       </c>
       <c r="K24" s="297">
-        <v>42720</v>
+        <v>160</v>
       </c>
       <c r="L24" s="299"/>
       <c r="M24" s="314"/>
@@ -6820,34 +6826,41 @@
     </row>
     <row r="25" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="87"/>
-      <c r="B25" s="308"/>
-      <c r="C25" s="309"/>
-      <c r="D25" s="310" t="s">
-        <v>177</v>
-      </c>
-      <c r="E25" s="308"/>
-      <c r="F25" s="309"/>
-      <c r="G25" s="311">
-        <f>SUM(G19:G24)</f>
-        <v>894827</v>
-      </c>
-      <c r="H25" s="311">
-        <f>SUM(H19:H24)</f>
-        <v>267180</v>
-      </c>
-      <c r="I25" s="311">
-        <f>SUMIF(I19:I24,"&gt;"&amp;0)</f>
-        <v>627647</v>
-      </c>
-      <c r="J25" s="312">
-        <f t="shared" si="1"/>
-        <v>0.29858285456294903</v>
-      </c>
-      <c r="K25" s="311">
-        <f>SUM(K19:K24)</f>
-        <v>285400</v>
-      </c>
-      <c r="L25" s="311"/>
+      <c r="B25" s="292" t="s">
+        <v>161</v>
+      </c>
+      <c r="C25" s="293" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="294" t="s">
+        <v>147</v>
+      </c>
+      <c r="E25" s="295" t="s">
+        <v>146</v>
+      </c>
+      <c r="F25" s="296">
+        <v>8006</v>
+      </c>
+      <c r="G25" s="296">
+        <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F25,MRP!$D$3:$D$150,0)),0)</f>
+        <v>47000</v>
+      </c>
+      <c r="H25" s="297">
+        <f>SUMPRODUCT((Production_Log!$F$3:$F$1000=F25)*Production_Log!$H$3:$H$1000)</f>
+        <v>42720</v>
+      </c>
+      <c r="I25" s="296">
+        <f t="shared" si="4"/>
+        <v>4280</v>
+      </c>
+      <c r="J25" s="298">
+        <f t="shared" si="2"/>
+        <v>0.90893617021276596</v>
+      </c>
+      <c r="K25" s="297">
+        <v>42720</v>
+      </c>
+      <c r="L25" s="299"/>
       <c r="M25" s="314"/>
       <c r="N25" s="315"/>
       <c r="O25" s="316"/>
@@ -6868,39 +6881,34 @@
     </row>
     <row r="26" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="133"/>
-      <c r="B26" s="292" t="s">
-        <v>154</v>
-      </c>
-      <c r="C26" s="293" t="s">
-        <v>187</v>
-      </c>
-      <c r="D26" s="294" t="s">
-        <v>188</v>
-      </c>
-      <c r="E26" s="295">
-        <v>12.5</v>
-      </c>
-      <c r="F26" s="296">
-        <v>9004</v>
-      </c>
-      <c r="G26" s="296">
-        <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F26,MRP!$D$3:$D$150,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="297">
-        <f>SUMPRODUCT((Production_Log!$F$3:$F$1000=F26)*((LEFT(Production_Log!$B$3:$B$1000,5)="Print")+(LEFT(Production_Log!$B$3:$B$1000,5)="PLINE"))*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$1000)))*Production_Log!$H$3:$H$1000)</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="296">
-        <f t="shared" ref="I26:I67" si="4">G26-H26</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="298" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="K26" s="297"/>
-      <c r="L26" s="299"/>
+      <c r="B26" s="308"/>
+      <c r="C26" s="309"/>
+      <c r="D26" s="310" t="s">
+        <v>178</v>
+      </c>
+      <c r="E26" s="308"/>
+      <c r="F26" s="309"/>
+      <c r="G26" s="311">
+        <f>SUM(G19:G25)</f>
+        <v>894827</v>
+      </c>
+      <c r="H26" s="311">
+        <f>SUM(H19:H25)</f>
+        <v>322360</v>
+      </c>
+      <c r="I26" s="311">
+        <f>SUMIF(I19:I25,"&gt;"&amp;0)</f>
+        <v>588727</v>
+      </c>
+      <c r="J26" s="312">
+        <f t="shared" si="2"/>
+        <v>0.36024840555772231</v>
+      </c>
+      <c r="K26" s="311">
+        <f>SUM(K19:K25)</f>
+        <v>285400</v>
+      </c>
+      <c r="L26" s="311"/>
       <c r="M26" s="314"/>
       <c r="N26" s="315"/>
       <c r="O26" s="316"/>
@@ -6925,16 +6933,16 @@
         <v>154</v>
       </c>
       <c r="C27" s="293" t="s">
+        <v>188</v>
+      </c>
+      <c r="D27" s="294" t="s">
         <v>189</v>
       </c>
-      <c r="D27" s="294" t="s">
-        <v>190</v>
-      </c>
       <c r="E27" s="295">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="F27" s="296">
-        <v>6561</v>
+        <v>9004</v>
       </c>
       <c r="G27" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F27,MRP!$D$3:$D$150,0)),0)</f>
@@ -6945,11 +6953,11 @@
         <v>0</v>
       </c>
       <c r="I27" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I27:I67" si="5">G27-H27</f>
         <v>0</v>
       </c>
       <c r="J27" s="298" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="K27" s="297"/>
@@ -6978,16 +6986,16 @@
         <v>154</v>
       </c>
       <c r="C28" s="293" t="s">
-        <v>13</v>
+        <v>190</v>
       </c>
       <c r="D28" s="294" t="s">
         <v>191</v>
       </c>
       <c r="E28" s="295">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F28" s="296">
-        <v>6624</v>
+        <v>6561</v>
       </c>
       <c r="G28" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F28,MRP!$D$3:$D$150,0)),0)</f>
@@ -6998,11 +7006,11 @@
         <v>0</v>
       </c>
       <c r="I28" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J28" s="298" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="K28" s="297"/>
@@ -7040,7 +7048,7 @@
         <v>19</v>
       </c>
       <c r="F29" s="296">
-        <v>6623</v>
+        <v>6624</v>
       </c>
       <c r="G29" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F29,MRP!$D$3:$D$150,0)),0)</f>
@@ -7051,11 +7059,11 @@
         <v>0</v>
       </c>
       <c r="I29" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J29" s="298" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="K29" s="297"/>
@@ -7084,16 +7092,16 @@
         <v>154</v>
       </c>
       <c r="C30" s="293" t="s">
-        <v>189</v>
+        <v>13</v>
       </c>
       <c r="D30" s="294" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E30" s="295">
         <v>19</v>
       </c>
       <c r="F30" s="296">
-        <v>6559</v>
+        <v>6623</v>
       </c>
       <c r="G30" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F30,MRP!$D$3:$D$150,0)),0)</f>
@@ -7104,11 +7112,11 @@
         <v>0</v>
       </c>
       <c r="I30" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J30" s="298" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="K30" s="297"/>
@@ -7137,7 +7145,7 @@
         <v>154</v>
       </c>
       <c r="C31" s="293" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D31" s="294" t="s">
         <v>193</v>
@@ -7146,7 +7154,7 @@
         <v>19</v>
       </c>
       <c r="F31" s="296">
-        <v>1085</v>
+        <v>6559</v>
       </c>
       <c r="G31" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F31,MRP!$D$3:$D$150,0)),0)</f>
@@ -7157,11 +7165,11 @@
         <v>0</v>
       </c>
       <c r="I31" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J31" s="298" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="K31" s="297"/>
@@ -7190,7 +7198,7 @@
         <v>154</v>
       </c>
       <c r="C32" s="293" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D32" s="294" t="s">
         <v>194</v>
@@ -7199,7 +7207,7 @@
         <v>19</v>
       </c>
       <c r="F32" s="296">
-        <v>6560</v>
+        <v>1085</v>
       </c>
       <c r="G32" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F32,MRP!$D$3:$D$150,0)),0)</f>
@@ -7210,11 +7218,11 @@
         <v>0</v>
       </c>
       <c r="I32" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J32" s="298" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="K32" s="297"/>
@@ -7243,16 +7251,16 @@
         <v>154</v>
       </c>
       <c r="C33" s="293" t="s">
-        <v>13</v>
+        <v>190</v>
       </c>
       <c r="D33" s="294" t="s">
         <v>195</v>
       </c>
       <c r="E33" s="295">
-        <v>20.5</v>
+        <v>19</v>
       </c>
       <c r="F33" s="296">
-        <v>5699</v>
+        <v>6560</v>
       </c>
       <c r="G33" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F33,MRP!$D$3:$D$150,0)),0)</f>
@@ -7263,11 +7271,11 @@
         <v>0</v>
       </c>
       <c r="I33" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J33" s="298" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="K33" s="297"/>
@@ -7305,7 +7313,7 @@
         <v>20.5</v>
       </c>
       <c r="F34" s="296">
-        <v>5731</v>
+        <v>5699</v>
       </c>
       <c r="G34" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F34,MRP!$D$3:$D$150,0)),0)</f>
@@ -7316,11 +7324,11 @@
         <v>0</v>
       </c>
       <c r="I34" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J34" s="298" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="K34" s="297"/>
@@ -7358,7 +7366,7 @@
         <v>20.5</v>
       </c>
       <c r="F35" s="296">
-        <v>5698</v>
+        <v>5731</v>
       </c>
       <c r="G35" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F35,MRP!$D$3:$D$150,0)),0)</f>
@@ -7369,11 +7377,11 @@
         <v>0</v>
       </c>
       <c r="I35" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J35" s="298" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="K35" s="297"/>
@@ -7411,7 +7419,7 @@
         <v>20.5</v>
       </c>
       <c r="F36" s="296">
-        <v>5732</v>
+        <v>5698</v>
       </c>
       <c r="G36" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F36,MRP!$D$3:$D$150,0)),0)</f>
@@ -7422,11 +7430,11 @@
         <v>0</v>
       </c>
       <c r="I36" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J36" s="298" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="K36" s="297"/>
@@ -7464,7 +7472,7 @@
         <v>20.5</v>
       </c>
       <c r="F37" s="296">
-        <v>6556</v>
+        <v>5732</v>
       </c>
       <c r="G37" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F37,MRP!$D$3:$D$150,0)),0)</f>
@@ -7475,11 +7483,11 @@
         <v>0</v>
       </c>
       <c r="I37" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J37" s="298" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="K37" s="297"/>
@@ -7517,7 +7525,7 @@
         <v>20.5</v>
       </c>
       <c r="F38" s="296">
-        <v>6557</v>
+        <v>6556</v>
       </c>
       <c r="G38" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F38,MRP!$D$3:$D$150,0)),0)</f>
@@ -7528,11 +7536,11 @@
         <v>0</v>
       </c>
       <c r="I38" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J38" s="298" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="K38" s="297"/>
@@ -7567,10 +7575,10 @@
         <v>201</v>
       </c>
       <c r="E39" s="295">
-        <v>25</v>
+        <v>20.5</v>
       </c>
       <c r="F39" s="296">
-        <v>5389</v>
+        <v>6557</v>
       </c>
       <c r="G39" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F39,MRP!$D$3:$D$150,0)),0)</f>
@@ -7581,11 +7589,11 @@
         <v>0</v>
       </c>
       <c r="I39" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J39" s="298" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="K39" s="297"/>
@@ -7623,7 +7631,7 @@
         <v>25</v>
       </c>
       <c r="F40" s="296">
-        <v>3447</v>
+        <v>5389</v>
       </c>
       <c r="G40" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F40,MRP!$D$3:$D$150,0)),0)</f>
@@ -7634,11 +7642,11 @@
         <v>0</v>
       </c>
       <c r="I40" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J40" s="298" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="K40" s="297"/>
@@ -7676,7 +7684,7 @@
         <v>25</v>
       </c>
       <c r="F41" s="296">
-        <v>3726</v>
+        <v>3447</v>
       </c>
       <c r="G41" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F41,MRP!$D$3:$D$150,0)),0)</f>
@@ -7687,11 +7695,11 @@
         <v>0</v>
       </c>
       <c r="I41" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J41" s="298" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="K41" s="297"/>
@@ -7729,7 +7737,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="296">
-        <v>6532</v>
+        <v>3726</v>
       </c>
       <c r="G42" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F42,MRP!$D$3:$D$150,0)),0)</f>
@@ -7740,11 +7748,11 @@
         <v>0</v>
       </c>
       <c r="I42" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J42" s="298" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="K42" s="297"/>
@@ -7782,7 +7790,7 @@
         <v>25</v>
       </c>
       <c r="F43" s="296">
-        <v>6506</v>
+        <v>6532</v>
       </c>
       <c r="G43" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F43,MRP!$D$3:$D$150,0)),0)</f>
@@ -7793,11 +7801,11 @@
         <v>0</v>
       </c>
       <c r="I43" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J43" s="298" t="str">
-        <f t="shared" ref="J43:J67" si="5">IF(G43=0,"-",H43/G43)</f>
+        <f t="shared" ref="J43:J67" si="6">IF(G43=0,"-",H43/G43)</f>
         <v>-</v>
       </c>
       <c r="K43" s="297"/>
@@ -7835,7 +7843,7 @@
         <v>25</v>
       </c>
       <c r="F44" s="296">
-        <v>9006</v>
+        <v>6506</v>
       </c>
       <c r="G44" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F44,MRP!$D$3:$D$150,0)),0)</f>
@@ -7846,11 +7854,11 @@
         <v>0</v>
       </c>
       <c r="I44" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J44" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K44" s="297"/>
@@ -7879,16 +7887,16 @@
         <v>154</v>
       </c>
       <c r="C45" s="293" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="294" t="s">
         <v>207</v>
-      </c>
-      <c r="D45" s="294" t="s">
-        <v>208</v>
       </c>
       <c r="E45" s="295">
         <v>25</v>
       </c>
       <c r="F45" s="296">
-        <v>6338</v>
+        <v>9006</v>
       </c>
       <c r="G45" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F45,MRP!$D$3:$D$150,0)),0)</f>
@@ -7899,11 +7907,11 @@
         <v>0</v>
       </c>
       <c r="I45" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J45" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K45" s="297"/>
@@ -7932,16 +7940,16 @@
         <v>154</v>
       </c>
       <c r="C46" s="293" t="s">
+        <v>208</v>
+      </c>
+      <c r="D46" s="294" t="s">
         <v>209</v>
-      </c>
-      <c r="D46" s="294" t="s">
-        <v>210</v>
       </c>
       <c r="E46" s="295">
         <v>25</v>
       </c>
       <c r="F46" s="296">
-        <v>4227</v>
+        <v>6338</v>
       </c>
       <c r="G46" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F46,MRP!$D$3:$D$150,0)),0)</f>
@@ -7952,11 +7960,11 @@
         <v>0</v>
       </c>
       <c r="I46" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J46" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K46" s="297"/>
@@ -7985,16 +7993,16 @@
         <v>154</v>
       </c>
       <c r="C47" s="293" t="s">
+        <v>210</v>
+      </c>
+      <c r="D47" s="294" t="s">
         <v>211</v>
       </c>
-      <c r="D47" s="294" t="s">
-        <v>212</v>
-      </c>
       <c r="E47" s="295">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F47" s="296">
-        <v>6595</v>
+        <v>4227</v>
       </c>
       <c r="G47" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F47,MRP!$D$3:$D$150,0)),0)</f>
@@ -8005,11 +8013,11 @@
         <v>0</v>
       </c>
       <c r="I47" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J47" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K47" s="297"/>
@@ -8038,16 +8046,16 @@
         <v>154</v>
       </c>
       <c r="C48" s="293" t="s">
+        <v>212</v>
+      </c>
+      <c r="D48" s="294" t="s">
         <v>213</v>
-      </c>
-      <c r="D48" s="294" t="s">
-        <v>214</v>
       </c>
       <c r="E48" s="295">
         <v>30</v>
       </c>
       <c r="F48" s="296">
-        <v>4050</v>
+        <v>6595</v>
       </c>
       <c r="G48" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F48,MRP!$D$3:$D$150,0)),0)</f>
@@ -8058,11 +8066,11 @@
         <v>0</v>
       </c>
       <c r="I48" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J48" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K48" s="297"/>
@@ -8091,7 +8099,7 @@
         <v>154</v>
       </c>
       <c r="C49" s="293" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D49" s="294" t="s">
         <v>215</v>
@@ -8100,7 +8108,7 @@
         <v>30</v>
       </c>
       <c r="F49" s="296">
-        <v>6312</v>
+        <v>4050</v>
       </c>
       <c r="G49" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F49,MRP!$D$3:$D$150,0)),0)</f>
@@ -8111,11 +8119,11 @@
         <v>0</v>
       </c>
       <c r="I49" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J49" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K49" s="297"/>
@@ -8144,16 +8152,16 @@
         <v>154</v>
       </c>
       <c r="C50" s="293" t="s">
+        <v>214</v>
+      </c>
+      <c r="D50" s="294" t="s">
         <v>216</v>
-      </c>
-      <c r="D50" s="294" t="s">
-        <v>217</v>
       </c>
       <c r="E50" s="295">
         <v>30</v>
       </c>
       <c r="F50" s="296">
-        <v>6416</v>
+        <v>6312</v>
       </c>
       <c r="G50" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F50,MRP!$D$3:$D$150,0)),0)</f>
@@ -8164,11 +8172,11 @@
         <v>0</v>
       </c>
       <c r="I50" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J50" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K50" s="297"/>
@@ -8197,7 +8205,7 @@
         <v>154</v>
       </c>
       <c r="C51" s="293" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D51" s="294" t="s">
         <v>218</v>
@@ -8206,7 +8214,7 @@
         <v>30</v>
       </c>
       <c r="F51" s="296">
-        <v>6337</v>
+        <v>6416</v>
       </c>
       <c r="G51" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F51,MRP!$D$3:$D$150,0)),0)</f>
@@ -8217,11 +8225,11 @@
         <v>0</v>
       </c>
       <c r="I51" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J51" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K51" s="297"/>
@@ -8250,7 +8258,7 @@
         <v>154</v>
       </c>
       <c r="C52" s="293" t="s">
-        <v>11</v>
+        <v>217</v>
       </c>
       <c r="D52" s="294" t="s">
         <v>219</v>
@@ -8259,7 +8267,7 @@
         <v>30</v>
       </c>
       <c r="F52" s="296">
-        <v>9002</v>
+        <v>6337</v>
       </c>
       <c r="G52" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F52,MRP!$D$3:$D$150,0)),0)</f>
@@ -8270,11 +8278,11 @@
         <v>0</v>
       </c>
       <c r="I52" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J52" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K52" s="297"/>
@@ -8303,7 +8311,7 @@
         <v>154</v>
       </c>
       <c r="C53" s="293" t="s">
-        <v>213</v>
+        <v>11</v>
       </c>
       <c r="D53" s="294" t="s">
         <v>220</v>
@@ -8312,7 +8320,7 @@
         <v>30</v>
       </c>
       <c r="F53" s="296">
-        <v>2909</v>
+        <v>9002</v>
       </c>
       <c r="G53" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F53,MRP!$D$3:$D$150,0)),0)</f>
@@ -8323,11 +8331,11 @@
         <v>0</v>
       </c>
       <c r="I53" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J53" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K53" s="297"/>
@@ -8356,16 +8364,16 @@
         <v>154</v>
       </c>
       <c r="C54" s="293" t="s">
+        <v>214</v>
+      </c>
+      <c r="D54" s="294" t="s">
         <v>221</v>
-      </c>
-      <c r="D54" s="294" t="s">
-        <v>222</v>
       </c>
       <c r="E54" s="295">
         <v>30</v>
       </c>
       <c r="F54" s="296">
-        <v>6151</v>
+        <v>2909</v>
       </c>
       <c r="G54" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F54,MRP!$D$3:$D$150,0)),0)</f>
@@ -8376,11 +8384,11 @@
         <v>0</v>
       </c>
       <c r="I54" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J54" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K54" s="297"/>
@@ -8409,16 +8417,16 @@
         <v>154</v>
       </c>
       <c r="C55" s="293" t="s">
+        <v>222</v>
+      </c>
+      <c r="D55" s="294" t="s">
         <v>223</v>
       </c>
-      <c r="D55" s="294" t="s">
-        <v>224</v>
-      </c>
       <c r="E55" s="295">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F55" s="296">
-        <v>6530</v>
+        <v>6151</v>
       </c>
       <c r="G55" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F55,MRP!$D$3:$D$150,0)),0)</f>
@@ -8429,11 +8437,11 @@
         <v>0</v>
       </c>
       <c r="I55" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J55" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K55" s="297"/>
@@ -8462,7 +8470,7 @@
         <v>154</v>
       </c>
       <c r="C56" s="293" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D56" s="294" t="s">
         <v>225</v>
@@ -8471,7 +8479,7 @@
         <v>35</v>
       </c>
       <c r="F56" s="296">
-        <v>6531</v>
+        <v>6530</v>
       </c>
       <c r="G56" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F56,MRP!$D$3:$D$150,0)),0)</f>
@@ -8482,11 +8490,11 @@
         <v>0</v>
       </c>
       <c r="I56" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J56" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K56" s="297"/>
@@ -8515,7 +8523,7 @@
         <v>154</v>
       </c>
       <c r="C57" s="293" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D57" s="294" t="s">
         <v>226</v>
@@ -8524,7 +8532,7 @@
         <v>35</v>
       </c>
       <c r="F57" s="296">
-        <v>6020</v>
+        <v>6531</v>
       </c>
       <c r="G57" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F57,MRP!$D$3:$D$150,0)),0)</f>
@@ -8535,11 +8543,11 @@
         <v>0</v>
       </c>
       <c r="I57" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J57" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K57" s="297"/>
@@ -8568,7 +8576,7 @@
         <v>154</v>
       </c>
       <c r="C58" s="293" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D58" s="294" t="s">
         <v>227</v>
@@ -8577,7 +8585,7 @@
         <v>35</v>
       </c>
       <c r="F58" s="296">
-        <v>6021</v>
+        <v>6020</v>
       </c>
       <c r="G58" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F58,MRP!$D$3:$D$150,0)),0)</f>
@@ -8588,11 +8596,11 @@
         <v>0</v>
       </c>
       <c r="I58" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J58" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K58" s="297"/>
@@ -8617,34 +8625,34 @@
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.3">
       <c r="B59" s="292" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C59" s="293" t="s">
-        <v>13</v>
+        <v>224</v>
       </c>
       <c r="D59" s="294" t="s">
         <v>228</v>
       </c>
-      <c r="E59" s="295" t="s">
-        <v>138</v>
+      <c r="E59" s="295">
+        <v>35</v>
       </c>
       <c r="F59" s="296">
-        <v>8011</v>
+        <v>6021</v>
       </c>
       <c r="G59" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F59,MRP!$D$3:$D$150,0)),0)</f>
         <v>0</v>
       </c>
       <c r="H59" s="297">
-        <f>SUMPRODUCT((Production_Log!$F$3:$F$1000=F59)*Production_Log!$H$3:$H$1000)</f>
+        <f>SUMPRODUCT((Production_Log!$F$3:$F$1000=F59)*((LEFT(Production_Log!$B$3:$B$1000,5)="Print")+(LEFT(Production_Log!$B$3:$B$1000,5)="PLINE"))*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$1000)))*Production_Log!$H$3:$H$1000)</f>
         <v>0</v>
       </c>
       <c r="I59" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J59" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K59" s="297"/>
@@ -8674,7 +8682,7 @@
         <v>138</v>
       </c>
       <c r="F60" s="296">
-        <v>8012</v>
+        <v>8011</v>
       </c>
       <c r="G60" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F60,MRP!$D$3:$D$150,0)),0)</f>
@@ -8685,11 +8693,11 @@
         <v>0</v>
       </c>
       <c r="I60" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J60" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K60" s="297"/>
@@ -8710,16 +8718,16 @@
         <v>161</v>
       </c>
       <c r="C61" s="293" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D61" s="294" t="s">
         <v>230</v>
       </c>
       <c r="E61" s="295" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F61" s="296">
-        <v>8010</v>
+        <v>8012</v>
       </c>
       <c r="G61" s="296">
         <f>IFERROR(INDEX(MRP!$F$3:$F$150,MATCH(F61,MRP!$D$3:$D$150,0)),0)</f>
@@ -8730,11 +8738,11 @@
         <v>0</v>
       </c>
       <c r="I61" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J61" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K61" s="297"/>
@@ -8765,11 +8773,11 @@
         <v>0</v>
       </c>
       <c r="I62" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J62" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K62" s="297"/>
@@ -8801,11 +8809,11 @@
         <v>0</v>
       </c>
       <c r="I63" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J63" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K63" s="297"/>
@@ -8852,11 +8860,11 @@
         <v>0</v>
       </c>
       <c r="I64" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J64" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K64" s="297"/>
@@ -8902,11 +8910,11 @@
         <v>0</v>
       </c>
       <c r="I65" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J65" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K65" s="297"/>
@@ -8937,11 +8945,11 @@
         <v>0</v>
       </c>
       <c r="I66" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J66" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K66" s="297"/>
@@ -8972,11 +8980,11 @@
         <v>0</v>
       </c>
       <c r="I67" s="296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J67" s="298" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="K67" s="297"/>
@@ -10726,13 +10734,14 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B9:L9"/>
+    <mergeCell ref="M15:O15"/>
     <mergeCell ref="B2:O2"/>
     <mergeCell ref="M5:O5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="J8:K8"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="E8:F8"/>
-    <mergeCell ref="M14:O14"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="E6:F6"/>
@@ -10740,7 +10749,6 @@
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="B9:L9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -10823,7 +10831,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -10919,7 +10927,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="230" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -10951,7 +10959,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -10983,7 +10991,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="230" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -11047,7 +11055,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="230" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -11079,7 +11087,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="230" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -11111,7 +11119,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="230" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -11143,7 +11151,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="230" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -11175,7 +11183,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="230" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -11207,7 +11215,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="230" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -11335,7 +11343,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="230" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -11399,7 +11407,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="230" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -11431,7 +11439,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="230" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -11553,13 +11561,13 @@
         <v>645</v>
       </c>
       <c r="H25" s="230" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I25" s="231">
         <v>60</v>
       </c>
       <c r="J25" s="230" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -11655,7 +11663,7 @@
         <v>60</v>
       </c>
       <c r="J28" s="230" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -11681,7 +11689,7 @@
         <v>645</v>
       </c>
       <c r="H29" s="230" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I29" s="231">
         <v>360</v>
@@ -11751,7 +11759,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="230" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -11815,7 +11823,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="230" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -11873,13 +11881,13 @@
         <v>645</v>
       </c>
       <c r="H35" s="230" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I35" s="231">
         <v>390</v>
       </c>
       <c r="J35" s="230" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -11911,7 +11919,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="230" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -11937,7 +11945,7 @@
         <v>678</v>
       </c>
       <c r="H37" s="230" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I37" s="231">
         <v>210</v>
@@ -11975,7 +11983,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="230" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -12007,7 +12015,7 @@
         <v>90</v>
       </c>
       <c r="J39" s="230" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -12039,7 +12047,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="230" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -12097,7 +12105,7 @@
         <v>645</v>
       </c>
       <c r="H42" s="230" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I42" s="231">
         <v>90</v>
@@ -12135,7 +12143,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="230" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -12167,7 +12175,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="230" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -12231,7 +12239,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="230" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -12295,7 +12303,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="230" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -12359,7 +12367,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="230" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -12423,7 +12431,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="230" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -12487,7 +12495,7 @@
         <v>300</v>
       </c>
       <c r="J54" s="230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -12519,7 +12527,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="230" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -12551,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="J56" s="230" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -12583,7 +12591,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="230" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -12609,7 +12617,7 @@
         <v>645</v>
       </c>
       <c r="H58" s="230" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I58" s="231">
         <v>180</v>
@@ -12647,7 +12655,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="230" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -12711,7 +12719,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="230" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -12737,7 +12745,7 @@
         <v>645</v>
       </c>
       <c r="H62" s="230" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I62" s="231">
         <v>60</v>
@@ -12769,13 +12777,13 @@
         <v>645</v>
       </c>
       <c r="H63" s="230" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I63" s="231">
         <v>120</v>
       </c>
       <c r="J63" s="230" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -12801,7 +12809,7 @@
         <v>645</v>
       </c>
       <c r="H64" s="230" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I64" s="231">
         <v>60</v>
@@ -12839,7 +12847,7 @@
         <v>240</v>
       </c>
       <c r="J65" s="230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -12903,7 +12911,7 @@
         <v>180</v>
       </c>
       <c r="J67" s="230" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -12993,7 +13001,7 @@
         <v>645</v>
       </c>
       <c r="H70" s="230" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I70" s="231">
         <v>120</v>
@@ -13031,7 +13039,7 @@
         <v>0</v>
       </c>
       <c r="J71" s="230" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -13121,7 +13129,7 @@
         <v>645</v>
       </c>
       <c r="H74" s="230" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I74" s="231">
         <v>20</v>
@@ -13319,7 +13327,7 @@
         <v>120</v>
       </c>
       <c r="J80" s="230" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -13377,13 +13385,13 @@
         <v>645</v>
       </c>
       <c r="H82" s="230" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I82" s="231">
         <v>120</v>
       </c>
       <c r="J82" s="230" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -13447,7 +13455,7 @@
         <v>150</v>
       </c>
       <c r="J84" s="230" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -13511,7 +13519,7 @@
         <v>150</v>
       </c>
       <c r="J86" s="230" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -13671,7 +13679,7 @@
         <v>120</v>
       </c>
       <c r="J91" s="230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -13703,7 +13711,7 @@
         <v>0</v>
       </c>
       <c r="J92" s="230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -13729,13 +13737,13 @@
         <v>645</v>
       </c>
       <c r="H93" s="230" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I93" s="231">
         <v>180</v>
       </c>
       <c r="J93" s="230" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -13761,7 +13769,7 @@
         <v>645</v>
       </c>
       <c r="H94" s="230" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I94" s="231">
         <v>300</v>
@@ -13793,13 +13801,13 @@
         <v>645</v>
       </c>
       <c r="H95" s="230" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I95" s="231">
         <v>150</v>
       </c>
       <c r="J95" s="230" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -13831,7 +13839,7 @@
         <v>0</v>
       </c>
       <c r="J96" s="230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -13857,13 +13865,13 @@
         <v>645</v>
       </c>
       <c r="H97" s="230" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I97" s="231">
         <v>240</v>
       </c>
       <c r="J97" s="230" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -13895,7 +13903,7 @@
         <v>0</v>
       </c>
       <c r="J98" s="230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -13927,7 +13935,7 @@
         <v>90</v>
       </c>
       <c r="J99" s="230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -13959,7 +13967,7 @@
         <v>90</v>
       </c>
       <c r="J100" s="230" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -13991,7 +13999,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="230" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -14023,7 +14031,7 @@
         <v>240</v>
       </c>
       <c r="J102" s="230" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -14055,7 +14063,7 @@
         <v>0</v>
       </c>
       <c r="J103" s="230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -14087,7 +14095,7 @@
         <v>120</v>
       </c>
       <c r="J104" s="230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -14119,7 +14127,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -14151,7 +14159,7 @@
         <v>0</v>
       </c>
       <c r="J106" s="230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -14174,10 +14182,10 @@
         <v>300</v>
       </c>
       <c r="G107" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H107" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I107" s="231">
         <v>120</v>
@@ -14206,16 +14214,16 @@
         <v>315</v>
       </c>
       <c r="G108" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H108" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I108" s="231">
         <v>60</v>
       </c>
       <c r="J108" s="230" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -14238,10 +14246,10 @@
         <v>500</v>
       </c>
       <c r="G109" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H109" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I109" s="231">
         <v>60</v>
@@ -14270,10 +14278,10 @@
         <v>500</v>
       </c>
       <c r="G110" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H110" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I110" s="231">
         <v>60</v>
@@ -14302,16 +14310,16 @@
         <v>350</v>
       </c>
       <c r="G111" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H111" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I111" s="231">
         <v>20</v>
       </c>
       <c r="J111" s="230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -14334,10 +14342,10 @@
         <v>395</v>
       </c>
       <c r="G112" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H112" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I112" s="231">
         <v>20</v>
@@ -14375,7 +14383,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="230" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -14430,10 +14438,10 @@
         <v>110</v>
       </c>
       <c r="G115" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H115" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I115" s="231">
         <v>345</v>
@@ -14462,10 +14470,10 @@
         <v>300</v>
       </c>
       <c r="G116" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H116" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I116" s="231">
         <v>345</v>
@@ -14631,7 +14639,7 @@
         <v>0</v>
       </c>
       <c r="J121" s="230" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -14695,7 +14703,7 @@
         <v>0</v>
       </c>
       <c r="J123" s="230" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
@@ -14759,7 +14767,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="230" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
@@ -14823,7 +14831,7 @@
         <v>240</v>
       </c>
       <c r="J127" s="230" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
@@ -14878,16 +14886,16 @@
         <v>330</v>
       </c>
       <c r="G129" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H129" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I129" s="231">
         <v>30</v>
       </c>
       <c r="J129" s="230" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -14910,10 +14918,10 @@
         <v>260</v>
       </c>
       <c r="G130" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H130" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I130" s="231">
         <v>30</v>
@@ -14951,7 +14959,7 @@
         <v>180</v>
       </c>
       <c r="J131" s="230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -15006,10 +15014,10 @@
         <v>700</v>
       </c>
       <c r="G133" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H133" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I133" s="231">
         <v>360</v>
@@ -15038,10 +15046,10 @@
         <v>600</v>
       </c>
       <c r="G134" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H134" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I134" s="231">
         <v>180</v>
@@ -15079,7 +15087,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -15335,7 +15343,7 @@
         <v>120</v>
       </c>
       <c r="J143" s="230" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -15361,7 +15369,7 @@
         <v>645</v>
       </c>
       <c r="H144" s="230" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I144" s="231">
         <v>120</v>
@@ -15399,7 +15407,7 @@
         <v>180</v>
       </c>
       <c r="J145" s="230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -15463,7 +15471,7 @@
         <v>300</v>
       </c>
       <c r="J147" s="230" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -15495,7 +15503,7 @@
         <v>0</v>
       </c>
       <c r="J148" s="230" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
@@ -15617,13 +15625,13 @@
         <v>645</v>
       </c>
       <c r="H152" s="230" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I152" s="231">
         <v>180</v>
       </c>
       <c r="J152" s="230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
@@ -15687,7 +15695,7 @@
         <v>0</v>
       </c>
       <c r="J154" s="230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
@@ -15742,16 +15750,16 @@
         <v>400</v>
       </c>
       <c r="G156" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H156" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I156" s="231">
         <v>30</v>
       </c>
       <c r="J156" s="230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
@@ -15774,10 +15782,10 @@
         <v>395</v>
       </c>
       <c r="G157" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H157" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I157" s="231">
         <v>30</v>
@@ -15815,7 +15823,7 @@
         <v>300</v>
       </c>
       <c r="J158" s="230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
@@ -15905,13 +15913,13 @@
         <v>645</v>
       </c>
       <c r="H161" s="230" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I161" s="231">
         <v>240</v>
       </c>
       <c r="J161" s="230" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
@@ -15934,16 +15942,16 @@
         <v>340</v>
       </c>
       <c r="G162" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H162" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I162" s="231">
         <v>40</v>
       </c>
       <c r="J162" s="230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
@@ -15966,10 +15974,10 @@
         <v>395</v>
       </c>
       <c r="G163" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H163" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I163" s="231">
         <v>40</v>
@@ -16161,7 +16169,7 @@
         <v>645</v>
       </c>
       <c r="H169" s="230" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I169" s="231">
         <v>180</v>
@@ -16295,7 +16303,7 @@
         <v>240</v>
       </c>
       <c r="J173" s="230" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
@@ -16487,7 +16495,7 @@
         <v>240</v>
       </c>
       <c r="J179" s="230" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
@@ -16615,7 +16623,7 @@
         <v>150</v>
       </c>
       <c r="J183" s="230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
@@ -16670,10 +16678,10 @@
         <v>160</v>
       </c>
       <c r="G185" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H185" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I185" s="231">
         <v>240</v>
@@ -16702,10 +16710,10 @@
         <v>210</v>
       </c>
       <c r="G186" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H186" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I186" s="231">
         <v>120</v>
@@ -16743,7 +16751,7 @@
         <v>180</v>
       </c>
       <c r="J187" s="230" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
@@ -16798,16 +16806,16 @@
         <v>155</v>
       </c>
       <c r="G189" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H189" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I189" s="231">
         <v>60</v>
       </c>
       <c r="J189" s="230" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
@@ -16926,10 +16934,10 @@
         <v>415</v>
       </c>
       <c r="G193" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H193" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I193" s="231">
         <v>160</v>
@@ -16958,16 +16966,16 @@
         <v>350</v>
       </c>
       <c r="G194" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H194" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I194" s="231">
         <v>180</v>
       </c>
       <c r="J194" s="230" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
@@ -17022,16 +17030,16 @@
         <v>550</v>
       </c>
       <c r="G196" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H196" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I196" s="231">
         <v>30</v>
       </c>
       <c r="J196" s="230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
@@ -17054,16 +17062,16 @@
         <v>365</v>
       </c>
       <c r="G197" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H197" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I197" s="231">
         <v>30</v>
       </c>
       <c r="J197" s="230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
@@ -17191,7 +17199,7 @@
         <v>100</v>
       </c>
       <c r="J201" s="230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
@@ -17255,7 +17263,7 @@
         <v>60</v>
       </c>
       <c r="J203" s="230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
@@ -17287,7 +17295,7 @@
         <v>360</v>
       </c>
       <c r="J204" s="230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
@@ -17319,7 +17327,7 @@
         <v>0</v>
       </c>
       <c r="J205" s="230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
@@ -17374,10 +17382,10 @@
         <v>470</v>
       </c>
       <c r="G207" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H207" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I207" s="231">
         <v>30</v>
@@ -17441,7 +17449,7 @@
         <v>645</v>
       </c>
       <c r="H209" s="230" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I209" s="231">
         <v>180</v>
@@ -17473,7 +17481,7 @@
         <v>645</v>
       </c>
       <c r="H210" s="230" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I210" s="231">
         <v>60</v>
@@ -17537,13 +17545,13 @@
         <v>645</v>
       </c>
       <c r="H212" s="230" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I212" s="231">
         <v>240</v>
       </c>
       <c r="J212" s="230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
@@ -17665,13 +17673,13 @@
         <v>645</v>
       </c>
       <c r="H216" s="230" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I216" s="231">
         <v>180</v>
       </c>
       <c r="J216" s="230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
@@ -17735,7 +17743,7 @@
         <v>0</v>
       </c>
       <c r="J218" s="230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
@@ -17761,13 +17769,13 @@
         <v>645</v>
       </c>
       <c r="H219" s="230" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I219" s="231">
         <v>120</v>
       </c>
       <c r="J219" s="230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
@@ -17793,13 +17801,13 @@
         <v>645</v>
       </c>
       <c r="H220" s="230" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I220" s="231">
         <v>60</v>
       </c>
       <c r="J220" s="230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
@@ -17831,7 +17839,7 @@
         <v>60</v>
       </c>
       <c r="J221" s="230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
@@ -18087,7 +18095,7 @@
         <v>0</v>
       </c>
       <c r="J229" s="230" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
@@ -18113,7 +18121,7 @@
         <v>645</v>
       </c>
       <c r="H230" s="230" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I230" s="231">
         <v>180</v>
@@ -18215,7 +18223,7 @@
         <v>45</v>
       </c>
       <c r="J233" s="230" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
@@ -18247,7 +18255,7 @@
         <v>0</v>
       </c>
       <c r="J234" s="230" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
@@ -18270,10 +18278,10 @@
         <v>350</v>
       </c>
       <c r="G235" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H235" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I235" s="231">
         <v>60</v>
@@ -18375,7 +18383,7 @@
         <v>0</v>
       </c>
       <c r="J238" s="230" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
@@ -18439,7 +18447,7 @@
         <v>0</v>
       </c>
       <c r="J240" s="230" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
@@ -18535,7 +18543,7 @@
         <v>210</v>
       </c>
       <c r="J243" s="230" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
@@ -18599,7 +18607,7 @@
         <v>120</v>
       </c>
       <c r="J245" s="230" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
@@ -18663,7 +18671,7 @@
         <v>0</v>
       </c>
       <c r="J247" s="230" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
@@ -18759,7 +18767,7 @@
         <v>0</v>
       </c>
       <c r="J250" s="230" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
@@ -18823,7 +18831,7 @@
         <v>120</v>
       </c>
       <c r="J252" s="230" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
@@ -18974,10 +18982,10 @@
         <v>180</v>
       </c>
       <c r="G257" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H257" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I257" s="231">
         <v>60</v>
@@ -19111,7 +19119,7 @@
         <v>120</v>
       </c>
       <c r="J261" s="230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.25">
@@ -19486,10 +19494,10 @@
         <v>230</v>
       </c>
       <c r="G273" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H273" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I273" s="231">
         <v>90</v>
@@ -19518,10 +19526,10 @@
         <v>550</v>
       </c>
       <c r="G274" s="228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H274" s="230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I274" s="231">
         <v>60</v>
@@ -20159,7 +20167,7 @@
         <v>0.2700909090909091</v>
       </c>
       <c r="F26" s="247" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G26" s="247" t="s">
         <v>863</v>
@@ -20184,7 +20192,7 @@
         <v>0.91081818181818186</v>
       </c>
       <c r="F27" s="247" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G27" s="247" t="s">
         <v>16</v>
@@ -20661,11 +20669,11 @@
       </c>
       <c r="G7" s="187">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$100,MATCH(MRP!D7,Tubex_Dashboard!$F$11:$F$100,0))</f>
-        <v>198008</v>
+        <v>310582</v>
       </c>
       <c r="H7" s="188">
         <f t="shared" si="0"/>
-        <v>501992</v>
+        <v>389418</v>
       </c>
       <c r="I7" s="188"/>
     </row>
@@ -20712,11 +20720,11 @@
       </c>
       <c r="G9" s="105">
         <f>SUM(G3:G8)</f>
-        <v>306788</v>
+        <v>419362</v>
       </c>
       <c r="H9" s="105">
         <f>SUMIF(H3:H8, "&gt;0")</f>
-        <v>746328</v>
+        <v>633754</v>
       </c>
       <c r="I9" s="12"/>
       <c r="J9" s="173"/>
@@ -21219,7 +21227,7 @@
       </c>
       <c r="E22" s="148">
         <f>SUMPRODUCT((TableBOM[Item ID]=A22)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))/1000)</f>
-        <v>4857.5296000000008</v>
+        <v>3866.8784000000005</v>
       </c>
       <c r="F22" s="149">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A22,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A22,TableInventory[Item ID],0)),0)</f>
@@ -21227,7 +21235,7 @@
       </c>
       <c r="G22" s="148">
         <f t="shared" si="1"/>
-        <v>-4262.5296000000008</v>
+        <v>-3271.8784000000005</v>
       </c>
       <c r="H22" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A22)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F22*1000*SUMPRODUCT((TableBOM[Item ID]=A22)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A22)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
@@ -21579,7 +21587,7 @@
       </c>
       <c r="E30" s="148">
         <f>SUMPRODUCT((TableBOM[Item ID]=A30)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))/1000)</f>
-        <v>208.23278960000002</v>
+        <v>173.55999760000003</v>
       </c>
       <c r="F30" s="148">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A30,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A30,TableInventory[Item ID],0)),0)</f>
@@ -21587,7 +21595,7 @@
       </c>
       <c r="G30" s="148">
         <f t="shared" si="1"/>
-        <v>-208.23278960000002</v>
+        <v>-173.55999760000003</v>
       </c>
       <c r="H30" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A30)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F30*1000*SUMPRODUCT((TableBOM[Item ID]=A30)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A30)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
@@ -21763,7 +21771,7 @@
       </c>
       <c r="E34" s="148">
         <f>SUMPRODUCT((TableBOM[Item ID]=A34)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))/1000)</f>
-        <v>562.09639200000004</v>
+        <v>479.12935400000003</v>
       </c>
       <c r="F34" s="148">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A34,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A34,TableInventory[Item ID],0)),0)</f>
@@ -21771,7 +21779,7 @@
       </c>
       <c r="G34" s="148">
         <f t="shared" si="1"/>
-        <v>-562.09639200000004</v>
+        <v>-479.12935400000003</v>
       </c>
       <c r="H34" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A34)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F34*1000*SUMPRODUCT((TableBOM[Item ID]=A34)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A34)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
@@ -22091,7 +22099,7 @@
       </c>
       <c r="E42" s="148">
         <f>SUMPRODUCT((TableBOM[Item ID]=A42)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))/1000)</f>
-        <v>293.91225600000001</v>
+        <v>259.239464</v>
       </c>
       <c r="F42" s="148">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A42,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A42,TableInventory[Item ID],0)),0)</f>
@@ -22099,11 +22107,11 @@
       </c>
       <c r="G42" s="148">
         <f t="shared" si="1"/>
-        <v>141.08774399999999</v>
+        <v>175.760536</v>
       </c>
       <c r="H42" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A42)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F42*1000*SUMPRODUCT((TableBOM[Item ID]=A42)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A42)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
-        <v>1072030</v>
+        <v>1026514</v>
       </c>
       <c r="I42" s="150" t="str">
         <f t="shared" si="2"/>
@@ -22685,7 +22693,7 @@
       </c>
       <c r="E57" s="148">
         <f>SUMPRODUCT((TableBOM[Item ID]=A57)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))/1000)</f>
-        <v>512031.84</v>
+        <v>397206.36</v>
       </c>
       <c r="F57" s="148">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A57,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A57,TableInventory[Item ID],0)),0)</f>
@@ -22693,7 +22701,7 @@
       </c>
       <c r="G57" s="148">
         <f t="shared" si="3"/>
-        <v>-432031.84</v>
+        <v>-317206.36</v>
       </c>
       <c r="H57" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A57)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F57*1000*SUMPRODUCT((TableBOM[Item ID]=A57)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A57)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
@@ -23179,7 +23187,7 @@
       </c>
       <c r="E70" s="148">
         <f>SUMPRODUCT((TableBOM[Item ID]=A70)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))/1000)</f>
-        <v>2551.1965459200001</v>
+        <v>2030.9065356800002</v>
       </c>
       <c r="F70" s="148">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A70,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A70,TableInventory[Item ID],0)),0)</f>
@@ -23187,7 +23195,7 @@
       </c>
       <c r="G70" s="148">
         <f t="shared" si="3"/>
-        <v>-1775.1965459200001</v>
+        <v>-1254.9065356800002</v>
       </c>
       <c r="H70" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A70)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F70*1000*SUMPRODUCT((TableBOM[Item ID]=A70)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A70)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
@@ -23331,7 +23339,7 @@
       </c>
       <c r="E74" s="148">
         <f>SUMPRODUCT((TableBOM[Item ID]=A74)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))/1000)</f>
-        <v>6.4963789439999999</v>
+        <v>5.466101696</v>
       </c>
       <c r="F74" s="148">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A74,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A74,TableInventory[Item ID],0)),0)</f>
@@ -23339,11 +23347,11 @@
       </c>
       <c r="G74" s="148">
         <f t="shared" si="3"/>
-        <v>15.003621056</v>
+        <v>16.033898304000001</v>
       </c>
       <c r="H74" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A74)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F74*1000*SUMPRODUCT((TableBOM[Item ID]=A74)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A74)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
-        <v>2304523</v>
+        <v>2296099</v>
       </c>
       <c r="I74" s="150" t="str">
         <f t="shared" si="4"/>
@@ -23415,7 +23423,7 @@
       </c>
       <c r="E76" s="148">
         <f>SUMPRODUCT((TableBOM[Item ID]=A76)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))/1000)</f>
-        <v>127.99732</v>
+        <v>108.67962160000002</v>
       </c>
       <c r="F76" s="148">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A76,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A76,TableInventory[Item ID],0)),0)</f>
@@ -23423,11 +23431,11 @@
       </c>
       <c r="G76" s="148">
         <f t="shared" ref="G76:G107" si="5">F76-E76</f>
-        <v>136.00268</v>
+        <v>155.32037839999998</v>
       </c>
       <c r="H76" s="155">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A76)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F76*1000*SUMPRODUCT((TableBOM[Item ID]=A76)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8)))/SUMPRODUCT((TableBOM[Item ID]=A76)*((SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))&gt;0)*(SUMIF($D$3:$D$8,TableBOM[Product ID],$H$3:$H$8))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
-        <v>1539334</v>
+        <v>1539489</v>
       </c>
       <c r="I76" s="150" t="str">
         <f t="shared" ref="I76:I92" si="6">IF(E76=0,"Not needed",IF(G76&lt;0,"SHORTAGE",IF(G76&lt;E76*0.1,"LOW","OK")))</f>
@@ -24170,11 +24178,11 @@
       </c>
       <c r="G98" s="192">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$100,MATCH(MRP!D98,Tubex_Dashboard!$F$11:$F$100,0))</f>
-        <v>36840</v>
+        <v>64920</v>
       </c>
       <c r="H98" s="193">
         <f>F98-G98</f>
-        <v>23320</v>
+        <v>-4760</v>
       </c>
       <c r="I98" s="194"/>
     </row>
@@ -24258,11 +24266,11 @@
       </c>
       <c r="G101" s="192">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$100,MATCH(MRP!D101,Tubex_Dashboard!$F$11:$F$100,0))</f>
-        <v>27120</v>
+        <v>42720</v>
       </c>
       <c r="H101" s="193">
         <f>F101-G101</f>
-        <v>19880</v>
+        <v>4280</v>
       </c>
       <c r="I101" s="194"/>
     </row>
@@ -24280,11 +24288,11 @@
       </c>
       <c r="G102" s="105">
         <f>SUM(G97:G101)</f>
-        <v>267180</v>
+        <v>310860</v>
       </c>
       <c r="H102" s="105">
         <f>SUMIF(H97:H101, "&gt;0")</f>
-        <v>627647</v>
+        <v>588727</v>
       </c>
       <c r="I102" s="12"/>
       <c r="J102" s="173"/>
@@ -24357,7 +24365,7 @@
       </c>
       <c r="E105" s="149">
         <f>SUMPRODUCT((TableBOM[Item ID]=A105)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))/1000)</f>
-        <v>15734.649599999997</v>
+        <v>14849.986799999997</v>
       </c>
       <c r="F105" s="149">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A105,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A105,TableInventory[Item ID],0)),0)</f>
@@ -24365,11 +24373,11 @@
       </c>
       <c r="G105" s="149">
         <f t="shared" ref="G105:G111" si="7">F105-E105</f>
-        <v>-12984.649599999997</v>
+        <v>-12099.986799999997</v>
       </c>
       <c r="H105" s="158">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A105)*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F105*1000*SUMPRODUCT((TableBOM[Item ID]=A105)*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101)))/SUMPRODUCT((TableBOM[Item ID]=A105)*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
-        <v>109696</v>
+        <v>109024</v>
       </c>
       <c r="I105" s="152" t="str">
         <f t="shared" ref="I105:I111" si="8">IF(E105=0,"Not needed",IF(G105&lt;0,"SHORTAGE",IF(G105&lt;E105*0.1,"LOW","OK")))</f>
@@ -24377,7 +24385,7 @@
       </c>
       <c r="J105" s="162" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A105)&gt;0)*($H$97&gt;0),"Alpha 75ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A105)&gt;0)*($H$98&gt;0),"Samsol Yellow 120ml, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A105)&gt;0)*($H$99&gt;0),"Mablay 130ml White, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A105)&gt;0)*($H$100&gt;0),"Alpha 150ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A105)&gt;0)*($H$101&gt;0),"Samsol Yellow 200ml, ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A105)&gt;0)*($H$97&gt;0),"Alpha 75ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A105)&gt;0)*($H$98&gt;0),"Samsol Yellow 120ml, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A105)&gt;0)*($H$99&gt;0),"Mablay 130ml White, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A105)&gt;0)*($H$100&gt;0),"Alpha 150ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A105)&gt;0)*($H$101&gt;0),"Samsol Yellow 200ml, ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A105)&gt;0)*($H$97&gt;0),"Alpha 75ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A105)&gt;0)*($H$98&gt;0),"Samsol Yellow 120ml, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A105)&gt;0)*($H$99&gt;0),"Mablay 130ml White, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A105)&gt;0)*($H$100&gt;0),"Alpha 150ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A105)&gt;0)*($H$101&gt;0),"Samsol Yellow 200ml, ",""))-2),"")</f>
-        <v>Alpha 75ml TRP, Samsol Yellow 120ml, Mablay 130ml White, Alpha 150ml TRP, Samsol Yellow 200ml</v>
+        <v>Alpha 75ml TRP, Mablay 130ml White, Alpha 150ml TRP, Samsol Yellow 200ml</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
@@ -24395,7 +24403,7 @@
       </c>
       <c r="E106" s="149">
         <f>SUMPRODUCT((TableBOM[Item ID]=A106)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))/1000)</f>
-        <v>52.713700000000003</v>
+        <v>6.1524999999999999</v>
       </c>
       <c r="F106" s="149">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A106,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A106,TableInventory[Item ID],0)),0)</f>
@@ -24403,19 +24411,19 @@
       </c>
       <c r="G106" s="149">
         <f t="shared" si="7"/>
-        <v>-27.713700000000003</v>
+        <v>18.8475</v>
       </c>
       <c r="H106" s="158">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A106)*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F106*1000*SUMPRODUCT((TableBOM[Item ID]=A106)*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101)))/SUMPRODUCT((TableBOM[Item ID]=A106)*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
-        <v>20488</v>
+        <v>17391</v>
       </c>
       <c r="I106" s="152" t="str">
         <f t="shared" si="8"/>
-        <v>SHORTAGE</v>
+        <v>OK</v>
       </c>
       <c r="J106" s="162" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A106)&gt;0)*($H$97&gt;0),"Alpha 75ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A106)&gt;0)*($H$98&gt;0),"Samsol Yellow 120ml, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A106)&gt;0)*($H$99&gt;0),"Mablay 130ml White, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A106)&gt;0)*($H$100&gt;0),"Alpha 150ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A106)&gt;0)*($H$101&gt;0),"Samsol Yellow 200ml, ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A106)&gt;0)*($H$97&gt;0),"Alpha 75ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A106)&gt;0)*($H$98&gt;0),"Samsol Yellow 120ml, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A106)&gt;0)*($H$99&gt;0),"Mablay 130ml White, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A106)&gt;0)*($H$100&gt;0),"Alpha 150ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A106)&gt;0)*($H$101&gt;0),"Samsol Yellow 200ml, ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A106)&gt;0)*($H$97&gt;0),"Alpha 75ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A106)&gt;0)*($H$98&gt;0),"Samsol Yellow 120ml, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A106)&gt;0)*($H$99&gt;0),"Mablay 130ml White, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A106)&gt;0)*($H$100&gt;0),"Alpha 150ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A106)&gt;0)*($H$101&gt;0),"Samsol Yellow 200ml, ",""))-2),"")</f>
-        <v>Samsol Yellow 120ml, Samsol Yellow 200ml</v>
+        <v>Samsol Yellow 200ml</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
@@ -24509,7 +24517,7 @@
       </c>
       <c r="E109" s="149">
         <f>SUMPRODUCT((TableBOM[Item ID]=A109)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))/1000)</f>
-        <v>5976.1343807999992</v>
+        <v>5752.6599867999994</v>
       </c>
       <c r="F109" s="149">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A109,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A109,TableInventory[Item ID],0)),0)</f>
@@ -24517,11 +24525,11 @@
       </c>
       <c r="G109" s="149">
         <f t="shared" si="7"/>
-        <v>-5676.1343807999992</v>
+        <v>-5452.6599867999994</v>
       </c>
       <c r="H109" s="158">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A109)*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F109*1000*SUMPRODUCT((TableBOM[Item ID]=A109)*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101)))/SUMPRODUCT((TableBOM[Item ID]=A109)*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
-        <v>30510</v>
+        <v>30479</v>
       </c>
       <c r="I109" s="152" t="str">
         <f t="shared" si="8"/>
@@ -24529,7 +24537,7 @@
       </c>
       <c r="J109" s="156" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A109)&gt;0)*($H$97&gt;0),"Alpha 75ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A109)&gt;0)*($H$98&gt;0),"Samsol Yellow 120ml, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A109)&gt;0)*($H$99&gt;0),"Mablay 130ml White, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A109)&gt;0)*($H$100&gt;0),"Alpha 150ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A109)&gt;0)*($H$101&gt;0),"Samsol Yellow 200ml, ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A109)&gt;0)*($H$97&gt;0),"Alpha 75ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A109)&gt;0)*($H$98&gt;0),"Samsol Yellow 120ml, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A109)&gt;0)*($H$99&gt;0),"Mablay 130ml White, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A109)&gt;0)*($H$100&gt;0),"Alpha 150ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A109)&gt;0)*($H$101&gt;0),"Samsol Yellow 200ml, ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A109)&gt;0)*($H$97&gt;0),"Alpha 75ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A109)&gt;0)*($H$98&gt;0),"Samsol Yellow 120ml, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A109)&gt;0)*($H$99&gt;0),"Mablay 130ml White, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A109)&gt;0)*($H$100&gt;0),"Alpha 150ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A109)&gt;0)*($H$101&gt;0),"Samsol Yellow 200ml, ",""))-2),"")</f>
-        <v>Alpha 75ml TRP, Samsol Yellow 120ml, Mablay 130ml White, Alpha 150ml TRP</v>
+        <v>Alpha 75ml TRP, Mablay 130ml White, Alpha 150ml TRP</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
@@ -24547,7 +24555,7 @@
       </c>
       <c r="E110" s="17">
         <f>SUMPRODUCT((TableBOM[Item ID]=A110)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))/1000)</f>
-        <v>190.50904600000001</v>
+        <v>41.015025999999999</v>
       </c>
       <c r="F110" s="17">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A110,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A110,TableInventory[Item ID],0)),0)</f>
@@ -24555,7 +24563,7 @@
       </c>
       <c r="G110" s="17">
         <f t="shared" si="7"/>
-        <v>-40.509046000000012</v>
+        <v>108.98497399999999</v>
       </c>
       <c r="H110" s="160">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A110)*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F110*1000*SUMPRODUCT((TableBOM[Item ID]=A110)*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101)))/SUMPRODUCT((TableBOM[Item ID]=A110)*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
@@ -24563,7 +24571,7 @@
       </c>
       <c r="I110" s="33" t="str">
         <f t="shared" si="8"/>
-        <v>SHORTAGE</v>
+        <v>OK</v>
       </c>
       <c r="J110" s="162" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A110)&gt;0)*($H$97&gt;0),"Alpha 75ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A110)&gt;0)*($H$98&gt;0),"Samsol Yellow 120ml, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A110)&gt;0)*($H$99&gt;0),"Mablay 130ml White, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A110)&gt;0)*($H$100&gt;0),"Alpha 150ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A110)&gt;0)*($H$101&gt;0),"Samsol Yellow 200ml, ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A110)&gt;0)*($H$97&gt;0),"Alpha 75ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A110)&gt;0)*($H$98&gt;0),"Samsol Yellow 120ml, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A110)&gt;0)*($H$99&gt;0),"Mablay 130ml White, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A110)&gt;0)*($H$100&gt;0),"Alpha 150ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A110)&gt;0)*($H$101&gt;0),"Samsol Yellow 200ml, ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A110)&gt;0)*($H$97&gt;0),"Alpha 75ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A110)&gt;0)*($H$98&gt;0),"Samsol Yellow 120ml, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A110)&gt;0)*($H$99&gt;0),"Mablay 130ml White, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A110)&gt;0)*($H$100&gt;0),"Alpha 150ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A110)&gt;0)*($H$101&gt;0),"Samsol Yellow 200ml, ",""))-2),"")</f>
@@ -24585,7 +24593,7 @@
       </c>
       <c r="E111" s="149">
         <f>SUMPRODUCT((TableBOM[Item ID]=A111)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))/1000)</f>
-        <v>3.60897025</v>
+        <v>3.3851802499999999</v>
       </c>
       <c r="F111" s="149">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A111,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A111,TableInventory[Item ID],0)),0)</f>
@@ -24593,7 +24601,7 @@
       </c>
       <c r="G111" s="149">
         <f t="shared" si="7"/>
-        <v>-3.60897025</v>
+        <v>-3.3851802499999999</v>
       </c>
       <c r="H111" s="158">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A111)*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %]))=0,"-",ROUND(F111*1000*SUMPRODUCT((TableBOM[Item ID]=A111)*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101)))/SUMPRODUCT((TableBOM[Item ID]=A111)*((SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))&gt;0)*(SUMIF($D$97:$D$101,TableBOM[Product ID],$H$97:$H$101))*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])),0)),"-")</f>
@@ -24605,7 +24613,7 @@
       </c>
       <c r="J111" s="156" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A111)&gt;0)*($H$97&gt;0),"Alpha 75ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A111)&gt;0)*($H$98&gt;0),"Samsol Yellow 120ml, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A111)&gt;0)*($H$99&gt;0),"Mablay 130ml White, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A111)&gt;0)*($H$100&gt;0),"Alpha 150ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A111)&gt;0)*($H$101&gt;0),"Samsol Yellow 200ml, ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A111)&gt;0)*($H$97&gt;0),"Alpha 75ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A111)&gt;0)*($H$98&gt;0),"Samsol Yellow 120ml, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A111)&gt;0)*($H$99&gt;0),"Mablay 130ml White, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A111)&gt;0)*($H$100&gt;0),"Alpha 150ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A111)&gt;0)*($H$101&gt;0),"Samsol Yellow 200ml, ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A111)&gt;0)*($H$97&gt;0),"Alpha 75ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A111)&gt;0)*($H$98&gt;0),"Samsol Yellow 120ml, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A111)&gt;0)*($H$99&gt;0),"Mablay 130ml White, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A111)&gt;0)*($H$100&gt;0),"Alpha 150ml TRP, ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A111)&gt;0)*($H$101&gt;0),"Samsol Yellow 200ml, ",""))-2),"")</f>
-        <v>Alpha 75ml TRP, Samsol Yellow 120ml, Mablay 130ml White, Alpha 150ml TRP, Samsol Yellow 200ml</v>
+        <v>Alpha 75ml TRP, Mablay 130ml White, Alpha 150ml TRP, Samsol Yellow 200ml</v>
       </c>
     </row>
   </sheetData>
@@ -25852,7 +25860,7 @@
         <v>135</v>
       </c>
       <c r="D27" s="265" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E27" s="265" t="s">
         <v>143</v>
@@ -26159,7 +26167,7 @@
         <v>135</v>
       </c>
       <c r="D34" s="265" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E34" s="265" t="s">
         <v>143</v>
@@ -26423,7 +26431,7 @@
         <v>135</v>
       </c>
       <c r="D40" s="265" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E40" s="265" t="s">
         <v>143</v>
@@ -26601,7 +26609,7 @@
         <v>135</v>
       </c>
       <c r="D44" s="265" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E44" s="265" t="s">
         <v>143</v>
@@ -26826,7 +26834,7 @@
         <v>135</v>
       </c>
       <c r="D49" s="265" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E49" s="265" t="s">
         <v>143</v>
@@ -27051,7 +27059,7 @@
         <v>135</v>
       </c>
       <c r="D54" s="265" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E54" s="265" t="s">
         <v>143</v>
@@ -27272,7 +27280,7 @@
         <v>135</v>
       </c>
       <c r="D59" s="265" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E59" s="265" t="s">
         <v>143</v>
@@ -27493,7 +27501,7 @@
         <v>135</v>
       </c>
       <c r="D64" s="265" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E64" s="265" t="s">
         <v>143</v>
@@ -27714,7 +27722,7 @@
         <v>135</v>
       </c>
       <c r="D69" s="265" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E69" s="265" t="s">
         <v>143</v>
@@ -27982,7 +27990,7 @@
         <v>135</v>
       </c>
       <c r="D75" s="265" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E75" s="265" t="s">
         <v>143</v>
@@ -28289,7 +28297,7 @@
         <v>135</v>
       </c>
       <c r="D82" s="265" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E82" s="265" t="s">
         <v>143</v>
@@ -28600,7 +28608,7 @@
         <v>135</v>
       </c>
       <c r="D89" s="265" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E89" s="265" t="s">
         <v>143</v>
@@ -29469,42 +29477,1402 @@
       <c r="S108" s="265"/>
       <c r="T108" s="265"/>
     </row>
-    <row r="109" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="266">
+        <v>46289</v>
+      </c>
+      <c r="B109" s="265" t="s">
+        <v>257</v>
+      </c>
+      <c r="C109" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D109" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E109" s="265">
+        <v>30</v>
+      </c>
+      <c r="F109" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G109" s="267">
+        <v>12000</v>
+      </c>
+      <c r="H109" s="267">
+        <v>11760</v>
+      </c>
+      <c r="I109" s="267">
+        <v>240</v>
+      </c>
+      <c r="J109" s="268">
+        <f t="shared" si="3"/>
+        <v>0.02</v>
+      </c>
+      <c r="K109" s="265"/>
+      <c r="L109" s="265"/>
+      <c r="M109" s="265"/>
+      <c r="N109" s="265"/>
+      <c r="O109" s="265"/>
+      <c r="P109" s="265"/>
+      <c r="Q109" s="265"/>
+      <c r="R109" s="265"/>
+      <c r="S109" s="265">
+        <v>180</v>
+      </c>
+      <c r="T109" s="265"/>
+    </row>
+    <row r="110" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="266">
+        <v>46289</v>
+      </c>
+      <c r="B110" s="265" t="s">
+        <v>258</v>
+      </c>
+      <c r="C110" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D110" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E110" s="265">
+        <v>30</v>
+      </c>
+      <c r="F110" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G110" s="267">
+        <v>8000</v>
+      </c>
+      <c r="H110" s="267">
+        <v>7990</v>
+      </c>
+      <c r="I110" s="267">
+        <v>10</v>
+      </c>
+      <c r="J110" s="268">
+        <f t="shared" si="3"/>
+        <v>1.25E-3</v>
+      </c>
+      <c r="K110" s="265"/>
+      <c r="L110" s="265"/>
+      <c r="M110" s="265"/>
+      <c r="N110" s="265"/>
+      <c r="O110" s="265"/>
+      <c r="P110" s="265"/>
+      <c r="Q110" s="265"/>
+      <c r="R110" s="265"/>
+      <c r="S110" s="265">
+        <v>180</v>
+      </c>
+      <c r="T110" s="265"/>
+    </row>
+    <row r="111" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="266">
+        <v>46289</v>
+      </c>
+      <c r="B111" s="265" t="s">
+        <v>259</v>
+      </c>
+      <c r="C111" s="265" t="s">
+        <v>13</v>
+      </c>
+      <c r="D111" s="265" t="s">
+        <v>147</v>
+      </c>
+      <c r="E111" s="265" t="s">
+        <v>146</v>
+      </c>
+      <c r="F111" s="265">
+        <v>8006</v>
+      </c>
+      <c r="G111" s="267">
+        <v>8400</v>
+      </c>
+      <c r="H111" s="267">
+        <v>5520</v>
+      </c>
+      <c r="I111" s="267">
+        <v>2880</v>
+      </c>
+      <c r="J111" s="268">
+        <f t="shared" si="3"/>
+        <v>0.34285714285714286</v>
+      </c>
+      <c r="K111" s="265">
+        <v>120</v>
+      </c>
+      <c r="L111" s="265">
+        <v>60</v>
+      </c>
+      <c r="M111" s="265"/>
+      <c r="N111" s="265"/>
+      <c r="O111" s="265"/>
+      <c r="P111" s="265"/>
+      <c r="Q111" s="265"/>
+      <c r="R111" s="265"/>
+      <c r="S111" s="265">
+        <v>240</v>
+      </c>
+      <c r="T111" s="265"/>
+    </row>
+    <row r="112" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="266">
+        <v>46289</v>
+      </c>
+      <c r="B112" s="265" t="s">
+        <v>260</v>
+      </c>
+      <c r="C112" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D112" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E112" s="265">
+        <v>30</v>
+      </c>
+      <c r="F112" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G112" s="267">
+        <v>9300</v>
+      </c>
+      <c r="H112" s="267">
+        <v>9205</v>
+      </c>
+      <c r="I112" s="267">
+        <v>95</v>
+      </c>
+      <c r="J112" s="268">
+        <f t="shared" si="3"/>
+        <v>1.0215053763440861E-2</v>
+      </c>
+      <c r="K112" s="265">
+        <v>60</v>
+      </c>
+      <c r="L112" s="265"/>
+      <c r="M112" s="265"/>
+      <c r="N112" s="265"/>
+      <c r="O112" s="265"/>
+      <c r="P112" s="265"/>
+      <c r="Q112" s="265"/>
+      <c r="R112" s="265"/>
+      <c r="S112" s="265">
+        <v>180</v>
+      </c>
+      <c r="T112" s="265"/>
+    </row>
+    <row r="113" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="266">
+        <v>46289</v>
+      </c>
+      <c r="B113" s="265" t="s">
+        <v>261</v>
+      </c>
+      <c r="C113" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D113" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E113" s="265">
+        <v>30</v>
+      </c>
+      <c r="F113" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G113" s="267">
+        <v>13450</v>
+      </c>
+      <c r="H113" s="267">
+        <v>13090</v>
+      </c>
+      <c r="I113" s="267">
+        <v>360</v>
+      </c>
+      <c r="J113" s="268">
+        <f t="shared" si="3"/>
+        <v>2.6765799256505577E-2</v>
+      </c>
+      <c r="K113" s="265"/>
+      <c r="L113" s="265"/>
+      <c r="M113" s="265"/>
+      <c r="N113" s="265"/>
+      <c r="O113" s="265"/>
+      <c r="P113" s="265"/>
+      <c r="Q113" s="265"/>
+      <c r="R113" s="265"/>
+      <c r="S113" s="265">
+        <v>180</v>
+      </c>
+      <c r="T113" s="265"/>
+    </row>
+    <row r="114" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="266">
+        <v>46290</v>
+      </c>
+      <c r="B114" s="265" t="s">
+        <v>257</v>
+      </c>
+      <c r="C114" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D114" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E114" s="265">
+        <v>30</v>
+      </c>
+      <c r="F114" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G114" s="267">
+        <v>16000</v>
+      </c>
+      <c r="H114" s="267">
+        <v>15715</v>
+      </c>
+      <c r="I114" s="267">
+        <v>285</v>
+      </c>
+      <c r="J114" s="268">
+        <f t="shared" si="3"/>
+        <v>1.7812499999999998E-2</v>
+      </c>
+      <c r="K114" s="265"/>
+      <c r="L114" s="265"/>
+      <c r="M114" s="265"/>
+      <c r="N114" s="265"/>
+      <c r="O114" s="265"/>
+      <c r="P114" s="265"/>
+      <c r="Q114" s="265"/>
+      <c r="R114" s="265"/>
+      <c r="S114" s="265">
+        <v>120</v>
+      </c>
+      <c r="T114" s="265"/>
+    </row>
+    <row r="115" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="266">
+        <v>46290</v>
+      </c>
+      <c r="B115" s="265" t="s">
+        <v>258</v>
+      </c>
+      <c r="C115" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D115" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E115" s="265">
+        <v>30</v>
+      </c>
+      <c r="F115" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G115" s="267">
+        <v>15000</v>
+      </c>
+      <c r="H115" s="267">
+        <v>14985</v>
+      </c>
+      <c r="I115" s="267">
+        <v>15</v>
+      </c>
+      <c r="J115" s="268">
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
+      </c>
+      <c r="K115" s="265"/>
+      <c r="L115" s="265"/>
+      <c r="M115" s="265"/>
+      <c r="N115" s="265"/>
+      <c r="O115" s="265"/>
+      <c r="P115" s="265"/>
+      <c r="Q115" s="265"/>
+      <c r="R115" s="265"/>
+      <c r="S115" s="265">
+        <v>120</v>
+      </c>
+      <c r="T115" s="265"/>
+    </row>
+    <row r="116" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="266">
+        <v>46290</v>
+      </c>
+      <c r="B116" s="265" t="s">
+        <v>259</v>
+      </c>
+      <c r="C116" s="265" t="s">
+        <v>13</v>
+      </c>
+      <c r="D116" s="265" t="s">
+        <v>147</v>
+      </c>
+      <c r="E116" s="265" t="s">
+        <v>146</v>
+      </c>
+      <c r="F116" s="265">
+        <v>8006</v>
+      </c>
+      <c r="G116" s="267">
+        <v>12520</v>
+      </c>
+      <c r="H116" s="267">
+        <v>10080</v>
+      </c>
+      <c r="I116" s="267">
+        <v>2440</v>
+      </c>
+      <c r="J116" s="268">
+        <f t="shared" si="3"/>
+        <v>0.19488817891373802</v>
+      </c>
+      <c r="K116" s="265"/>
+      <c r="L116" s="265">
+        <v>240</v>
+      </c>
+      <c r="M116" s="265"/>
+      <c r="N116" s="265"/>
+      <c r="O116" s="265"/>
+      <c r="P116" s="265"/>
+      <c r="Q116" s="265"/>
+      <c r="R116" s="265"/>
+      <c r="S116" s="265">
+        <v>120</v>
+      </c>
+      <c r="T116" s="265"/>
+    </row>
+    <row r="117" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="266">
+        <v>46290</v>
+      </c>
+      <c r="B117" s="265" t="s">
+        <v>260</v>
+      </c>
+      <c r="C117" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D117" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E117" s="265">
+        <v>30</v>
+      </c>
+      <c r="F117" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G117" s="267">
+        <v>9600</v>
+      </c>
+      <c r="H117" s="267">
+        <v>9500</v>
+      </c>
+      <c r="I117" s="267">
+        <v>100</v>
+      </c>
+      <c r="J117" s="268">
+        <f t="shared" si="3"/>
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="K117" s="265">
+        <v>120</v>
+      </c>
+      <c r="L117" s="265"/>
+      <c r="M117" s="265"/>
+      <c r="N117" s="265"/>
+      <c r="O117" s="265"/>
+      <c r="P117" s="265"/>
+      <c r="Q117" s="265"/>
+      <c r="R117" s="265"/>
+      <c r="S117" s="265">
+        <v>120</v>
+      </c>
+      <c r="T117" s="265"/>
+    </row>
+    <row r="118" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="266">
+        <v>46290</v>
+      </c>
+      <c r="B118" s="265" t="s">
+        <v>261</v>
+      </c>
+      <c r="C118" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D118" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E118" s="265">
+        <v>30</v>
+      </c>
+      <c r="F118" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G118" s="267">
+        <v>19177</v>
+      </c>
+      <c r="H118" s="267">
+        <v>18802</v>
+      </c>
+      <c r="I118" s="267">
+        <v>375</v>
+      </c>
+      <c r="J118" s="268">
+        <f t="shared" si="3"/>
+        <v>1.9554674870939145E-2</v>
+      </c>
+      <c r="K118" s="265"/>
+      <c r="L118" s="265"/>
+      <c r="M118" s="265"/>
+      <c r="N118" s="265"/>
+      <c r="O118" s="265"/>
+      <c r="P118" s="265"/>
+      <c r="Q118" s="265"/>
+      <c r="R118" s="265"/>
+      <c r="S118" s="265">
+        <v>120</v>
+      </c>
+      <c r="T118" s="265"/>
+    </row>
+    <row r="119" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="266">
+        <v>46291</v>
+      </c>
+      <c r="B119" s="265" t="s">
+        <v>257</v>
+      </c>
+      <c r="C119" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D119" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E119" s="265">
+        <v>30</v>
+      </c>
+      <c r="F119" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G119" s="267">
+        <v>18000</v>
+      </c>
+      <c r="H119" s="267">
+        <v>17750</v>
+      </c>
+      <c r="I119" s="267">
+        <v>250</v>
+      </c>
+      <c r="J119" s="268">
+        <f t="shared" si="3"/>
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="K119" s="265"/>
+      <c r="L119" s="265"/>
+      <c r="M119" s="265"/>
+      <c r="N119" s="265"/>
+      <c r="O119" s="265"/>
+      <c r="P119" s="265"/>
+      <c r="Q119" s="265"/>
+      <c r="R119" s="265"/>
+      <c r="S119" s="265">
+        <v>120</v>
+      </c>
+      <c r="T119" s="265"/>
+    </row>
+    <row r="120" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="266">
+        <v>46291</v>
+      </c>
+      <c r="B120" s="265" t="s">
+        <v>258</v>
+      </c>
+      <c r="C120" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D120" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E120" s="265">
+        <v>30</v>
+      </c>
+      <c r="F120" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G120" s="267">
+        <v>9996</v>
+      </c>
+      <c r="H120" s="267">
+        <v>9986</v>
+      </c>
+      <c r="I120" s="267">
+        <v>10</v>
+      </c>
+      <c r="J120" s="268">
+        <f t="shared" si="3"/>
+        <v>1.0004001600640256E-3</v>
+      </c>
+      <c r="K120" s="265"/>
+      <c r="L120" s="265"/>
+      <c r="M120" s="265"/>
+      <c r="N120" s="265"/>
+      <c r="O120" s="265"/>
+      <c r="P120" s="265"/>
+      <c r="Q120" s="265"/>
+      <c r="R120" s="265"/>
+      <c r="S120" s="265">
+        <v>60</v>
+      </c>
+      <c r="T120" s="265"/>
+    </row>
+    <row r="121" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="266">
+        <v>46291</v>
+      </c>
+      <c r="B121" s="265" t="s">
+        <v>258</v>
+      </c>
+      <c r="C121" s="265" t="s">
+        <v>224</v>
+      </c>
+      <c r="D121" s="265" t="s">
+        <v>225</v>
+      </c>
+      <c r="E121" s="265">
+        <v>35</v>
+      </c>
+      <c r="F121" s="265">
+        <v>6530</v>
+      </c>
+      <c r="G121" s="267">
+        <v>7200</v>
+      </c>
+      <c r="H121" s="267">
+        <v>7195</v>
+      </c>
+      <c r="I121" s="267">
+        <v>5</v>
+      </c>
+      <c r="J121" s="268">
+        <f t="shared" si="3"/>
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K121" s="265"/>
+      <c r="L121" s="265"/>
+      <c r="M121" s="265"/>
+      <c r="N121" s="265"/>
+      <c r="O121" s="265"/>
+      <c r="P121" s="265"/>
+      <c r="Q121" s="265"/>
+      <c r="R121" s="265"/>
+      <c r="S121" s="265"/>
+      <c r="T121" s="265"/>
+    </row>
+    <row r="122" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="266">
+        <v>46291</v>
+      </c>
+      <c r="B122" s="265" t="s">
+        <v>259</v>
+      </c>
+      <c r="C122" s="265" t="s">
+        <v>13</v>
+      </c>
+      <c r="D122" s="265" t="s">
+        <v>139</v>
+      </c>
+      <c r="E122" s="265" t="s">
+        <v>138</v>
+      </c>
+      <c r="F122" s="265">
+        <v>8005</v>
+      </c>
+      <c r="G122" s="267">
+        <v>7111</v>
+      </c>
+      <c r="H122" s="267">
+        <v>6000</v>
+      </c>
+      <c r="I122" s="267">
+        <v>1111</v>
+      </c>
+      <c r="J122" s="268">
+        <f t="shared" si="3"/>
+        <v>0.15623681620025312</v>
+      </c>
+      <c r="K122" s="265"/>
+      <c r="L122" s="265">
+        <v>40</v>
+      </c>
+      <c r="M122" s="265"/>
+      <c r="N122" s="265">
+        <v>480</v>
+      </c>
+      <c r="O122" s="265"/>
+      <c r="P122" s="265"/>
+      <c r="Q122" s="265"/>
+      <c r="R122" s="265"/>
+      <c r="S122" s="265">
+        <v>50</v>
+      </c>
+      <c r="T122" s="265"/>
+    </row>
+    <row r="123" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="266">
+        <v>46291</v>
+      </c>
+      <c r="B123" s="265" t="s">
+        <v>260</v>
+      </c>
+      <c r="C123" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D123" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E123" s="265">
+        <v>30</v>
+      </c>
+      <c r="F123" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G123" s="267">
+        <v>25000</v>
+      </c>
+      <c r="H123" s="267">
+        <v>24850</v>
+      </c>
+      <c r="I123" s="267">
+        <v>150</v>
+      </c>
+      <c r="J123" s="268">
+        <f t="shared" si="3"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="K123" s="265"/>
+      <c r="L123" s="265"/>
+      <c r="M123" s="265"/>
+      <c r="N123" s="265"/>
+      <c r="O123" s="265"/>
+      <c r="P123" s="265"/>
+      <c r="Q123" s="265"/>
+      <c r="R123" s="265"/>
+      <c r="S123" s="265"/>
+      <c r="T123" s="265"/>
+    </row>
+    <row r="124" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="266">
+        <v>46291</v>
+      </c>
+      <c r="B124" s="265" t="s">
+        <v>261</v>
+      </c>
+      <c r="C124" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D124" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E124" s="265">
+        <v>30</v>
+      </c>
+      <c r="F124" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G124" s="267">
+        <v>13638</v>
+      </c>
+      <c r="H124" s="267">
+        <v>13328</v>
+      </c>
+      <c r="I124" s="267">
+        <v>310</v>
+      </c>
+      <c r="J124" s="268">
+        <f t="shared" si="3"/>
+        <v>2.2730605660654053E-2</v>
+      </c>
+      <c r="K124" s="265"/>
+      <c r="L124" s="265"/>
+      <c r="M124" s="265">
+        <v>60</v>
+      </c>
+      <c r="N124" s="265"/>
+      <c r="O124" s="265"/>
+      <c r="P124" s="265"/>
+      <c r="Q124" s="265"/>
+      <c r="R124" s="265"/>
+      <c r="S124" s="265">
+        <v>120</v>
+      </c>
+      <c r="T124" s="265"/>
+    </row>
+    <row r="125" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="266">
+        <v>46293</v>
+      </c>
+      <c r="B125" s="265" t="s">
+        <v>257</v>
+      </c>
+      <c r="C125" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D125" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E125" s="265">
+        <v>30</v>
+      </c>
+      <c r="F125" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G125" s="267">
+        <v>26000</v>
+      </c>
+      <c r="H125" s="267">
+        <v>25550</v>
+      </c>
+      <c r="I125" s="267">
+        <v>450</v>
+      </c>
+      <c r="J125" s="268">
+        <f t="shared" si="3"/>
+        <v>1.7307692307692309E-2</v>
+      </c>
+      <c r="K125" s="265"/>
+      <c r="L125" s="265"/>
+      <c r="M125" s="265"/>
+      <c r="N125" s="265"/>
+      <c r="O125" s="265"/>
+      <c r="P125" s="265"/>
+      <c r="Q125" s="265"/>
+      <c r="R125" s="265"/>
+      <c r="S125" s="265"/>
+      <c r="T125" s="265"/>
+    </row>
+    <row r="126" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="266">
+        <v>46293</v>
+      </c>
+      <c r="B126" s="265" t="s">
+        <v>258</v>
+      </c>
+      <c r="C126" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D126" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E126" s="265">
+        <v>30</v>
+      </c>
+      <c r="F126" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G126" s="267">
+        <v>25066</v>
+      </c>
+      <c r="H126" s="267">
+        <v>25046</v>
+      </c>
+      <c r="I126" s="267">
+        <v>20</v>
+      </c>
+      <c r="J126" s="268">
+        <f t="shared" si="3"/>
+        <v>7.9789356099896271E-4</v>
+      </c>
+      <c r="K126" s="265"/>
+      <c r="L126" s="265"/>
+      <c r="M126" s="265"/>
+      <c r="N126" s="265"/>
+      <c r="O126" s="265"/>
+      <c r="P126" s="265"/>
+      <c r="Q126" s="265"/>
+      <c r="R126" s="265"/>
+      <c r="S126" s="265"/>
+      <c r="T126" s="265"/>
+    </row>
+    <row r="127" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="266">
+        <v>46293</v>
+      </c>
+      <c r="B127" s="265" t="s">
+        <v>259</v>
+      </c>
+      <c r="C127" s="265" t="s">
+        <v>13</v>
+      </c>
+      <c r="D127" s="265" t="s">
+        <v>139</v>
+      </c>
+      <c r="E127" s="265" t="s">
+        <v>138</v>
+      </c>
+      <c r="F127" s="265">
+        <v>8005</v>
+      </c>
+      <c r="G127" s="267">
+        <v>16000</v>
+      </c>
+      <c r="H127" s="267">
+        <v>9240</v>
+      </c>
+      <c r="I127" s="267">
+        <v>6760</v>
+      </c>
+      <c r="J127" s="268">
+        <f t="shared" si="3"/>
+        <v>0.42249999999999999</v>
+      </c>
+      <c r="K127" s="265">
+        <v>50</v>
+      </c>
+      <c r="L127" s="265">
+        <v>60</v>
+      </c>
+      <c r="M127" s="265"/>
+      <c r="N127" s="265"/>
+      <c r="O127" s="265"/>
+      <c r="P127" s="265"/>
+      <c r="Q127" s="265"/>
+      <c r="R127" s="265"/>
+      <c r="S127" s="265">
+        <v>70</v>
+      </c>
+      <c r="T127" s="265"/>
+    </row>
+    <row r="128" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="266">
+        <v>46293</v>
+      </c>
+      <c r="B128" s="265" t="s">
+        <v>260</v>
+      </c>
+      <c r="C128" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D128" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E128" s="265">
+        <v>30</v>
+      </c>
+      <c r="F128" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G128" s="267">
+        <v>27000</v>
+      </c>
+      <c r="H128" s="267">
+        <v>26835</v>
+      </c>
+      <c r="I128" s="267">
+        <v>165</v>
+      </c>
+      <c r="J128" s="268">
+        <f t="shared" si="3"/>
+        <v>6.1111111111111114E-3</v>
+      </c>
+      <c r="K128" s="265"/>
+      <c r="L128" s="265"/>
+      <c r="M128" s="265"/>
+      <c r="N128" s="265"/>
+      <c r="O128" s="265"/>
+      <c r="P128" s="265"/>
+      <c r="Q128" s="265"/>
+      <c r="R128" s="265"/>
+      <c r="S128" s="265"/>
+      <c r="T128" s="265"/>
+    </row>
+    <row r="129" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="266">
+        <v>46293</v>
+      </c>
+      <c r="B129" s="265" t="s">
+        <v>261</v>
+      </c>
+      <c r="C129" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D129" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E129" s="265">
+        <v>30</v>
+      </c>
+      <c r="F129" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G129" s="267">
+        <v>26492</v>
+      </c>
+      <c r="H129" s="267">
+        <v>25942</v>
+      </c>
+      <c r="I129" s="267">
+        <v>550</v>
+      </c>
+      <c r="J129" s="268">
+        <f t="shared" si="3"/>
+        <v>2.0760984448135286E-2</v>
+      </c>
+      <c r="K129" s="265"/>
+      <c r="L129" s="265"/>
+      <c r="M129" s="265"/>
+      <c r="N129" s="265"/>
+      <c r="O129" s="265"/>
+      <c r="P129" s="265"/>
+      <c r="Q129" s="265"/>
+      <c r="R129" s="265"/>
+      <c r="S129" s="265"/>
+      <c r="T129" s="265"/>
+    </row>
+    <row r="130" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="266">
+        <v>46294</v>
+      </c>
+      <c r="B130" s="265" t="s">
+        <v>257</v>
+      </c>
+      <c r="C130" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D130" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E130" s="265">
+        <v>30</v>
+      </c>
+      <c r="F130" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G130" s="267">
+        <v>23000</v>
+      </c>
+      <c r="H130" s="267">
+        <v>22550</v>
+      </c>
+      <c r="I130" s="267">
+        <v>450</v>
+      </c>
+      <c r="J130" s="268">
+        <f t="shared" si="3"/>
+        <v>1.9565217391304349E-2</v>
+      </c>
+      <c r="K130" s="265"/>
+      <c r="L130" s="265"/>
+      <c r="M130" s="265"/>
+      <c r="N130" s="265"/>
+      <c r="O130" s="265"/>
+      <c r="P130" s="265"/>
+      <c r="Q130" s="265"/>
+      <c r="R130" s="265"/>
+      <c r="S130" s="265"/>
+      <c r="T130" s="265"/>
+    </row>
+    <row r="131" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="266">
+        <v>46294</v>
+      </c>
+      <c r="B131" s="265" t="s">
+        <v>258</v>
+      </c>
+      <c r="C131" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D131" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E131" s="265">
+        <v>30</v>
+      </c>
+      <c r="F131" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G131" s="267">
+        <v>25000</v>
+      </c>
+      <c r="H131" s="267">
+        <v>24980</v>
+      </c>
+      <c r="I131" s="267">
+        <v>20</v>
+      </c>
+      <c r="J131" s="268">
+        <f t="shared" ref="J131:J162" si="4">IFERROR(I131/(H131+I131),"")</f>
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="K131" s="265"/>
+      <c r="L131" s="265"/>
+      <c r="M131" s="265"/>
+      <c r="N131" s="265"/>
+      <c r="O131" s="265"/>
+      <c r="P131" s="265"/>
+      <c r="Q131" s="265"/>
+      <c r="R131" s="265"/>
+      <c r="S131" s="265"/>
+      <c r="T131" s="265"/>
+    </row>
+    <row r="132" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="266">
+        <v>46294</v>
+      </c>
+      <c r="B132" s="265" t="s">
+        <v>259</v>
+      </c>
+      <c r="C132" s="265" t="s">
+        <v>13</v>
+      </c>
+      <c r="D132" s="265" t="s">
+        <v>139</v>
+      </c>
+      <c r="E132" s="265" t="s">
+        <v>138</v>
+      </c>
+      <c r="F132" s="265">
+        <v>8005</v>
+      </c>
+      <c r="G132" s="267">
+        <v>19100</v>
+      </c>
+      <c r="H132" s="267">
+        <v>12840</v>
+      </c>
+      <c r="I132" s="267">
+        <v>6260</v>
+      </c>
+      <c r="J132" s="268">
+        <f t="shared" si="4"/>
+        <v>0.32774869109947646</v>
+      </c>
+      <c r="K132" s="265"/>
+      <c r="L132" s="265"/>
+      <c r="M132" s="265"/>
+      <c r="N132" s="265"/>
+      <c r="O132" s="265"/>
+      <c r="P132" s="265"/>
+      <c r="Q132" s="265"/>
+      <c r="R132" s="265"/>
+      <c r="S132" s="265"/>
+      <c r="T132" s="265"/>
+    </row>
+    <row r="133" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="266">
+        <v>46294</v>
+      </c>
+      <c r="B133" s="265" t="s">
+        <v>260</v>
+      </c>
+      <c r="C133" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D133" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E133" s="265">
+        <v>30</v>
+      </c>
+      <c r="F133" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G133" s="267">
+        <v>17000</v>
+      </c>
+      <c r="H133" s="267">
+        <v>16890</v>
+      </c>
+      <c r="I133" s="267">
+        <v>110</v>
+      </c>
+      <c r="J133" s="268">
+        <f t="shared" si="4"/>
+        <v>6.4705882352941177E-3</v>
+      </c>
+      <c r="K133" s="265">
+        <v>180</v>
+      </c>
+      <c r="L133" s="265"/>
+      <c r="M133" s="265"/>
+      <c r="N133" s="265"/>
+      <c r="O133" s="265"/>
+      <c r="P133" s="265"/>
+      <c r="Q133" s="265"/>
+      <c r="R133" s="265"/>
+      <c r="S133" s="265"/>
+      <c r="T133" s="265"/>
+    </row>
+    <row r="134" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="266">
+        <v>46294</v>
+      </c>
+      <c r="B134" s="265" t="s">
+        <v>261</v>
+      </c>
+      <c r="C134" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D134" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E134" s="265">
+        <v>30</v>
+      </c>
+      <c r="F134" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G134" s="267">
+        <v>26507</v>
+      </c>
+      <c r="H134" s="267">
+        <v>25942</v>
+      </c>
+      <c r="I134" s="267">
+        <v>565</v>
+      </c>
+      <c r="J134" s="268">
+        <f t="shared" si="4"/>
+        <v>2.1315124306786885E-2</v>
+      </c>
+      <c r="K134" s="265"/>
+      <c r="L134" s="265"/>
+      <c r="M134" s="265"/>
+      <c r="N134" s="265"/>
+      <c r="O134" s="265"/>
+      <c r="P134" s="265"/>
+      <c r="Q134" s="265"/>
+      <c r="R134" s="265"/>
+      <c r="S134" s="265"/>
+      <c r="T134" s="265"/>
+    </row>
+    <row r="135" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="266">
+        <v>46295</v>
+      </c>
+      <c r="B135" s="265" t="s">
+        <v>257</v>
+      </c>
+      <c r="C135" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D135" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E135" s="265">
+        <v>30</v>
+      </c>
+      <c r="F135" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G135" s="267">
+        <v>21000</v>
+      </c>
+      <c r="H135" s="267">
+        <v>20550</v>
+      </c>
+      <c r="I135" s="267">
+        <v>450</v>
+      </c>
+      <c r="J135" s="268">
+        <f t="shared" si="4"/>
+        <v>2.1428571428571429E-2</v>
+      </c>
+      <c r="K135" s="265"/>
+      <c r="L135" s="265"/>
+      <c r="M135" s="265"/>
+      <c r="N135" s="265"/>
+      <c r="O135" s="265"/>
+      <c r="P135" s="265"/>
+      <c r="Q135" s="265"/>
+      <c r="R135" s="265"/>
+      <c r="S135" s="265"/>
+      <c r="T135" s="265"/>
+    </row>
+    <row r="136" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="266">
+        <v>46295</v>
+      </c>
+      <c r="B136" s="265" t="s">
+        <v>258</v>
+      </c>
+      <c r="C136" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D136" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E136" s="265">
+        <v>30</v>
+      </c>
+      <c r="F136" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G136" s="267">
+        <v>26180</v>
+      </c>
+      <c r="H136" s="267">
+        <v>26155</v>
+      </c>
+      <c r="I136" s="267">
+        <v>25</v>
+      </c>
+      <c r="J136" s="268">
+        <f t="shared" si="4"/>
+        <v>9.5492742551566085E-4</v>
+      </c>
+      <c r="K136" s="265"/>
+      <c r="L136" s="265"/>
+      <c r="M136" s="265"/>
+      <c r="N136" s="265"/>
+      <c r="O136" s="265"/>
+      <c r="P136" s="265"/>
+      <c r="Q136" s="265"/>
+      <c r="R136" s="265"/>
+      <c r="S136" s="265"/>
+      <c r="T136" s="265"/>
+    </row>
+    <row r="137" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="266">
+        <v>46295</v>
+      </c>
+      <c r="B137" s="265" t="s">
+        <v>259</v>
+      </c>
+      <c r="C137" s="265" t="s">
+        <v>11</v>
+      </c>
+      <c r="D137" s="265" t="s">
+        <v>184</v>
+      </c>
+      <c r="E137" s="265" t="s">
+        <v>141</v>
+      </c>
+      <c r="F137" s="265">
+        <v>8010</v>
+      </c>
+      <c r="G137" s="267">
+        <v>13100</v>
+      </c>
+      <c r="H137" s="267">
+        <v>11500</v>
+      </c>
+      <c r="I137" s="267">
+        <v>1600</v>
+      </c>
+      <c r="J137" s="268">
+        <f t="shared" si="4"/>
+        <v>0.12213740458015267</v>
+      </c>
+      <c r="K137" s="265"/>
+      <c r="L137" s="265"/>
+      <c r="M137" s="265"/>
+      <c r="N137" s="265">
+        <v>150</v>
+      </c>
+      <c r="O137" s="265">
+        <v>240</v>
+      </c>
+      <c r="P137" s="265"/>
+      <c r="Q137" s="265"/>
+      <c r="R137" s="265"/>
+      <c r="S137" s="265"/>
+      <c r="T137" s="265"/>
+    </row>
+    <row r="138" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="266">
+        <v>46295</v>
+      </c>
+      <c r="B138" s="265" t="s">
+        <v>260</v>
+      </c>
+      <c r="C138" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D138" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E138" s="265">
+        <v>30</v>
+      </c>
+      <c r="F138" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G138" s="267">
+        <v>27000</v>
+      </c>
+      <c r="H138" s="267">
+        <v>26835</v>
+      </c>
+      <c r="I138" s="267">
+        <v>165</v>
+      </c>
+      <c r="J138" s="268">
+        <f t="shared" si="4"/>
+        <v>6.1111111111111114E-3</v>
+      </c>
+      <c r="K138" s="265"/>
+      <c r="L138" s="265"/>
+      <c r="M138" s="265"/>
+      <c r="N138" s="265"/>
+      <c r="O138" s="265"/>
+      <c r="P138" s="265"/>
+      <c r="Q138" s="265"/>
+      <c r="R138" s="265"/>
+      <c r="S138" s="265"/>
+      <c r="T138" s="265"/>
+    </row>
+    <row r="139" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="266">
+        <v>46295</v>
+      </c>
+      <c r="B139" s="265" t="s">
+        <v>261</v>
+      </c>
+      <c r="C139" s="265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D139" s="265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E139" s="265">
+        <v>30</v>
+      </c>
+      <c r="F139" s="265">
+        <v>6206</v>
+      </c>
+      <c r="G139" s="267">
+        <v>16120</v>
+      </c>
+      <c r="H139" s="267">
+        <v>15470</v>
+      </c>
+      <c r="I139" s="267">
+        <v>650</v>
+      </c>
+      <c r="J139" s="268">
+        <f t="shared" si="4"/>
+        <v>4.0322580645161289E-2</v>
+      </c>
+      <c r="K139" s="265"/>
+      <c r="L139" s="265"/>
+      <c r="M139" s="265">
+        <v>120</v>
+      </c>
+      <c r="N139" s="265"/>
+      <c r="O139" s="265"/>
+      <c r="P139" s="265"/>
+      <c r="Q139" s="265"/>
+      <c r="R139" s="265"/>
+      <c r="S139" s="265"/>
+      <c r="T139" s="265"/>
+    </row>
+    <row r="140" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="145" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="146" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="147" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -29637,17 +31005,17 @@
       <c r="A1" s="337" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="336"/>
-      <c r="C1" s="336"/>
-      <c r="D1" s="336"/>
-      <c r="E1" s="336"/>
-      <c r="F1" s="336"/>
-      <c r="G1" s="336"/>
-      <c r="H1" s="336"/>
-      <c r="I1" s="336"/>
-      <c r="J1" s="336"/>
-      <c r="K1" s="336"/>
-      <c r="L1" s="336"/>
+      <c r="B1" s="334"/>
+      <c r="C1" s="334"/>
+      <c r="D1" s="334"/>
+      <c r="E1" s="334"/>
+      <c r="F1" s="334"/>
+      <c r="G1" s="334"/>
+      <c r="H1" s="334"/>
+      <c r="I1" s="334"/>
+      <c r="J1" s="334"/>
+      <c r="K1" s="334"/>
+      <c r="L1" s="334"/>
       <c r="M1" s="338"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
@@ -29704,7 +31072,7 @@
         <v>273</v>
       </c>
       <c r="D3" s="197" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E3" s="196">
         <v>13.5</v>
@@ -29746,10 +31114,10 @@
         <v>190</v>
       </c>
       <c r="C4" s="197" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D4" s="197" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E4" s="196">
         <v>16</v>
@@ -29789,10 +31157,10 @@
         <v>190</v>
       </c>
       <c r="C5" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D5" s="201" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E5" s="200">
         <v>16</v>
@@ -29832,10 +31200,10 @@
         <v>190</v>
       </c>
       <c r="C6" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D6" s="201" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E6" s="200">
         <v>16</v>
@@ -29875,10 +31243,10 @@
         <v>190</v>
       </c>
       <c r="C7" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D7" s="201" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E7" s="200">
         <v>16</v>
@@ -29918,10 +31286,10 @@
         <v>190</v>
       </c>
       <c r="C8" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D8" s="201" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E8" s="200">
         <v>16</v>
@@ -29961,10 +31329,10 @@
         <v>190</v>
       </c>
       <c r="C9" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D9" s="201" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E9" s="200">
         <v>16</v>
@@ -30004,10 +31372,10 @@
         <v>190</v>
       </c>
       <c r="C10" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D10" s="201" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E10" s="200">
         <v>16</v>
@@ -30047,10 +31415,10 @@
         <v>190</v>
       </c>
       <c r="C11" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D11" s="201" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E11" s="200">
         <v>16</v>
@@ -30090,10 +31458,10 @@
         <v>190</v>
       </c>
       <c r="C12" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D12" s="201" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E12" s="200">
         <v>16</v>
@@ -30133,10 +31501,10 @@
         <v>189</v>
       </c>
       <c r="C13" s="197" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D13" s="197" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E13" s="196">
         <v>19</v>
@@ -30176,10 +31544,10 @@
         <v>189</v>
       </c>
       <c r="C14" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D14" s="201" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E14" s="200">
         <v>19</v>
@@ -30219,10 +31587,10 @@
         <v>189</v>
       </c>
       <c r="C15" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D15" s="201" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E15" s="200">
         <v>19</v>
@@ -30262,10 +31630,10 @@
         <v>189</v>
       </c>
       <c r="C16" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D16" s="201" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E16" s="200">
         <v>19</v>
@@ -30305,10 +31673,10 @@
         <v>189</v>
       </c>
       <c r="C17" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D17" s="201" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E17" s="200">
         <v>19</v>
@@ -30348,10 +31716,10 @@
         <v>189</v>
       </c>
       <c r="C18" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D18" s="201" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E18" s="200">
         <v>19</v>
@@ -30391,10 +31759,10 @@
         <v>189</v>
       </c>
       <c r="C19" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D19" s="201" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E19" s="200">
         <v>19</v>
@@ -30434,7 +31802,7 @@
         <v>188</v>
       </c>
       <c r="C20" s="197" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D20" s="197" t="s">
         <v>285</v>
@@ -30477,7 +31845,7 @@
         <v>188</v>
       </c>
       <c r="C21" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D21" s="201" t="s">
         <v>285</v>
@@ -30520,7 +31888,7 @@
         <v>188</v>
       </c>
       <c r="C22" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D22" s="201" t="s">
         <v>285</v>
@@ -30563,7 +31931,7 @@
         <v>188</v>
       </c>
       <c r="C23" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D23" s="201" t="s">
         <v>285</v>
@@ -30606,7 +31974,7 @@
         <v>188</v>
       </c>
       <c r="C24" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D24" s="201" t="s">
         <v>285</v>
@@ -30649,7 +32017,7 @@
         <v>188</v>
       </c>
       <c r="C25" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D25" s="201" t="s">
         <v>285</v>
@@ -30692,7 +32060,7 @@
         <v>188</v>
       </c>
       <c r="C26" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D26" s="201" t="s">
         <v>285</v>
@@ -30735,10 +32103,10 @@
         <v>187</v>
       </c>
       <c r="C27" s="197" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D27" s="197" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E27" s="196">
         <v>19</v>
@@ -30778,10 +32146,10 @@
         <v>187</v>
       </c>
       <c r="C28" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D28" s="201" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E28" s="200">
         <v>19</v>
@@ -30821,10 +32189,10 @@
         <v>187</v>
       </c>
       <c r="C29" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D29" s="201" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E29" s="200">
         <v>19</v>
@@ -30864,10 +32232,10 @@
         <v>187</v>
       </c>
       <c r="C30" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D30" s="201" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E30" s="200">
         <v>19</v>
@@ -30907,10 +32275,10 @@
         <v>187</v>
       </c>
       <c r="C31" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D31" s="201" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E31" s="200">
         <v>19</v>
@@ -30950,10 +32318,10 @@
         <v>187</v>
       </c>
       <c r="C32" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D32" s="201" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E32" s="200">
         <v>19</v>
@@ -30993,10 +32361,10 @@
         <v>187</v>
       </c>
       <c r="C33" s="201" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D33" s="201" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E33" s="200">
         <v>19</v>
@@ -31039,7 +32407,7 @@
         <v>13</v>
       </c>
       <c r="D34" s="197" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E34" s="196">
         <v>19</v>
@@ -31082,7 +32450,7 @@
         <v>13</v>
       </c>
       <c r="D35" s="201" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E35" s="200">
         <v>19</v>
@@ -31125,7 +32493,7 @@
         <v>13</v>
       </c>
       <c r="D36" s="201" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E36" s="200">
         <v>19</v>
@@ -31168,7 +32536,7 @@
         <v>13</v>
       </c>
       <c r="D37" s="201" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E37" s="200">
         <v>19</v>
@@ -31211,7 +32579,7 @@
         <v>13</v>
       </c>
       <c r="D38" s="201" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E38" s="200">
         <v>19</v>
@@ -31254,7 +32622,7 @@
         <v>13</v>
       </c>
       <c r="D39" s="201" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E39" s="200">
         <v>19</v>
@@ -31297,7 +32665,7 @@
         <v>13</v>
       </c>
       <c r="D40" s="201" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E40" s="200">
         <v>19</v>
@@ -31340,7 +32708,7 @@
         <v>13</v>
       </c>
       <c r="D41" s="197" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E41" s="196">
         <v>19</v>
@@ -31383,7 +32751,7 @@
         <v>13</v>
       </c>
       <c r="D42" s="201" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E42" s="200">
         <v>19</v>
@@ -31426,7 +32794,7 @@
         <v>13</v>
       </c>
       <c r="D43" s="201" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E43" s="200">
         <v>19</v>
@@ -31469,7 +32837,7 @@
         <v>13</v>
       </c>
       <c r="D44" s="201" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E44" s="200">
         <v>19</v>
@@ -31512,7 +32880,7 @@
         <v>13</v>
       </c>
       <c r="D45" s="201" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E45" s="200">
         <v>19</v>
@@ -31555,7 +32923,7 @@
         <v>13</v>
       </c>
       <c r="D46" s="201" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E46" s="200">
         <v>19</v>
@@ -31598,7 +32966,7 @@
         <v>13</v>
       </c>
       <c r="D47" s="201" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E47" s="200">
         <v>19</v>
@@ -31942,7 +33310,7 @@
         <v>13</v>
       </c>
       <c r="D55" s="197" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E55" s="196">
         <v>20.5</v>
@@ -31985,7 +33353,7 @@
         <v>13</v>
       </c>
       <c r="D56" s="201" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E56" s="200">
         <v>20.5</v>
@@ -32028,7 +33396,7 @@
         <v>13</v>
       </c>
       <c r="D57" s="201" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E57" s="200">
         <v>20.5</v>
@@ -32071,7 +33439,7 @@
         <v>13</v>
       </c>
       <c r="D58" s="201" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E58" s="200">
         <v>20.5</v>
@@ -32114,7 +33482,7 @@
         <v>13</v>
       </c>
       <c r="D59" s="201" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E59" s="200">
         <v>20.5</v>
@@ -32157,7 +33525,7 @@
         <v>13</v>
       </c>
       <c r="D60" s="201" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E60" s="200">
         <v>20.5</v>
@@ -32200,7 +33568,7 @@
         <v>13</v>
       </c>
       <c r="D61" s="201" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E61" s="200">
         <v>20.5</v>
@@ -32243,7 +33611,7 @@
         <v>13</v>
       </c>
       <c r="D62" s="197" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E62" s="196">
         <v>20.5</v>
@@ -32286,7 +33654,7 @@
         <v>13</v>
       </c>
       <c r="D63" s="201" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E63" s="200">
         <v>20.5</v>
@@ -32329,7 +33697,7 @@
         <v>13</v>
       </c>
       <c r="D64" s="201" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E64" s="200">
         <v>20.5</v>
@@ -32372,7 +33740,7 @@
         <v>13</v>
       </c>
       <c r="D65" s="201" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E65" s="200">
         <v>20.5</v>
@@ -32415,7 +33783,7 @@
         <v>13</v>
       </c>
       <c r="D66" s="201" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E66" s="200">
         <v>20.5</v>
@@ -32458,7 +33826,7 @@
         <v>13</v>
       </c>
       <c r="D67" s="201" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E67" s="200">
         <v>20.5</v>
@@ -32501,7 +33869,7 @@
         <v>13</v>
       </c>
       <c r="D68" s="201" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E68" s="200">
         <v>20.5</v>
@@ -32544,7 +33912,7 @@
         <v>13</v>
       </c>
       <c r="D69" s="197" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E69" s="196">
         <v>20.5</v>
@@ -32587,7 +33955,7 @@
         <v>13</v>
       </c>
       <c r="D70" s="201" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E70" s="200">
         <v>20.5</v>
@@ -32630,7 +33998,7 @@
         <v>13</v>
       </c>
       <c r="D71" s="201" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E71" s="200">
         <v>20.5</v>
@@ -32673,7 +34041,7 @@
         <v>13</v>
       </c>
       <c r="D72" s="201" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E72" s="200">
         <v>20.5</v>
@@ -32716,7 +34084,7 @@
         <v>13</v>
       </c>
       <c r="D73" s="201" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E73" s="200">
         <v>20.5</v>
@@ -32759,7 +34127,7 @@
         <v>13</v>
       </c>
       <c r="D74" s="201" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E74" s="200">
         <v>20.5</v>
@@ -32802,7 +34170,7 @@
         <v>13</v>
       </c>
       <c r="D75" s="201" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E75" s="200">
         <v>20.5</v>
@@ -32845,7 +34213,7 @@
         <v>13</v>
       </c>
       <c r="D76" s="197" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E76" s="196">
         <v>20.5</v>
@@ -32888,7 +34256,7 @@
         <v>13</v>
       </c>
       <c r="D77" s="201" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E77" s="200">
         <v>20.5</v>
@@ -32931,7 +34299,7 @@
         <v>13</v>
       </c>
       <c r="D78" s="201" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E78" s="200">
         <v>20.5</v>
@@ -32974,7 +34342,7 @@
         <v>13</v>
       </c>
       <c r="D79" s="201" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E79" s="200">
         <v>20.5</v>
@@ -33017,7 +34385,7 @@
         <v>13</v>
       </c>
       <c r="D80" s="201" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E80" s="200">
         <v>20.5</v>
@@ -33060,7 +34428,7 @@
         <v>13</v>
       </c>
       <c r="D81" s="201" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E81" s="200">
         <v>20.5</v>
@@ -33103,7 +34471,7 @@
         <v>13</v>
       </c>
       <c r="D82" s="201" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E82" s="200">
         <v>20.5</v>
@@ -33146,7 +34514,7 @@
         <v>13</v>
       </c>
       <c r="D83" s="197" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E83" s="196">
         <v>20.5</v>
@@ -33189,7 +34557,7 @@
         <v>13</v>
       </c>
       <c r="D84" s="201" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E84" s="200">
         <v>20.5</v>
@@ -33232,7 +34600,7 @@
         <v>13</v>
       </c>
       <c r="D85" s="201" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E85" s="200">
         <v>20.5</v>
@@ -33275,7 +34643,7 @@
         <v>13</v>
       </c>
       <c r="D86" s="201" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E86" s="200">
         <v>20.5</v>
@@ -33318,7 +34686,7 @@
         <v>13</v>
       </c>
       <c r="D87" s="201" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E87" s="200">
         <v>20.5</v>
@@ -33361,7 +34729,7 @@
         <v>13</v>
       </c>
       <c r="D88" s="201" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E88" s="200">
         <v>20.5</v>
@@ -33404,7 +34772,7 @@
         <v>13</v>
       </c>
       <c r="D89" s="201" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E89" s="200">
         <v>20.5</v>
@@ -33447,7 +34815,7 @@
         <v>13</v>
       </c>
       <c r="D90" s="197" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E90" s="196">
         <v>20.5</v>
@@ -33490,7 +34858,7 @@
         <v>13</v>
       </c>
       <c r="D91" s="201" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E91" s="200">
         <v>20.5</v>
@@ -33533,7 +34901,7 @@
         <v>13</v>
       </c>
       <c r="D92" s="201" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E92" s="200">
         <v>20.5</v>
@@ -33576,7 +34944,7 @@
         <v>13</v>
       </c>
       <c r="D93" s="201" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E93" s="200">
         <v>20.5</v>
@@ -33619,7 +34987,7 @@
         <v>13</v>
       </c>
       <c r="D94" s="201" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E94" s="200">
         <v>20.5</v>
@@ -33662,7 +35030,7 @@
         <v>13</v>
       </c>
       <c r="D95" s="201" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E95" s="200">
         <v>20.5</v>
@@ -33705,7 +35073,7 @@
         <v>13</v>
       </c>
       <c r="D96" s="201" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E96" s="200">
         <v>20.5</v>
@@ -33745,10 +35113,10 @@
         <v>167</v>
       </c>
       <c r="C97" s="197" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D97" s="197" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E97" s="196">
         <v>25</v>
@@ -33788,10 +35156,10 @@
         <v>167</v>
       </c>
       <c r="C98" s="201" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D98" s="201" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E98" s="200">
         <v>25</v>
@@ -33831,10 +35199,10 @@
         <v>167</v>
       </c>
       <c r="C99" s="201" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D99" s="201" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E99" s="200">
         <v>25</v>
@@ -33874,10 +35242,10 @@
         <v>167</v>
       </c>
       <c r="C100" s="201" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D100" s="201" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E100" s="200">
         <v>25</v>
@@ -33917,10 +35285,10 @@
         <v>167</v>
       </c>
       <c r="C101" s="201" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D101" s="201" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E101" s="200">
         <v>25</v>
@@ -33960,10 +35328,10 @@
         <v>167</v>
       </c>
       <c r="C102" s="201" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D102" s="201" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E102" s="200">
         <v>25</v>
@@ -34003,10 +35371,10 @@
         <v>167</v>
       </c>
       <c r="C103" s="201" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D103" s="201" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E103" s="200">
         <v>25</v>
@@ -34390,10 +35758,10 @@
         <v>20</v>
       </c>
       <c r="C112" s="197" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D112" s="197" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E112" s="196">
         <v>25</v>
@@ -34433,10 +35801,10 @@
         <v>20</v>
       </c>
       <c r="C113" s="201" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D113" s="201" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E113" s="200">
         <v>25</v>
@@ -34476,10 +35844,10 @@
         <v>20</v>
       </c>
       <c r="C114" s="201" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D114" s="201" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E114" s="200">
         <v>25</v>
@@ -34519,10 +35887,10 @@
         <v>20</v>
       </c>
       <c r="C115" s="201" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D115" s="201" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E115" s="200">
         <v>25</v>
@@ -34562,10 +35930,10 @@
         <v>20</v>
       </c>
       <c r="C116" s="201" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D116" s="201" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E116" s="200">
         <v>25</v>
@@ -34605,10 +35973,10 @@
         <v>20</v>
       </c>
       <c r="C117" s="201" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D117" s="201" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E117" s="200">
         <v>25</v>
@@ -34648,10 +36016,10 @@
         <v>20</v>
       </c>
       <c r="C118" s="201" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D118" s="201" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E118" s="200">
         <v>25</v>
@@ -34694,7 +36062,7 @@
         <v>13</v>
       </c>
       <c r="D119" s="197" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E119" s="196">
         <v>25</v>
@@ -34737,7 +36105,7 @@
         <v>13</v>
       </c>
       <c r="D120" s="201" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E120" s="200">
         <v>25</v>
@@ -34780,7 +36148,7 @@
         <v>13</v>
       </c>
       <c r="D121" s="201" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E121" s="200">
         <v>25</v>
@@ -34823,7 +36191,7 @@
         <v>13</v>
       </c>
       <c r="D122" s="201" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E122" s="200">
         <v>25</v>
@@ -34866,7 +36234,7 @@
         <v>13</v>
       </c>
       <c r="D123" s="201" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E123" s="200">
         <v>25</v>
@@ -34909,7 +36277,7 @@
         <v>13</v>
       </c>
       <c r="D124" s="201" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E124" s="200">
         <v>25</v>
@@ -34952,7 +36320,7 @@
         <v>13</v>
       </c>
       <c r="D125" s="201" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E125" s="200">
         <v>25</v>
@@ -34995,7 +36363,7 @@
         <v>13</v>
       </c>
       <c r="D126" s="197" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E126" s="196">
         <v>25</v>
@@ -35038,7 +36406,7 @@
         <v>13</v>
       </c>
       <c r="D127" s="201" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E127" s="200">
         <v>25</v>
@@ -35081,7 +36449,7 @@
         <v>13</v>
       </c>
       <c r="D128" s="201" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E128" s="200">
         <v>25</v>
@@ -35124,7 +36492,7 @@
         <v>13</v>
       </c>
       <c r="D129" s="201" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E129" s="200">
         <v>25</v>
@@ -35167,7 +36535,7 @@
         <v>13</v>
       </c>
       <c r="D130" s="201" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E130" s="200">
         <v>25</v>
@@ -35210,7 +36578,7 @@
         <v>13</v>
       </c>
       <c r="D131" s="201" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E131" s="200">
         <v>25</v>
@@ -35253,7 +36621,7 @@
         <v>13</v>
       </c>
       <c r="D132" s="201" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E132" s="200">
         <v>25</v>
@@ -35296,7 +36664,7 @@
         <v>13</v>
       </c>
       <c r="D133" s="197" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E133" s="196">
         <v>25</v>
@@ -35339,7 +36707,7 @@
         <v>13</v>
       </c>
       <c r="D134" s="201" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E134" s="200">
         <v>25</v>
@@ -35382,7 +36750,7 @@
         <v>13</v>
       </c>
       <c r="D135" s="201" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E135" s="200">
         <v>25</v>
@@ -35425,7 +36793,7 @@
         <v>13</v>
       </c>
       <c r="D136" s="201" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E136" s="200">
         <v>25</v>
@@ -35468,7 +36836,7 @@
         <v>13</v>
       </c>
       <c r="D137" s="201" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E137" s="200">
         <v>25</v>
@@ -35511,7 +36879,7 @@
         <v>13</v>
       </c>
       <c r="D138" s="201" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E138" s="200">
         <v>25</v>
@@ -35554,7 +36922,7 @@
         <v>13</v>
       </c>
       <c r="D139" s="201" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E139" s="200">
         <v>25</v>
@@ -35597,7 +36965,7 @@
         <v>13</v>
       </c>
       <c r="D140" s="197" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E140" s="196">
         <v>25</v>
@@ -35640,7 +37008,7 @@
         <v>13</v>
       </c>
       <c r="D141" s="201" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E141" s="200">
         <v>25</v>
@@ -35683,7 +37051,7 @@
         <v>13</v>
       </c>
       <c r="D142" s="201" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E142" s="200">
         <v>25</v>
@@ -35726,7 +37094,7 @@
         <v>13</v>
       </c>
       <c r="D143" s="201" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E143" s="200">
         <v>25</v>
@@ -35769,7 +37137,7 @@
         <v>13</v>
       </c>
       <c r="D144" s="201" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E144" s="200">
         <v>25</v>
@@ -35812,7 +37180,7 @@
         <v>13</v>
       </c>
       <c r="D145" s="201" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E145" s="200">
         <v>25</v>
@@ -35855,7 +37223,7 @@
         <v>13</v>
       </c>
       <c r="D146" s="201" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E146" s="200">
         <v>25</v>
@@ -36285,7 +37653,7 @@
         <v>13</v>
       </c>
       <c r="D156" s="197" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E156" s="196">
         <v>25</v>
@@ -36328,7 +37696,7 @@
         <v>13</v>
       </c>
       <c r="D157" s="201" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E157" s="200">
         <v>25</v>
@@ -36371,7 +37739,7 @@
         <v>13</v>
       </c>
       <c r="D158" s="201" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E158" s="200">
         <v>25</v>
@@ -36414,7 +37782,7 @@
         <v>13</v>
       </c>
       <c r="D159" s="201" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E159" s="200">
         <v>25</v>
@@ -36457,7 +37825,7 @@
         <v>13</v>
       </c>
       <c r="D160" s="201" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E160" s="200">
         <v>25</v>
@@ -36500,7 +37868,7 @@
         <v>13</v>
       </c>
       <c r="D161" s="201" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E161" s="200">
         <v>25</v>
@@ -36543,7 +37911,7 @@
         <v>13</v>
       </c>
       <c r="D162" s="201" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E162" s="200">
         <v>25</v>
@@ -36583,10 +37951,10 @@
         <v>166</v>
       </c>
       <c r="C163" s="197" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D163" s="197" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E163" s="196">
         <v>30</v>
@@ -36628,10 +37996,10 @@
         <v>166</v>
       </c>
       <c r="C164" s="201" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D164" s="201" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E164" s="200">
         <v>30</v>
@@ -36671,10 +38039,10 @@
         <v>166</v>
       </c>
       <c r="C165" s="201" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D165" s="201" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E165" s="200">
         <v>30</v>
@@ -36714,10 +38082,10 @@
         <v>166</v>
       </c>
       <c r="C166" s="201" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D166" s="201" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E166" s="200">
         <v>30</v>
@@ -36757,10 +38125,10 @@
         <v>166</v>
       </c>
       <c r="C167" s="201" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D167" s="201" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E167" s="200">
         <v>30</v>
@@ -36800,10 +38168,10 @@
         <v>166</v>
       </c>
       <c r="C168" s="201" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D168" s="201" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E168" s="200">
         <v>30</v>
@@ -36843,10 +38211,10 @@
         <v>166</v>
       </c>
       <c r="C169" s="201" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D169" s="201" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E169" s="200">
         <v>30</v>
@@ -36886,10 +38254,10 @@
         <v>166</v>
       </c>
       <c r="C170" s="201" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D170" s="201" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E170" s="200">
         <v>30</v>
@@ -36929,10 +38297,10 @@
         <v>171</v>
       </c>
       <c r="C171" s="197" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D171" s="197" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E171" s="196">
         <v>30</v>
@@ -36974,10 +38342,10 @@
         <v>171</v>
       </c>
       <c r="C172" s="201" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D172" s="201" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E172" s="200">
         <v>30</v>
@@ -37017,10 +38385,10 @@
         <v>171</v>
       </c>
       <c r="C173" s="201" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D173" s="201" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E173" s="200">
         <v>30</v>
@@ -37060,10 +38428,10 @@
         <v>171</v>
       </c>
       <c r="C174" s="201" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D174" s="201" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E174" s="200">
         <v>30</v>
@@ -37103,10 +38471,10 @@
         <v>171</v>
       </c>
       <c r="C175" s="201" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D175" s="201" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E175" s="200">
         <v>30</v>
@@ -37146,10 +38514,10 @@
         <v>171</v>
       </c>
       <c r="C176" s="201" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D176" s="201" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E176" s="200">
         <v>30</v>
@@ -37189,10 +38557,10 @@
         <v>171</v>
       </c>
       <c r="C177" s="201" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D177" s="201" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E177" s="200">
         <v>30</v>
@@ -37232,10 +38600,10 @@
         <v>171</v>
       </c>
       <c r="C178" s="201" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D178" s="201" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E178" s="200">
         <v>30</v>
@@ -37967,10 +39335,10 @@
         <v>146</v>
       </c>
       <c r="C195" s="197" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D195" s="197" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E195" s="196">
         <v>30</v>
@@ -38012,10 +39380,10 @@
         <v>146</v>
       </c>
       <c r="C196" s="201" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D196" s="201" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E196" s="200">
         <v>30</v>
@@ -38055,10 +39423,10 @@
         <v>146</v>
       </c>
       <c r="C197" s="201" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D197" s="201" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E197" s="200">
         <v>30</v>
@@ -38098,10 +39466,10 @@
         <v>146</v>
       </c>
       <c r="C198" s="201" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D198" s="201" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E198" s="200">
         <v>30</v>
@@ -38141,10 +39509,10 @@
         <v>146</v>
       </c>
       <c r="C199" s="201" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D199" s="201" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E199" s="200">
         <v>30</v>
@@ -38184,10 +39552,10 @@
         <v>146</v>
       </c>
       <c r="C200" s="201" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D200" s="201" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E200" s="200">
         <v>30</v>
@@ -38227,10 +39595,10 @@
         <v>146</v>
       </c>
       <c r="C201" s="201" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D201" s="201" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E201" s="200">
         <v>30</v>
@@ -38270,10 +39638,10 @@
         <v>146</v>
       </c>
       <c r="C202" s="201" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D202" s="201" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E202" s="200">
         <v>30</v>
@@ -38313,10 +39681,10 @@
         <v>146</v>
       </c>
       <c r="C203" s="201" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D203" s="201" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E203" s="200">
         <v>30</v>
@@ -38359,7 +39727,7 @@
         <v>303</v>
       </c>
       <c r="D204" s="197" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E204" s="196">
         <v>30</v>
@@ -38404,7 +39772,7 @@
         <v>303</v>
       </c>
       <c r="D205" s="201" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E205" s="200">
         <v>30</v>
@@ -38447,7 +39815,7 @@
         <v>303</v>
       </c>
       <c r="D206" s="201" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E206" s="200">
         <v>30</v>
@@ -38490,7 +39858,7 @@
         <v>303</v>
       </c>
       <c r="D207" s="201" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E207" s="200">
         <v>30</v>
@@ -38533,7 +39901,7 @@
         <v>303</v>
       </c>
       <c r="D208" s="201" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E208" s="200">
         <v>30</v>
@@ -38576,7 +39944,7 @@
         <v>303</v>
       </c>
       <c r="D209" s="201" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E209" s="200">
         <v>30</v>
@@ -38616,10 +39984,10 @@
         <v>19</v>
       </c>
       <c r="C210" s="197" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D210" s="197" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E210" s="196">
         <v>30</v>
@@ -38661,10 +40029,10 @@
         <v>19</v>
       </c>
       <c r="C211" s="201" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D211" s="201" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E211" s="200">
         <v>30</v>
@@ -38704,10 +40072,10 @@
         <v>19</v>
       </c>
       <c r="C212" s="201" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D212" s="201" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E212" s="200">
         <v>30</v>
@@ -38747,10 +40115,10 @@
         <v>19</v>
       </c>
       <c r="C213" s="201" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D213" s="201" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E213" s="200">
         <v>30</v>
@@ -38790,10 +40158,10 @@
         <v>19</v>
       </c>
       <c r="C214" s="201" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D214" s="201" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E214" s="200">
         <v>30</v>
@@ -38833,10 +40201,10 @@
         <v>19</v>
       </c>
       <c r="C215" s="201" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D215" s="201" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E215" s="200">
         <v>30</v>
@@ -38876,10 +40244,10 @@
         <v>19</v>
       </c>
       <c r="C216" s="201" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D216" s="201" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E216" s="200">
         <v>30</v>
@@ -38919,10 +40287,10 @@
         <v>19</v>
       </c>
       <c r="C217" s="201" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D217" s="201" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E217" s="200">
         <v>30</v>
@@ -38962,10 +40330,10 @@
         <v>157</v>
       </c>
       <c r="C218" s="197" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D218" s="197" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E218" s="196">
         <v>30</v>
@@ -39007,10 +40375,10 @@
         <v>157</v>
       </c>
       <c r="C219" s="201" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D219" s="201" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E219" s="200">
         <v>30</v>
@@ -39050,10 +40418,10 @@
         <v>157</v>
       </c>
       <c r="C220" s="201" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D220" s="201" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E220" s="200">
         <v>30</v>
@@ -39093,10 +40461,10 @@
         <v>157</v>
       </c>
       <c r="C221" s="201" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D221" s="201" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E221" s="200">
         <v>30</v>
@@ -39136,10 +40504,10 @@
         <v>157</v>
       </c>
       <c r="C222" s="201" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D222" s="201" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E222" s="200">
         <v>30</v>
@@ -39179,10 +40547,10 @@
         <v>157</v>
       </c>
       <c r="C223" s="201" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D223" s="201" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E223" s="200">
         <v>30</v>
@@ -39222,10 +40590,10 @@
         <v>191</v>
       </c>
       <c r="C224" s="197" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D224" s="197" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E224" s="196">
         <v>30</v>
@@ -39267,10 +40635,10 @@
         <v>191</v>
       </c>
       <c r="C225" s="201" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D225" s="201" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E225" s="200">
         <v>30</v>
@@ -39310,10 +40678,10 @@
         <v>191</v>
       </c>
       <c r="C226" s="201" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D226" s="201" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E226" s="200">
         <v>30</v>
@@ -39353,10 +40721,10 @@
         <v>191</v>
       </c>
       <c r="C227" s="201" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D227" s="201" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E227" s="200">
         <v>30</v>
@@ -39396,10 +40764,10 @@
         <v>191</v>
       </c>
       <c r="C228" s="201" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D228" s="201" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E228" s="200">
         <v>30</v>
@@ -39439,10 +40807,10 @@
         <v>191</v>
       </c>
       <c r="C229" s="201" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D229" s="201" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E229" s="200">
         <v>30</v>
@@ -39482,10 +40850,10 @@
         <v>191</v>
       </c>
       <c r="C230" s="201" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D230" s="201" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E230" s="200">
         <v>30</v>
@@ -39525,10 +40893,10 @@
         <v>191</v>
       </c>
       <c r="C231" s="201" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D231" s="201" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E231" s="200">
         <v>30</v>
@@ -40256,10 +41624,10 @@
         <v>130</v>
       </c>
       <c r="C248" s="197" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D248" s="197" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E248" s="196">
         <v>35</v>
@@ -40299,10 +41667,10 @@
         <v>130</v>
       </c>
       <c r="C249" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D249" s="201" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E249" s="200">
         <v>35</v>
@@ -40342,10 +41710,10 @@
         <v>130</v>
       </c>
       <c r="C250" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D250" s="201" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E250" s="200">
         <v>35</v>
@@ -40385,10 +41753,10 @@
         <v>130</v>
       </c>
       <c r="C251" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D251" s="201" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E251" s="200">
         <v>35</v>
@@ -40428,10 +41796,10 @@
         <v>130</v>
       </c>
       <c r="C252" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D252" s="201" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E252" s="200">
         <v>35</v>
@@ -40471,10 +41839,10 @@
         <v>130</v>
       </c>
       <c r="C253" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D253" s="201" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E253" s="200">
         <v>35</v>
@@ -40514,10 +41882,10 @@
         <v>130</v>
       </c>
       <c r="C254" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D254" s="201" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E254" s="200">
         <v>35</v>
@@ -40557,10 +41925,10 @@
         <v>130</v>
       </c>
       <c r="C255" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D255" s="201" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E255" s="200">
         <v>35</v>
@@ -40600,10 +41968,10 @@
         <v>130</v>
       </c>
       <c r="C256" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D256" s="201" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E256" s="200">
         <v>35</v>
@@ -40643,10 +42011,10 @@
         <v>131</v>
       </c>
       <c r="C257" s="197" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D257" s="197" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E257" s="196">
         <v>35</v>
@@ -40686,10 +42054,10 @@
         <v>131</v>
       </c>
       <c r="C258" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D258" s="201" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E258" s="200">
         <v>35</v>
@@ -40729,10 +42097,10 @@
         <v>131</v>
       </c>
       <c r="C259" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D259" s="201" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E259" s="200">
         <v>35</v>
@@ -40772,10 +42140,10 @@
         <v>131</v>
       </c>
       <c r="C260" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D260" s="201" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E260" s="200">
         <v>35</v>
@@ -40815,10 +42183,10 @@
         <v>131</v>
       </c>
       <c r="C261" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D261" s="201" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E261" s="200">
         <v>35</v>
@@ -40858,10 +42226,10 @@
         <v>131</v>
       </c>
       <c r="C262" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D262" s="201" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E262" s="200">
         <v>35</v>
@@ -40901,10 +42269,10 @@
         <v>131</v>
       </c>
       <c r="C263" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D263" s="201" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E263" s="200">
         <v>35</v>
@@ -40944,10 +42312,10 @@
         <v>131</v>
       </c>
       <c r="C264" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D264" s="201" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E264" s="200">
         <v>35</v>
@@ -40987,10 +42355,10 @@
         <v>131</v>
       </c>
       <c r="C265" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D265" s="201" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E265" s="200">
         <v>35</v>
@@ -41030,10 +42398,10 @@
         <v>182</v>
       </c>
       <c r="C266" s="197" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D266" s="197" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E266" s="196">
         <v>35</v>
@@ -41073,10 +42441,10 @@
         <v>182</v>
       </c>
       <c r="C267" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D267" s="201" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E267" s="200">
         <v>35</v>
@@ -41116,10 +42484,10 @@
         <v>182</v>
       </c>
       <c r="C268" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D268" s="201" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E268" s="200">
         <v>35</v>
@@ -41159,10 +42527,10 @@
         <v>182</v>
       </c>
       <c r="C269" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D269" s="201" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E269" s="200">
         <v>35</v>
@@ -41202,10 +42570,10 @@
         <v>182</v>
       </c>
       <c r="C270" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D270" s="201" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E270" s="200">
         <v>35</v>
@@ -41245,10 +42613,10 @@
         <v>182</v>
       </c>
       <c r="C271" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D271" s="201" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E271" s="200">
         <v>35</v>
@@ -41288,10 +42656,10 @@
         <v>182</v>
       </c>
       <c r="C272" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D272" s="201" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E272" s="200">
         <v>35</v>
@@ -41331,10 +42699,10 @@
         <v>183</v>
       </c>
       <c r="C273" s="197" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D273" s="197" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E273" s="196">
         <v>35</v>
@@ -41374,10 +42742,10 @@
         <v>183</v>
       </c>
       <c r="C274" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D274" s="201" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E274" s="200">
         <v>35</v>
@@ -41417,10 +42785,10 @@
         <v>183</v>
       </c>
       <c r="C275" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D275" s="201" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E275" s="200">
         <v>35</v>
@@ -41460,10 +42828,10 @@
         <v>183</v>
       </c>
       <c r="C276" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D276" s="201" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E276" s="200">
         <v>35</v>
@@ -41503,10 +42871,10 @@
         <v>183</v>
       </c>
       <c r="C277" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D277" s="201" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E277" s="200">
         <v>35</v>
@@ -41546,10 +42914,10 @@
         <v>183</v>
       </c>
       <c r="C278" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D278" s="201" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E278" s="200">
         <v>35</v>
@@ -41585,10 +42953,10 @@
         <v>183</v>
       </c>
       <c r="C279" s="201" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D279" s="201" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E279" s="200">
         <v>35</v>
@@ -41836,7 +43204,7 @@
         <v>13</v>
       </c>
       <c r="D285" s="197" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E285" s="196" t="s">
         <v>138</v>
@@ -41879,7 +43247,7 @@
         <v>13</v>
       </c>
       <c r="D286" s="201" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E286" s="200" t="s">
         <v>138</v>
@@ -41922,7 +43290,7 @@
         <v>13</v>
       </c>
       <c r="D287" s="201" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E287" s="200" t="s">
         <v>138</v>
@@ -41965,7 +43333,7 @@
         <v>13</v>
       </c>
       <c r="D288" s="201" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E288" s="200" t="s">
         <v>138</v>
@@ -42180,7 +43548,7 @@
         <v>13</v>
       </c>
       <c r="D293" s="197" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E293" s="196" t="s">
         <v>138</v>
@@ -42223,7 +43591,7 @@
         <v>13</v>
       </c>
       <c r="D294" s="201" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E294" s="200" t="s">
         <v>138</v>
@@ -42262,7 +43630,7 @@
         <v>13</v>
       </c>
       <c r="D295" s="201" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E295" s="200" t="s">
         <v>138</v>
@@ -42301,7 +43669,7 @@
         <v>13</v>
       </c>
       <c r="D296" s="201" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E296" s="200" t="s">
         <v>138</v>
@@ -42590,7 +43958,7 @@
         <v>11</v>
       </c>
       <c r="D303" s="197" t="s">
-        <v>230</v>
+        <v>184</v>
       </c>
       <c r="E303" s="196" t="s">
         <v>141</v>
@@ -42633,7 +44001,7 @@
         <v>11</v>
       </c>
       <c r="D304" s="201" t="s">
-        <v>230</v>
+        <v>184</v>
       </c>
       <c r="E304" s="200" t="s">
         <v>141</v>
@@ -42676,7 +44044,7 @@
         <v>11</v>
       </c>
       <c r="D305" s="201" t="s">
-        <v>230</v>
+        <v>184</v>
       </c>
       <c r="E305" s="200" t="s">
         <v>141</v>
@@ -42719,7 +44087,7 @@
         <v>11</v>
       </c>
       <c r="D306" s="201" t="s">
-        <v>230</v>
+        <v>184</v>
       </c>
       <c r="E306" s="200" t="s">
         <v>141</v>
@@ -42762,7 +44130,7 @@
         <v>11</v>
       </c>
       <c r="D307" s="201" t="s">
-        <v>230</v>
+        <v>184</v>
       </c>
       <c r="E307" s="200" t="s">
         <v>141</v>
@@ -42805,7 +44173,7 @@
         <v>135</v>
       </c>
       <c r="D308" s="197" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E308" s="196" t="s">
         <v>143</v>
@@ -42848,7 +44216,7 @@
         <v>135</v>
       </c>
       <c r="D309" s="201" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E309" s="200" t="s">
         <v>143</v>
@@ -42891,7 +44259,7 @@
         <v>135</v>
       </c>
       <c r="D310" s="201" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E310" s="200" t="s">
         <v>143</v>
@@ -42934,7 +44302,7 @@
         <v>135</v>
       </c>
       <c r="D311" s="201" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E311" s="200" t="s">
         <v>143</v>
@@ -42977,7 +44345,7 @@
         <v>135</v>
       </c>
       <c r="D312" s="201" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E312" s="200" t="s">
         <v>143</v>
@@ -43017,7 +44385,7 @@
         <v>817</v>
       </c>
       <c r="C313" s="197" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D313" s="197" t="s">
         <v>144</v>
@@ -43060,7 +44428,7 @@
         <v>817</v>
       </c>
       <c r="C314" s="201" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D314" s="201" t="s">
         <v>144</v>
@@ -43103,7 +44471,7 @@
         <v>817</v>
       </c>
       <c r="C315" s="201" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D315" s="201" t="s">
         <v>144</v>
@@ -43146,7 +44514,7 @@
         <v>817</v>
       </c>
       <c r="C316" s="201" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D316" s="201" t="s">
         <v>144</v>
@@ -43189,7 +44557,7 @@
         <v>817</v>
       </c>
       <c r="C317" s="201" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D317" s="201" t="s">
         <v>144</v>
@@ -44543,13 +45911,13 @@
       <c r="A1" s="339" t="s">
         <v>314</v>
       </c>
-      <c r="B1" s="336"/>
-      <c r="C1" s="336"/>
-      <c r="D1" s="336"/>
-      <c r="E1" s="336"/>
-      <c r="F1" s="336"/>
-      <c r="G1" s="336"/>
-      <c r="H1" s="336"/>
+      <c r="B1" s="334"/>
+      <c r="C1" s="334"/>
+      <c r="D1" s="334"/>
+      <c r="E1" s="334"/>
+      <c r="F1" s="334"/>
+      <c r="G1" s="334"/>
+      <c r="H1" s="334"/>
       <c r="I1" s="45" t="s">
         <v>1</v>
       </c>
@@ -48581,10 +49949,10 @@
         <v>904</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D3" s="40" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E3" s="39">
         <v>12.5</v>
@@ -48639,10 +50007,10 @@
         <v>190</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D4" s="40" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E4" s="39">
         <v>16</v>
@@ -48697,10 +50065,10 @@
         <v>187</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D5" s="40" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E5" s="39">
         <v>19</v>
@@ -48755,7 +50123,7 @@
         <v>188</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D6" s="40" t="s">
         <v>285</v>
@@ -48813,10 +50181,10 @@
         <v>189</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E7" s="39">
         <v>19</v>
@@ -48874,7 +50242,7 @@
         <v>13</v>
       </c>
       <c r="D8" s="40" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E8" s="39">
         <v>19</v>
@@ -48928,7 +50296,7 @@
         <v>13</v>
       </c>
       <c r="D9" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E9" s="39">
         <v>19</v>
@@ -49044,7 +50412,7 @@
         <v>13</v>
       </c>
       <c r="D11" s="40" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E11" s="39">
         <v>20.5</v>
@@ -49102,7 +50470,7 @@
         <v>13</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E12" s="39">
         <v>20.5</v>
@@ -49160,7 +50528,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E13" s="39">
         <v>20.5</v>
@@ -49218,7 +50586,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="40" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E14" s="39">
         <v>20.5</v>
@@ -49276,7 +50644,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="40" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E15" s="39">
         <v>20.5</v>
@@ -49334,7 +50702,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E16" s="39">
         <v>20.5</v>
@@ -49450,7 +50818,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="40" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E18" s="39">
         <v>25</v>
@@ -49508,7 +50876,7 @@
         <v>13</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E19" s="39">
         <v>25</v>
@@ -49624,7 +50992,7 @@
         <v>13</v>
       </c>
       <c r="D21" s="40" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E21" s="39">
         <v>25</v>
@@ -49682,7 +51050,7 @@
         <v>13</v>
       </c>
       <c r="D22" s="40" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E22" s="39">
         <v>25</v>
@@ -49739,10 +51107,10 @@
         <v>167</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D23" s="40" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E23" s="39">
         <v>25</v>
@@ -49797,10 +51165,10 @@
         <v>166</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D24" s="40" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E24" s="39">
         <v>30</v>
@@ -49855,10 +51223,10 @@
         <v>171</v>
       </c>
       <c r="C25" s="39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D25" s="40" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E25" s="39">
         <v>30</v>
@@ -50032,7 +51400,7 @@
         <v>11</v>
       </c>
       <c r="D28" s="40" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E28" s="39">
         <v>30</v>
@@ -50087,10 +51455,10 @@
         <v>19</v>
       </c>
       <c r="C29" s="39" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D29" s="40" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E29" s="39">
         <v>30</v>
@@ -50145,10 +51513,10 @@
         <v>157</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D30" s="40" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E30" s="39">
         <v>30</v>
@@ -50203,10 +51571,10 @@
         <v>191</v>
       </c>
       <c r="C31" s="39" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D31" s="40" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E31" s="39">
         <v>30</v>
@@ -50377,10 +51745,10 @@
         <v>130</v>
       </c>
       <c r="C34" s="39" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D34" s="40" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E34" s="39">
         <v>35</v>
@@ -50435,10 +51803,10 @@
         <v>131</v>
       </c>
       <c r="C35" s="39" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D35" s="40" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E35" s="39">
         <v>35</v>
@@ -50493,10 +51861,10 @@
         <v>182</v>
       </c>
       <c r="C36" s="39" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D36" s="40" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E36" s="39">
         <v>35</v>
@@ -50551,10 +51919,10 @@
         <v>183</v>
       </c>
       <c r="C37" s="39" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D37" s="40" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E37" s="39">
         <v>35</v>
@@ -50672,7 +52040,7 @@
         <v>13</v>
       </c>
       <c r="D39" s="40" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E39" s="39" t="s">
         <v>138</v>
@@ -50730,7 +52098,7 @@
         <v>13</v>
       </c>
       <c r="D40" s="40" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E40" s="39" t="s">
         <v>138</v>
@@ -50788,7 +52156,7 @@
         <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>230</v>
+        <v>184</v>
       </c>
       <c r="E41" s="39" t="s">
         <v>141</v>
@@ -50896,7 +52264,7 @@
         <v>135</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E43" s="39" t="s">
         <v>143</v>
@@ -51359,10 +52727,10 @@
         <v>56</v>
       </c>
       <c r="C51" s="39" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D51" s="40" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E51" s="39">
         <v>30</v>
@@ -51417,10 +52785,10 @@
         <v>20</v>
       </c>
       <c r="C52" s="39" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D52" s="40" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E52" s="39">
         <v>25</v>
@@ -51478,7 +52846,7 @@
         <v>13</v>
       </c>
       <c r="D53" s="40" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E53" s="39">
         <v>25</v>
@@ -51533,10 +52901,10 @@
         <v>146</v>
       </c>
       <c r="C54" s="39" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D54" s="40" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E54" s="39">
         <v>30</v>
@@ -51591,7 +52959,7 @@
         <v>817</v>
       </c>
       <c r="C55" s="135" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D55" s="136" t="s">
         <v>144</v>
@@ -51828,7 +53196,7 @@
         <v>11</v>
       </c>
       <c r="D6" s="63" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E6" s="63">
         <v>30</v>
@@ -51887,10 +53255,10 @@
         <v>904</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D8" s="63" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E8" s="63">
         <v>12.5</v>
@@ -51921,7 +53289,7 @@
         <v>391</v>
       </c>
       <c r="D9" s="70" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E9" s="70">
         <v>25</v>
@@ -52016,7 +53384,7 @@
         <v>6020</v>
       </c>
       <c r="B14" s="62" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C14" s="63"/>
       <c r="D14" s="63" t="s">
@@ -52045,7 +53413,7 @@
         <v>6021</v>
       </c>
       <c r="B15" s="69" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C15" s="70"/>
       <c r="D15" s="70" t="s">
@@ -52074,7 +53442,7 @@
         <v>6020</v>
       </c>
       <c r="B16" s="62" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C16" s="63"/>
       <c r="D16" s="63" t="s">
@@ -52103,7 +53471,7 @@
         <v>6021</v>
       </c>
       <c r="B17" s="69" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C17" s="70"/>
       <c r="D17" s="70" t="s">
@@ -52190,7 +53558,7 @@
         <v>6338</v>
       </c>
       <c r="B20" s="62" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C20" s="63"/>
       <c r="D20" s="63" t="s">
@@ -52219,7 +53587,7 @@
         <v>6531</v>
       </c>
       <c r="B21" s="69" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C21" s="70"/>
       <c r="D21" s="70" t="s">
@@ -52330,7 +53698,7 @@
         <v>6312</v>
       </c>
       <c r="B26" s="65" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C26" s="66"/>
       <c r="D26" s="66" t="s">
@@ -52357,7 +53725,7 @@
         <v>6338</v>
       </c>
       <c r="B27" s="62" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C27" s="63"/>
       <c r="D27" s="63" t="s">
@@ -52411,7 +53779,7 @@
         <v>6312</v>
       </c>
       <c r="B29" s="65" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C29" s="66"/>
       <c r="D29" s="66" t="s">
@@ -52465,7 +53833,7 @@
         <v>6530</v>
       </c>
       <c r="B31" s="62" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C31" s="63"/>
       <c r="D31" s="63" t="s">
@@ -52492,7 +53860,7 @@
         <v>6531</v>
       </c>
       <c r="B32" s="65" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C32" s="66"/>
       <c r="D32" s="66" t="s">
@@ -52643,7 +54011,7 @@
         <v>167</v>
       </c>
       <c r="C38" s="63" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D38" s="63" t="s">
         <v>57</v>
@@ -52674,7 +54042,7 @@
         <v>167</v>
       </c>
       <c r="C39" s="70" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D39" s="70" t="s">
         <v>50</v>
@@ -52860,7 +54228,7 @@
         <v>34</v>
       </c>
       <c r="C45" s="70" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D45" s="70" t="s">
         <v>57</v>
@@ -52891,7 +54259,7 @@
         <v>34</v>
       </c>
       <c r="C46" s="63" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D46" s="63" t="s">
         <v>71</v>
@@ -52922,7 +54290,7 @@
         <v>34</v>
       </c>
       <c r="C47" s="70" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D47" s="70" t="s">
         <v>50</v>
@@ -53139,7 +54507,7 @@
         <v>181</v>
       </c>
       <c r="C54" s="63" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D54" s="63" t="s">
         <v>57</v>
@@ -53170,7 +54538,7 @@
         <v>181</v>
       </c>
       <c r="C55" s="70" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D55" s="70" t="s">
         <v>50</v>
@@ -53201,7 +54569,7 @@
         <v>9</v>
       </c>
       <c r="C56" s="63" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D56" s="63" t="s">
         <v>57</v>
@@ -53232,7 +54600,7 @@
         <v>9</v>
       </c>
       <c r="C57" s="70" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D57" s="70" t="s">
         <v>50</v>
@@ -53356,7 +54724,7 @@
         <v>901</v>
       </c>
       <c r="C61" s="70" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D61" s="70" t="s">
         <v>57</v>
@@ -53387,7 +54755,7 @@
         <v>901</v>
       </c>
       <c r="C62" s="63" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D62" s="63" t="s">
         <v>50</v>
@@ -53418,7 +54786,7 @@
         <v>901</v>
       </c>
       <c r="C63" s="70" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D63" s="70" t="s">
         <v>95</v>
@@ -53874,7 +55242,7 @@
         <v>166</v>
       </c>
       <c r="C83" s="63" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D83" s="63" t="s">
         <v>526</v>
@@ -53901,7 +55269,7 @@
         <v>171</v>
       </c>
       <c r="C84" s="70" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D84" s="70" t="s">
         <v>526</v>
@@ -53982,7 +55350,7 @@
         <v>901</v>
       </c>
       <c r="C87" s="63" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D87" s="63" t="s">
         <v>526</v>
@@ -54009,7 +55377,7 @@
         <v>142</v>
       </c>
       <c r="C88" s="70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D88" s="70" t="s">
         <v>526</v>
@@ -54036,7 +55404,7 @@
         <v>157</v>
       </c>
       <c r="C89" s="63" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D89" s="63" t="s">
         <v>526</v>
@@ -54063,7 +55431,7 @@
         <v>192</v>
       </c>
       <c r="C90" s="70" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D90" s="70" t="s">
         <v>526</v>
@@ -55220,14 +56588,14 @@
   </autoFilter>
   <mergeCells count="9">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A75:K75"/>
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A92:K92"/>
+    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A65:K65"/>
     <mergeCell ref="A81:K81"/>
-    <mergeCell ref="A75:K75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -55313,7 +56681,7 @@
         <v>135</v>
       </c>
       <c r="D4" s="270" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E4" s="269" t="s">
         <v>584</v>
@@ -55337,19 +56705,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="269">
-        <v>6228</v>
+        <v>8010</v>
       </c>
       <c r="C5" s="270" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="270" t="s">
-        <v>16</v>
+        <v>184</v>
       </c>
       <c r="E5" s="269" t="s">
         <v>587</v>
       </c>
       <c r="F5" s="271">
-        <v>20769</v>
+        <v>11500</v>
       </c>
       <c r="G5" s="269" t="s">
         <v>585</v>
@@ -55367,19 +56735,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="269">
-        <v>6206</v>
+        <v>8005</v>
       </c>
       <c r="C6" s="270" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D6" s="270" t="s">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="E6" s="269" t="s">
         <v>588</v>
       </c>
       <c r="F6" s="271">
-        <v>35000</v>
+        <v>12840</v>
       </c>
       <c r="G6" s="269" t="s">
         <v>585</v>
@@ -55400,13 +56768,13 @@
         <v>4050</v>
       </c>
       <c r="C7" s="270" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D7" s="270" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E7" s="269" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F7" s="271">
         <v>9450</v>
@@ -55430,13 +56798,13 @@
         <v>6337</v>
       </c>
       <c r="C8" s="270" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D8" s="270" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E8" s="269" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F8" s="271">
         <v>15680</v>
@@ -55460,13 +56828,13 @@
         <v>6416</v>
       </c>
       <c r="C9" s="270" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D9" s="270" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E9" s="269" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F9" s="271">
         <v>15435</v>
@@ -55490,13 +56858,13 @@
         <v>6531</v>
       </c>
       <c r="C10" s="270" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D10" s="270" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E10" s="269" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F10" s="271">
         <v>4320</v>
@@ -55520,16 +56888,16 @@
         <v>6530</v>
       </c>
       <c r="C11" s="270" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D11" s="270" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E11" s="269" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F11" s="271">
-        <v>4500</v>
+        <v>15422</v>
       </c>
       <c r="G11" s="269" t="s">
         <v>585</v>
@@ -55553,10 +56921,10 @@
         <v>13</v>
       </c>
       <c r="D12" s="270" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E12" s="269" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F12" s="271">
         <v>46000</v>
@@ -55565,7 +56933,7 @@
         <v>585</v>
       </c>
       <c r="H12" s="272" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="I12" s="273"/>
       <c r="J12" s="274"/>
@@ -55583,10 +56951,10 @@
         <v>13</v>
       </c>
       <c r="D13" s="270" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E13" s="269" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F13" s="271">
         <v>16000</v>
@@ -55595,7 +56963,7 @@
         <v>585</v>
       </c>
       <c r="H13" s="272" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I13" s="273"/>
       <c r="J13" s="274"/>
@@ -55613,7 +56981,7 @@
         <v>135</v>
       </c>
       <c r="D14" s="270" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E14" s="269" t="s">
         <v>584</v>
@@ -55625,7 +56993,7 @@
         <v>585</v>
       </c>
       <c r="H14" s="272" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="I14" s="273"/>
       <c r="J14" s="274"/>
@@ -55646,16 +57014,16 @@
         <v>20</v>
       </c>
       <c r="E15" s="269" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F15" s="271">
-        <v>35970</v>
+        <v>37000</v>
       </c>
       <c r="G15" s="269" t="s">
         <v>585</v>
       </c>
       <c r="H15" s="272" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="I15" s="273"/>
       <c r="J15" s="274"/>
@@ -55676,16 +57044,16 @@
         <v>20</v>
       </c>
       <c r="E16" s="269" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F16" s="271">
-        <v>28082</v>
+        <v>25000</v>
       </c>
       <c r="G16" s="269" t="s">
         <v>585</v>
       </c>
       <c r="H16" s="272" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="I16" s="273"/>
       <c r="J16" s="274"/>
@@ -55697,25 +57065,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="269">
-        <v>6515</v>
+        <v>5699</v>
       </c>
       <c r="C17" s="270" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D17" s="270" t="s">
-        <v>22</v>
+        <v>196</v>
       </c>
       <c r="E17" s="269" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="F17" s="271">
-        <v>10000</v>
+        <v>14790</v>
       </c>
       <c r="G17" s="269" t="s">
         <v>585</v>
       </c>
       <c r="H17" s="272" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="I17" s="273"/>
       <c r="J17" s="274"/>
@@ -55723,29 +57091,29 @@
       <c r="L17" s="274"/>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="275">
+      <c r="A18" s="269">
         <v>15</v>
       </c>
-      <c r="B18" s="275">
-        <v>6530</v>
-      </c>
-      <c r="C18" s="276" t="s">
-        <v>223</v>
-      </c>
-      <c r="D18" s="276" t="s">
-        <v>224</v>
-      </c>
-      <c r="E18" s="275" t="s">
-        <v>589</v>
-      </c>
-      <c r="F18" s="277">
-        <v>11340</v>
-      </c>
-      <c r="G18" s="275" t="s">
-        <v>596</v>
-      </c>
-      <c r="H18" s="278" t="s">
+      <c r="B18" s="269">
+        <v>5731</v>
+      </c>
+      <c r="C18" s="270" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="270" t="s">
+        <v>197</v>
+      </c>
+      <c r="E18" s="269" t="s">
         <v>597</v>
+      </c>
+      <c r="F18" s="271">
+        <v>13770</v>
+      </c>
+      <c r="G18" s="269" t="s">
+        <v>585</v>
+      </c>
+      <c r="H18" s="272" t="s">
+        <v>598</v>
       </c>
       <c r="I18" s="273"/>
       <c r="J18" s="274"/>
@@ -55753,29 +57121,29 @@
       <c r="L18" s="274"/>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="269">
+      <c r="A19" s="275">
         <v>16</v>
       </c>
-      <c r="B19" s="269">
-        <v>5699</v>
-      </c>
-      <c r="C19" s="270" t="s">
+      <c r="B19" s="275">
+        <v>6624</v>
+      </c>
+      <c r="C19" s="276" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="270" t="s">
-        <v>195</v>
-      </c>
-      <c r="E19" s="269" t="s">
+      <c r="D19" s="276" t="s">
+        <v>192</v>
+      </c>
+      <c r="E19" s="275" t="s">
+        <v>599</v>
+      </c>
+      <c r="F19" s="277">
+        <v>15876</v>
+      </c>
+      <c r="G19" s="275" t="s">
+        <v>600</v>
+      </c>
+      <c r="H19" s="278" t="s">
         <v>598</v>
-      </c>
-      <c r="F19" s="271">
-        <v>14790</v>
-      </c>
-      <c r="G19" s="269" t="s">
-        <v>585</v>
-      </c>
-      <c r="H19" s="272" t="s">
-        <v>599</v>
       </c>
       <c r="I19" s="273"/>
       <c r="J19" s="274"/>
@@ -55783,29 +57151,29 @@
       <c r="L19" s="274"/>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="269">
+      <c r="A20" s="275">
         <v>17</v>
       </c>
-      <c r="B20" s="269">
+      <c r="B20" s="275">
         <v>5731</v>
       </c>
-      <c r="C20" s="270" t="s">
+      <c r="C20" s="276" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="270" t="s">
-        <v>196</v>
-      </c>
-      <c r="E20" s="269" t="s">
+      <c r="D20" s="276" t="s">
+        <v>197</v>
+      </c>
+      <c r="E20" s="275" t="s">
+        <v>597</v>
+      </c>
+      <c r="F20" s="277">
+        <v>33660</v>
+      </c>
+      <c r="G20" s="275" t="s">
+        <v>600</v>
+      </c>
+      <c r="H20" s="278" t="s">
         <v>598</v>
-      </c>
-      <c r="F20" s="271">
-        <v>13770</v>
-      </c>
-      <c r="G20" s="269" t="s">
-        <v>585</v>
-      </c>
-      <c r="H20" s="272" t="s">
-        <v>599</v>
       </c>
       <c r="I20" s="273"/>
       <c r="J20" s="274"/>
@@ -55813,60 +57181,28 @@
       <c r="L20" s="274"/>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="275">
-        <v>18</v>
-      </c>
-      <c r="B21" s="275">
-        <v>6624</v>
-      </c>
-      <c r="C21" s="276" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="276" t="s">
-        <v>191</v>
-      </c>
-      <c r="E21" s="275" t="s">
-        <v>600</v>
-      </c>
-      <c r="F21" s="277">
-        <v>15876</v>
-      </c>
-      <c r="G21" s="275" t="s">
-        <v>596</v>
-      </c>
-      <c r="H21" s="278" t="s">
-        <v>599</v>
-      </c>
+      <c r="A21" s="279"/>
+      <c r="B21" s="279"/>
+      <c r="C21" s="280"/>
+      <c r="D21" s="280"/>
+      <c r="E21" s="279"/>
+      <c r="F21" s="281"/>
+      <c r="G21" s="279"/>
+      <c r="H21" s="282"/>
       <c r="I21" s="273"/>
       <c r="J21" s="274"/>
       <c r="K21" s="274"/>
       <c r="L21" s="274"/>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="275">
-        <v>19</v>
-      </c>
-      <c r="B22" s="275">
-        <v>5731</v>
-      </c>
-      <c r="C22" s="276" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="276" t="s">
-        <v>196</v>
-      </c>
-      <c r="E22" s="275" t="s">
-        <v>598</v>
-      </c>
-      <c r="F22" s="277">
-        <v>33660</v>
-      </c>
-      <c r="G22" s="275" t="s">
-        <v>596</v>
-      </c>
-      <c r="H22" s="278" t="s">
-        <v>599</v>
-      </c>
+      <c r="A22" s="279"/>
+      <c r="B22" s="279"/>
+      <c r="C22" s="280"/>
+      <c r="D22" s="280"/>
+      <c r="E22" s="279"/>
+      <c r="F22" s="281"/>
+      <c r="G22" s="279"/>
+      <c r="H22" s="282"/>
       <c r="I22" s="273"/>
       <c r="J22" s="274"/>
       <c r="K22" s="274"/>
